--- a/Vessel_Device_Installation_Tracker NV.xlsx
+++ b/Vessel_Device_Installation_Tracker NV.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://britoilos-my.sharepoint.com/personal/axel_faurax_britoil_com_sg/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Axel.Faurax\OneDrive - Britoil Offshore Services Pte Ltd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1774" documentId="13_ncr:1_{E5929760-29B4-4FBD-B5DB-E23A2F078BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E30172E6-81BF-412B-BD12-AAFCD4002696}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EA246E-B88E-4322-AD10-B37DD069D849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="322">
   <si>
     <r>
       <t>This is the Vessel</t>
@@ -1110,9 +1110,6 @@
     <t>POC OK?</t>
   </si>
   <si>
-    <t>BOS Express</t>
-  </si>
-  <si>
     <t>Britoil Dynamic</t>
   </si>
   <si>
@@ -1159,6 +1156,21 @@
   </si>
   <si>
     <t>Savings Scope1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask for quotes </t>
+  </si>
+  <si>
+    <t>Ask for quotes</t>
+  </si>
+  <si>
+    <t>Britoil Courage</t>
+  </si>
+  <si>
+    <t>Was intalled with cap eye , but we remove after end of charter</t>
+  </si>
+  <si>
+    <t>Installed on Propeller, bow thrusters, sea chest</t>
   </si>
 </sst>
 </file>
@@ -2372,6 +2384,21 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2388,69 +2415,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2525,11 +2489,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2977,7 +2989,7 @@
                 <c:formatCode>"$"#,##0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>83316.233401907608</c:v>
+                  <c:v>79887.581821582193</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>61944.305217879184</c:v>
@@ -3468,10 +3480,10 @@
                 <c:formatCode>"$"#,##0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>678473.38040022447</c:v>
+                  <c:v>694442.61548531894</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>396663.58238264447</c:v>
+                  <c:v>393234.93080231902</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>477830.54984103231</c:v>
@@ -4058,7 +4070,7 @@
                   <c:v>289000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>215600</c:v>
+                  <c:v>223300</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>90000</c:v>
@@ -4073,7 +4085,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24000</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>210000</c:v>
@@ -4395,10 +4407,10 @@
                   <c:v>20775.241297436187</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24791.473898915279</c:v>
+                  <c:v>24577.183175144939</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24231.192157150876</c:v>
+                  <c:v>24801.521981618534</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4876,7 +4888,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>180</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -5336,7 +5348,7 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>137.4516695199321</c:v>
+                  <c:v>134.81424522737407</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="General">
                   <c:v>100.21664275503811</c:v>
@@ -6070,13 +6082,13 @@
                   <c:v>0.25714285714285712</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.58730158730158732</c:v>
+                  <c:v>0.95454545454545459</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.28888888888888886</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.39436619718309857</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -6085,7 +6097,7 @@
                   <c:v>1.3888888888888888E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.6</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.97222222222222221</c:v>
@@ -6097,7 +6109,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.62228672047360289</c:v>
+                  <c:v>0.64709378138821827</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6414,7 +6426,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>217</c:v>
+                  <c:v>218</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -6479,7 +6491,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>21</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -6546,7 +6558,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>332</c:v>
+                  <c:v>306</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -6614,7 +6626,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>570</c:v>
+                  <c:v>550</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -12301,34 +12313,34 @@
       <c r="I1" s="8"/>
       <c r="J1" s="49"/>
       <c r="K1" s="9"/>
-      <c r="AB1" s="161" t="s">
+      <c r="AB1" s="155" t="s">
         <v>293</v>
       </c>
-      <c r="AC1" s="162"/>
-      <c r="AD1" s="162"/>
-      <c r="AE1" s="163"/>
-      <c r="AM1" s="161" t="s">
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
+      <c r="AE1" s="157"/>
+      <c r="AM1" s="155" t="s">
         <v>292</v>
       </c>
-      <c r="AN1" s="162"/>
-      <c r="AO1" s="162"/>
-      <c r="AP1" s="163"/>
+      <c r="AN1" s="156"/>
+      <c r="AO1" s="156"/>
+      <c r="AP1" s="157"/>
     </row>
     <row r="2" spans="1:43" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="182" t="s">
+      <c r="B2" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="183"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="194" t="s">
+      <c r="C2" s="167"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="178" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="195"/>
-      <c r="G2" s="195"/>
-      <c r="H2" s="196"/>
+      <c r="F2" s="179"/>
+      <c r="G2" s="179"/>
+      <c r="H2" s="180"/>
       <c r="I2" s="48"/>
       <c r="J2" s="50"/>
-      <c r="K2" s="174" t="s">
+      <c r="K2" s="207" t="s">
         <v>1</v>
       </c>
       <c r="N2" s="8" t="s">
@@ -12341,14 +12353,14 @@
         <f>2000*0.01</f>
         <v>20</v>
       </c>
-      <c r="T2" s="164" t="s">
+      <c r="T2" s="197" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="167" t="s">
+      <c r="U2" s="200" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="167"/>
-      <c r="W2" s="168"/>
+      <c r="V2" s="200"/>
+      <c r="W2" s="201"/>
       <c r="AB2" s="23" t="s">
         <v>97</v>
       </c>
@@ -12381,16 +12393,16 @@
       </c>
     </row>
     <row r="3" spans="1:43" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="185"/>
-      <c r="C3" s="186"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="198"/>
-      <c r="G3" s="198"/>
-      <c r="H3" s="199"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="181"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="182"/>
+      <c r="H3" s="183"/>
       <c r="I3" s="48"/>
       <c r="J3" s="50"/>
-      <c r="K3" s="169"/>
+      <c r="K3" s="202"/>
       <c r="N3" s="8" t="s">
         <v>114</v>
       </c>
@@ -12401,10 +12413,10 @@
         <f>O3*Q2</f>
         <v>64</v>
       </c>
-      <c r="T3" s="165"/>
-      <c r="U3" s="169"/>
-      <c r="V3" s="169"/>
-      <c r="W3" s="170"/>
+      <c r="T3" s="198"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="202"/>
+      <c r="W3" s="203"/>
       <c r="AB3" s="137" t="s">
         <v>13</v>
       </c>
@@ -12437,26 +12449,26 @@
       </c>
     </row>
     <row r="4" spans="1:43" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="192" t="s">
+      <c r="B4" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="188" t="s">
+      <c r="C4" s="172" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="189"/>
-      <c r="E4" s="200" t="s">
+      <c r="D4" s="173"/>
+      <c r="E4" s="184" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="202" t="s">
+      <c r="F4" s="186" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="202"/>
-      <c r="H4" s="204" t="s">
+      <c r="G4" s="186"/>
+      <c r="H4" s="188" t="s">
         <v>132</v>
       </c>
       <c r="I4" s="47"/>
       <c r="J4" s="51"/>
-      <c r="K4" s="169"/>
+      <c r="K4" s="202"/>
       <c r="N4" s="8" t="s">
         <v>117</v>
       </c>
@@ -12470,10 +12482,10 @@
         <f>8000/25</f>
         <v>320</v>
       </c>
-      <c r="T4" s="165"/>
-      <c r="U4" s="169"/>
-      <c r="V4" s="169"/>
-      <c r="W4" s="170"/>
+      <c r="T4" s="198"/>
+      <c r="U4" s="202"/>
+      <c r="V4" s="202"/>
+      <c r="W4" s="203"/>
       <c r="AB4" s="109" t="s">
         <v>93</v>
       </c>
@@ -12507,20 +12519,20 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="192"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="200"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="204"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="188"/>
       <c r="I5" s="47"/>
       <c r="J5" s="51"/>
-      <c r="K5" s="169"/>
-      <c r="T5" s="165"/>
-      <c r="U5" s="169"/>
-      <c r="V5" s="169"/>
-      <c r="W5" s="170"/>
+      <c r="K5" s="202"/>
+      <c r="T5" s="198"/>
+      <c r="U5" s="202"/>
+      <c r="V5" s="202"/>
+      <c r="W5" s="203"/>
       <c r="AB5" s="109" t="s">
         <v>110</v>
       </c>
@@ -12554,20 +12566,20 @@
       </c>
     </row>
     <row r="6" spans="1:43" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="193"/>
-      <c r="C6" s="190"/>
-      <c r="D6" s="191"/>
-      <c r="E6" s="201"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="205"/>
+      <c r="B6" s="177"/>
+      <c r="C6" s="174"/>
+      <c r="D6" s="175"/>
+      <c r="E6" s="185"/>
+      <c r="F6" s="187"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="189"/>
       <c r="I6" s="47"/>
       <c r="J6" s="51"/>
-      <c r="K6" s="169"/>
-      <c r="T6" s="166"/>
-      <c r="U6" s="171"/>
-      <c r="V6" s="171"/>
-      <c r="W6" s="172"/>
+      <c r="K6" s="202"/>
+      <c r="T6" s="199"/>
+      <c r="U6" s="204"/>
+      <c r="V6" s="204"/>
+      <c r="W6" s="205"/>
       <c r="AB6" s="109" t="s">
         <v>290</v>
       </c>
@@ -12730,13 +12742,13 @@
       <c r="A9" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="158">
+      <c r="B9" s="163">
         <v>1</v>
       </c>
-      <c r="C9" s="158" t="s">
+      <c r="C9" s="163" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="158" t="s">
+      <c r="D9" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="26" t="s">
@@ -12809,9 +12821,9 @@
       </c>
     </row>
     <row r="10" spans="1:43" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="159"/>
+      <c r="B10" s="164"/>
+      <c r="C10" s="164"/>
+      <c r="D10" s="164"/>
       <c r="E10" s="3" t="s">
         <v>106</v>
       </c>
@@ -12881,9 +12893,9 @@
       </c>
     </row>
     <row r="11" spans="1:43" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="159"/>
-      <c r="C11" s="159"/>
-      <c r="D11" s="159"/>
+      <c r="B11" s="164"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="164"/>
       <c r="E11" s="3" t="s">
         <v>109</v>
       </c>
@@ -12954,9 +12966,9 @@
       </c>
     </row>
     <row r="12" spans="1:43" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="159"/>
-      <c r="C12" s="159"/>
-      <c r="D12" s="159"/>
+      <c r="B12" s="164"/>
+      <c r="C12" s="164"/>
+      <c r="D12" s="164"/>
       <c r="E12" s="3" t="s">
         <v>13</v>
       </c>
@@ -13012,9 +13024,9 @@
       </c>
     </row>
     <row r="13" spans="1:43" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="160"/>
-      <c r="C13" s="160"/>
-      <c r="D13" s="160"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
       <c r="E13" s="3" t="s">
         <v>14</v>
       </c>
@@ -13073,13 +13085,13 @@
       <c r="A14" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="155">
+      <c r="B14" s="160">
         <v>2</v>
       </c>
-      <c r="C14" s="155" t="s">
+      <c r="C14" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="155" t="s">
+      <c r="D14" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="27" t="s">
@@ -13099,7 +13111,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K14" s="155" t="s">
+      <c r="K14" s="160" t="s">
         <v>172</v>
       </c>
       <c r="L14" s="44"/>
@@ -13121,7 +13133,7 @@
       </c>
       <c r="Z14" s="121"/>
       <c r="AB14" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AC14" s="8">
         <v>10000</v>
@@ -13150,9 +13162,9 @@
       </c>
     </row>
     <row r="15" spans="1:43" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="156"/>
-      <c r="C15" s="156"/>
-      <c r="D15" s="156"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="161"/>
+      <c r="D15" s="161"/>
       <c r="E15" s="6" t="s">
         <v>106</v>
       </c>
@@ -13172,7 +13184,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K15" s="156"/>
+      <c r="K15" s="161"/>
       <c r="L15" s="45"/>
       <c r="U15" s="119" t="s">
         <v>15</v>
@@ -13191,7 +13203,7 @@
       </c>
       <c r="Z15" s="121"/>
       <c r="AB15" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AC15" s="8">
         <v>8000</v>
@@ -13223,9 +13235,9 @@
       </c>
     </row>
     <row r="16" spans="1:43" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="156"/>
-      <c r="C16" s="156"/>
-      <c r="D16" s="156"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="161"/>
+      <c r="D16" s="161"/>
       <c r="E16" s="6" t="s">
         <v>109</v>
       </c>
@@ -13245,7 +13257,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K16" s="156"/>
+      <c r="K16" s="161"/>
       <c r="L16" s="45"/>
       <c r="U16" s="119" t="s">
         <v>15</v>
@@ -13296,9 +13308,9 @@
       </c>
     </row>
     <row r="17" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="161"/>
+      <c r="D17" s="161"/>
       <c r="E17" s="6" t="s">
         <v>13</v>
       </c>
@@ -13320,7 +13332,7 @@
         <f t="shared" si="3"/>
         <v>32.915653637553767</v>
       </c>
-      <c r="K17" s="156"/>
+      <c r="K17" s="161"/>
       <c r="L17" s="45"/>
       <c r="U17" s="119" t="s">
         <v>15</v>
@@ -13355,9 +13367,9 @@
       </c>
     </row>
     <row r="18" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="157"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="157"/>
+      <c r="B18" s="162"/>
+      <c r="C18" s="162"/>
+      <c r="D18" s="162"/>
       <c r="E18" s="6" t="s">
         <v>14</v>
       </c>
@@ -13377,7 +13389,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K18" s="157"/>
+      <c r="K18" s="162"/>
       <c r="L18" s="46"/>
       <c r="U18" s="119" t="s">
         <v>15</v>
@@ -13415,13 +13427,13 @@
       <c r="A19" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="158">
+      <c r="B19" s="163">
         <v>3</v>
       </c>
-      <c r="C19" s="158" t="s">
+      <c r="C19" s="163" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="158" t="s">
+      <c r="D19" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E19" s="26" t="s">
@@ -13488,9 +13500,9 @@
       </c>
     </row>
     <row r="20" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="159"/>
-      <c r="C20" s="159"/>
-      <c r="D20" s="159"/>
+      <c r="B20" s="164"/>
+      <c r="C20" s="164"/>
+      <c r="D20" s="164"/>
       <c r="E20" s="3" t="s">
         <v>13</v>
       </c>
@@ -13545,9 +13557,9 @@
       </c>
     </row>
     <row r="21" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="159"/>
-      <c r="C21" s="159"/>
-      <c r="D21" s="159"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="164"/>
       <c r="E21" s="3" t="s">
         <v>109</v>
       </c>
@@ -13599,9 +13611,9 @@
       </c>
     </row>
     <row r="22" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="159"/>
-      <c r="C22" s="159"/>
-      <c r="D22" s="159"/>
+      <c r="B22" s="164"/>
+      <c r="C22" s="164"/>
+      <c r="D22" s="164"/>
       <c r="E22" s="3" t="s">
         <v>106</v>
       </c>
@@ -13656,9 +13668,9 @@
       </c>
     </row>
     <row r="23" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="160"/>
-      <c r="C23" s="160"/>
-      <c r="D23" s="160"/>
+      <c r="B23" s="165"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="165"/>
       <c r="E23" s="3" t="s">
         <v>14</v>
       </c>
@@ -13716,13 +13728,13 @@
       <c r="A24" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B24" s="155">
+      <c r="B24" s="160">
         <v>4</v>
       </c>
-      <c r="C24" s="155" t="s">
+      <c r="C24" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="155" t="s">
+      <c r="D24" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="27" t="s">
@@ -13742,7 +13754,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K24" s="179" t="s">
+      <c r="K24" s="190" t="s">
         <v>100</v>
       </c>
       <c r="L24" s="44"/>
@@ -13767,9 +13779,9 @@
       <c r="Z24" s="121"/>
     </row>
     <row r="25" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="156"/>
-      <c r="C25" s="156"/>
-      <c r="D25" s="156"/>
+      <c r="B25" s="161"/>
+      <c r="C25" s="161"/>
+      <c r="D25" s="161"/>
       <c r="E25" s="6" t="s">
         <v>13</v>
       </c>
@@ -13789,7 +13801,7 @@
         <f t="shared" si="3"/>
         <v>83.2</v>
       </c>
-      <c r="K25" s="180"/>
+      <c r="K25" s="191"/>
       <c r="L25" s="45"/>
       <c r="U25" s="119" t="s">
         <v>18</v>
@@ -13807,15 +13819,15 @@
         <v>32083</v>
       </c>
       <c r="Z25" s="121"/>
-      <c r="AJ25" s="206" t="s">
+      <c r="AJ25" s="158" t="s">
         <v>159</v>
       </c>
-      <c r="AK25" s="207"/>
+      <c r="AK25" s="159"/>
     </row>
     <row r="26" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="156"/>
-      <c r="C26" s="156"/>
-      <c r="D26" s="156"/>
+      <c r="B26" s="161"/>
+      <c r="C26" s="161"/>
+      <c r="D26" s="161"/>
       <c r="E26" s="6" t="s">
         <v>109</v>
       </c>
@@ -13835,7 +13847,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K26" s="180"/>
+      <c r="K26" s="191"/>
       <c r="L26" s="45"/>
       <c r="U26" s="119" t="s">
         <v>18</v>
@@ -13855,9 +13867,9 @@
       <c r="Z26" s="121"/>
     </row>
     <row r="27" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="156"/>
-      <c r="C27" s="156"/>
-      <c r="D27" s="156"/>
+      <c r="B27" s="161"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="161"/>
       <c r="E27" s="6" t="s">
         <v>106</v>
       </c>
@@ -13877,7 +13889,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K27" s="180"/>
+      <c r="K27" s="191"/>
       <c r="L27" s="45"/>
       <c r="U27" s="119" t="s">
         <v>18</v>
@@ -13897,9 +13909,9 @@
       <c r="Z27" s="121"/>
     </row>
     <row r="28" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="157"/>
-      <c r="C28" s="157"/>
-      <c r="D28" s="157"/>
+      <c r="B28" s="162"/>
+      <c r="C28" s="162"/>
+      <c r="D28" s="162"/>
       <c r="E28" s="7" t="s">
         <v>14</v>
       </c>
@@ -13921,7 +13933,7 @@
         <f t="shared" si="3"/>
         <v>10.4</v>
       </c>
-      <c r="K28" s="181"/>
+      <c r="K28" s="192"/>
       <c r="L28" s="46"/>
       <c r="U28" s="119" t="s">
         <v>18</v>
@@ -13944,13 +13956,13 @@
       <c r="A29" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="158">
+      <c r="B29" s="163">
         <v>5</v>
       </c>
-      <c r="C29" s="158" t="s">
+      <c r="C29" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="158" t="s">
+      <c r="D29" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="26" t="s">
@@ -14005,9 +14017,9 @@
       </c>
     </row>
     <row r="30" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="159"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="159"/>
+      <c r="B30" s="164"/>
+      <c r="C30" s="164"/>
+      <c r="D30" s="164"/>
       <c r="E30" s="3" t="s">
         <v>13</v>
       </c>
@@ -14069,9 +14081,9 @@
       </c>
     </row>
     <row r="31" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="159"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="159"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
       <c r="E31" s="3" t="s">
         <v>109</v>
       </c>
@@ -14134,9 +14146,9 @@
       </c>
     </row>
     <row r="32" spans="1:38" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="159"/>
-      <c r="C32" s="159"/>
-      <c r="D32" s="159"/>
+      <c r="B32" s="164"/>
+      <c r="C32" s="164"/>
+      <c r="D32" s="164"/>
       <c r="E32" s="3" t="s">
         <v>106</v>
       </c>
@@ -14199,9 +14211,9 @@
       </c>
     </row>
     <row r="33" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="160"/>
-      <c r="C33" s="160"/>
-      <c r="D33" s="160"/>
+      <c r="B33" s="165"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
       <c r="E33" s="4" t="s">
         <v>14</v>
       </c>
@@ -14267,13 +14279,13 @@
       <c r="A34" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="155">
+      <c r="B34" s="160">
         <v>6</v>
       </c>
-      <c r="C34" s="155" t="s">
+      <c r="C34" s="160" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="155" t="s">
+      <c r="D34" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="27" t="s">
@@ -14336,9 +14348,9 @@
       </c>
     </row>
     <row r="35" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="156"/>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
+      <c r="B35" s="161"/>
+      <c r="C35" s="161"/>
+      <c r="D35" s="161"/>
       <c r="E35" s="6" t="s">
         <v>13</v>
       </c>
@@ -14401,9 +14413,9 @@
       </c>
     </row>
     <row r="36" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="156"/>
-      <c r="C36" s="156"/>
-      <c r="D36" s="156"/>
+      <c r="B36" s="161"/>
+      <c r="C36" s="161"/>
+      <c r="D36" s="161"/>
       <c r="E36" s="6" t="s">
         <v>109</v>
       </c>
@@ -14466,9 +14478,9 @@
       </c>
     </row>
     <row r="37" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="156"/>
-      <c r="C37" s="156"/>
-      <c r="D37" s="156"/>
+      <c r="B37" s="161"/>
+      <c r="C37" s="161"/>
+      <c r="D37" s="161"/>
       <c r="E37" s="6" t="s">
         <v>106</v>
       </c>
@@ -14531,27 +14543,27 @@
       </c>
     </row>
     <row r="38" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="157"/>
-      <c r="C38" s="157"/>
-      <c r="D38" s="157"/>
+      <c r="B38" s="162"/>
+      <c r="C38" s="162"/>
+      <c r="D38" s="162"/>
       <c r="E38" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F38" s="32" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G38" s="38"/>
-      <c r="H38" s="63" t="str">
+      <c r="H38" s="63">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I38" s="63" t="str">
+        <v>1157.1909481952498</v>
+      </c>
+      <c r="I38" s="63">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J38" s="64" t="str">
+        <v>4783.0559192070323</v>
+      </c>
+      <c r="J38" s="64">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6.1716850570413317</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="46"/>
@@ -14599,13 +14611,13 @@
       <c r="A39" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B39" s="158">
+      <c r="B39" s="163">
         <v>7</v>
       </c>
-      <c r="C39" s="158" t="s">
+      <c r="C39" s="163" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="158" t="s">
+      <c r="D39" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E39" s="26" t="s">
@@ -14668,9 +14680,9 @@
       </c>
     </row>
     <row r="40" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="159"/>
-      <c r="C40" s="159"/>
-      <c r="D40" s="159"/>
+      <c r="B40" s="164"/>
+      <c r="C40" s="164"/>
+      <c r="D40" s="164"/>
       <c r="E40" s="3" t="s">
         <v>13</v>
       </c>
@@ -14733,9 +14745,9 @@
       </c>
     </row>
     <row r="41" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="159"/>
-      <c r="C41" s="159"/>
-      <c r="D41" s="159"/>
+      <c r="B41" s="164"/>
+      <c r="C41" s="164"/>
+      <c r="D41" s="164"/>
       <c r="E41" s="3" t="s">
         <v>109</v>
       </c>
@@ -14798,30 +14810,34 @@
       </c>
     </row>
     <row r="42" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="159"/>
-      <c r="C42" s="159"/>
-      <c r="D42" s="159"/>
+      <c r="B42" s="164"/>
+      <c r="C42" s="164"/>
+      <c r="D42" s="164"/>
       <c r="E42" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="G42" s="35"/>
-      <c r="H42" s="57" t="str">
+        <v>17</v>
+      </c>
+      <c r="G42" s="35">
+        <v>45951</v>
+      </c>
+      <c r="H42" s="57">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I42" s="57" t="str">
+        <v>6171.6850570413317</v>
+      </c>
+      <c r="I42" s="57">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J42" s="58" t="str">
+        <v>3857.3031606508325</v>
+      </c>
+      <c r="J42" s="58">
         <f t="shared" si="3"/>
-        <v/>
+        <v>35.487189077987658</v>
       </c>
       <c r="K42" s="3"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42" t="s">
+        <v>321</v>
+      </c>
       <c r="U42" s="119" t="str" cm="1">
         <f t="array" ref="U42">IF(C42="",INDEX(C39:C42,MATCH(TRUE,INDEX((C39:C42&lt;&gt;""),0),0)),C42)</f>
         <v>Britoil 63</v>
@@ -14840,7 +14856,7 @@
       </c>
       <c r="Z42" s="121"/>
       <c r="AB42" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AC42" s="118">
         <v>7216</v>
@@ -14863,9 +14879,9 @@
       </c>
     </row>
     <row r="43" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="159"/>
-      <c r="C43" s="159"/>
-      <c r="D43" s="159"/>
+      <c r="B43" s="164"/>
+      <c r="C43" s="164"/>
+      <c r="D43" s="164"/>
       <c r="E43" s="3" t="s">
         <v>106</v>
       </c>
@@ -14928,16 +14944,18 @@
       </c>
     </row>
     <row r="44" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="160"/>
-      <c r="C44" s="160"/>
-      <c r="D44" s="160"/>
+      <c r="B44" s="165"/>
+      <c r="C44" s="165"/>
+      <c r="D44" s="165"/>
       <c r="E44" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F44" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="35"/>
+      <c r="G44" s="35">
+        <v>45748</v>
+      </c>
       <c r="H44" s="57">
         <f t="shared" si="1"/>
         <v>1157.1909481952498</v>
@@ -14996,13 +15014,13 @@
       <c r="A45" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B45" s="155">
+      <c r="B45" s="160">
         <v>8</v>
       </c>
-      <c r="C45" s="155" t="s">
+      <c r="C45" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="155" t="s">
+      <c r="D45" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E45" s="27" t="s">
@@ -15065,9 +15083,9 @@
       </c>
     </row>
     <row r="46" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="156"/>
-      <c r="C46" s="156"/>
-      <c r="D46" s="156"/>
+      <c r="B46" s="161"/>
+      <c r="C46" s="161"/>
+      <c r="D46" s="161"/>
       <c r="E46" s="6" t="s">
         <v>13</v>
       </c>
@@ -15130,9 +15148,9 @@
       </c>
     </row>
     <row r="47" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="156"/>
-      <c r="C47" s="156"/>
-      <c r="D47" s="156"/>
+      <c r="B47" s="161"/>
+      <c r="C47" s="161"/>
+      <c r="D47" s="161"/>
       <c r="E47" s="6" t="s">
         <v>109</v>
       </c>
@@ -15195,9 +15213,9 @@
       </c>
     </row>
     <row r="48" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="156"/>
-      <c r="C48" s="156"/>
-      <c r="D48" s="156"/>
+      <c r="B48" s="161"/>
+      <c r="C48" s="161"/>
+      <c r="D48" s="161"/>
       <c r="E48" s="6" t="s">
         <v>106</v>
       </c>
@@ -15260,9 +15278,9 @@
       </c>
     </row>
     <row r="49" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="157"/>
-      <c r="C49" s="157"/>
-      <c r="D49" s="157"/>
+      <c r="B49" s="162"/>
+      <c r="C49" s="162"/>
+      <c r="D49" s="162"/>
       <c r="E49" s="7" t="s">
         <v>14</v>
       </c>
@@ -15328,13 +15346,13 @@
       <c r="A50" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B50" s="158">
+      <c r="B50" s="163">
         <v>9</v>
       </c>
-      <c r="C50" s="158" t="s">
+      <c r="C50" s="163" t="s">
         <v>24</v>
       </c>
-      <c r="D50" s="158" t="s">
+      <c r="D50" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E50" s="26" t="s">
@@ -15397,9 +15415,9 @@
       </c>
     </row>
     <row r="51" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="159"/>
-      <c r="C51" s="159"/>
-      <c r="D51" s="159"/>
+      <c r="B51" s="164"/>
+      <c r="C51" s="164"/>
+      <c r="D51" s="164"/>
       <c r="E51" s="3" t="s">
         <v>13</v>
       </c>
@@ -15462,9 +15480,9 @@
       </c>
     </row>
     <row r="52" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="159"/>
-      <c r="C52" s="159"/>
-      <c r="D52" s="159"/>
+      <c r="B52" s="164"/>
+      <c r="C52" s="164"/>
+      <c r="D52" s="164"/>
       <c r="E52" s="3" t="s">
         <v>109</v>
       </c>
@@ -15527,9 +15545,9 @@
       </c>
     </row>
     <row r="53" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="159"/>
-      <c r="C53" s="159"/>
-      <c r="D53" s="159"/>
+      <c r="B53" s="164"/>
+      <c r="C53" s="164"/>
+      <c r="D53" s="164"/>
       <c r="E53" s="3" t="s">
         <v>106</v>
       </c>
@@ -15592,9 +15610,9 @@
       </c>
     </row>
     <row r="54" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="160"/>
-      <c r="C54" s="160"/>
-      <c r="D54" s="160"/>
+      <c r="B54" s="165"/>
+      <c r="C54" s="165"/>
+      <c r="D54" s="165"/>
       <c r="E54" s="4" t="s">
         <v>14</v>
       </c>
@@ -15660,13 +15678,13 @@
       <c r="A55" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B55" s="155">
+      <c r="B55" s="160">
         <v>10</v>
       </c>
-      <c r="C55" s="155" t="s">
+      <c r="C55" s="160" t="s">
         <v>25</v>
       </c>
-      <c r="D55" s="155" t="s">
+      <c r="D55" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="27" t="s">
@@ -15729,9 +15747,9 @@
       </c>
     </row>
     <row r="56" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="156"/>
-      <c r="C56" s="156"/>
-      <c r="D56" s="156"/>
+      <c r="B56" s="161"/>
+      <c r="C56" s="161"/>
+      <c r="D56" s="161"/>
       <c r="E56" s="6" t="s">
         <v>13</v>
       </c>
@@ -15771,7 +15789,7 @@
       </c>
       <c r="Z56" s="121"/>
       <c r="AB56" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AC56" s="118">
         <v>8000</v>
@@ -15794,9 +15812,9 @@
       </c>
     </row>
     <row r="57" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="156"/>
-      <c r="C57" s="156"/>
-      <c r="D57" s="156"/>
+      <c r="B57" s="161"/>
+      <c r="C57" s="161"/>
+      <c r="D57" s="161"/>
       <c r="E57" s="6" t="s">
         <v>109</v>
       </c>
@@ -15859,9 +15877,9 @@
       </c>
     </row>
     <row r="58" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="156"/>
-      <c r="C58" s="156"/>
-      <c r="D58" s="156"/>
+      <c r="B58" s="161"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="161"/>
       <c r="E58" s="6" t="s">
         <v>106</v>
       </c>
@@ -15924,9 +15942,9 @@
       </c>
     </row>
     <row r="59" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="157"/>
-      <c r="C59" s="157"/>
-      <c r="D59" s="157"/>
+      <c r="B59" s="162"/>
+      <c r="C59" s="162"/>
+      <c r="D59" s="162"/>
       <c r="E59" s="7" t="s">
         <v>14</v>
       </c>
@@ -15994,13 +16012,13 @@
       <c r="A60" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="158">
+      <c r="B60" s="163">
         <v>11</v>
       </c>
-      <c r="C60" s="158" t="s">
+      <c r="C60" s="163" t="s">
         <v>26</v>
       </c>
-      <c r="D60" s="158" t="s">
+      <c r="D60" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E60" s="26" t="s">
@@ -16020,7 +16038,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K60" s="158" t="s">
+      <c r="K60" s="163" t="s">
         <v>165</v>
       </c>
       <c r="L60" s="41"/>
@@ -16065,9 +16083,9 @@
       </c>
     </row>
     <row r="61" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="159"/>
-      <c r="C61" s="159"/>
-      <c r="D61" s="159"/>
+      <c r="B61" s="164"/>
+      <c r="C61" s="164"/>
+      <c r="D61" s="164"/>
       <c r="E61" s="3" t="s">
         <v>13</v>
       </c>
@@ -16087,7 +16105,7 @@
         <f t="shared" si="3"/>
         <v>49.373480456330654</v>
       </c>
-      <c r="K61" s="159"/>
+      <c r="K61" s="164"/>
       <c r="L61" s="42" t="s">
         <v>166</v>
       </c>
@@ -16132,9 +16150,9 @@
       </c>
     </row>
     <row r="62" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="159"/>
-      <c r="C62" s="159"/>
-      <c r="D62" s="159"/>
+      <c r="B62" s="164"/>
+      <c r="C62" s="164"/>
+      <c r="D62" s="164"/>
       <c r="E62" s="3" t="s">
         <v>109</v>
       </c>
@@ -16154,7 +16172,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K62" s="159"/>
+      <c r="K62" s="164"/>
       <c r="L62" s="42"/>
       <c r="U62" s="119" t="str" cm="1">
         <f t="array" ref="U62">IF(C62="",INDEX(C59:C62,MATCH(TRUE,INDEX((C59:C62&lt;&gt;""),0),0)),C62)</f>
@@ -16197,9 +16215,9 @@
       </c>
     </row>
     <row r="63" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="159"/>
-      <c r="C63" s="159"/>
-      <c r="D63" s="159"/>
+      <c r="B63" s="164"/>
+      <c r="C63" s="164"/>
+      <c r="D63" s="164"/>
       <c r="E63" s="3" t="s">
         <v>106</v>
       </c>
@@ -16219,7 +16237,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K63" s="159"/>
+      <c r="K63" s="164"/>
       <c r="L63" s="42"/>
       <c r="U63" s="119" t="str" cm="1">
         <f t="array" ref="U63">IF(C63="",INDEX(C60:C63,MATCH(TRUE,INDEX((C60:C63&lt;&gt;""),0),0)),C63)</f>
@@ -16262,9 +16280,9 @@
       </c>
     </row>
     <row r="64" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="160"/>
-      <c r="C64" s="160"/>
-      <c r="D64" s="160"/>
+      <c r="B64" s="165"/>
+      <c r="C64" s="165"/>
+      <c r="D64" s="165"/>
       <c r="E64" s="4" t="s">
         <v>14</v>
       </c>
@@ -16284,7 +16302,7 @@
         <f t="shared" si="3"/>
         <v>6.1716850570413317</v>
       </c>
-      <c r="K64" s="160"/>
+      <c r="K64" s="165"/>
       <c r="L64" s="43"/>
       <c r="U64" s="119" t="str" cm="1">
         <f t="array" ref="U64">IF(C64="",INDEX(C60:C64,MATCH(TRUE,INDEX((C60:C64&lt;&gt;""),0),0)),C64)</f>
@@ -16330,13 +16348,13 @@
       <c r="A65" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B65" s="155">
+      <c r="B65" s="160">
         <v>12</v>
       </c>
-      <c r="C65" s="155" t="s">
+      <c r="C65" s="160" t="s">
         <v>27</v>
       </c>
-      <c r="D65" s="155" t="s">
+      <c r="D65" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E65" s="27" t="s">
@@ -16356,7 +16374,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K65" s="155" t="s">
+      <c r="K65" s="160" t="s">
         <v>146</v>
       </c>
       <c r="L65" s="44"/>
@@ -16401,9 +16419,9 @@
       </c>
     </row>
     <row r="66" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="156"/>
-      <c r="C66" s="156"/>
-      <c r="D66" s="156"/>
+      <c r="B66" s="161"/>
+      <c r="C66" s="161"/>
+      <c r="D66" s="161"/>
       <c r="E66" s="6" t="s">
         <v>13</v>
       </c>
@@ -16423,7 +16441,7 @@
         <f t="shared" si="3"/>
         <v>65.974939218253226</v>
       </c>
-      <c r="K66" s="156"/>
+      <c r="K66" s="161"/>
       <c r="L66" s="45"/>
       <c r="U66" s="119" t="str" cm="1">
         <f t="array" ref="U66">IF(C66="",INDEX(C62:C66,MATCH(TRUE,INDEX((C62:C66&lt;&gt;""),0),0)),C66)</f>
@@ -16466,9 +16484,9 @@
       </c>
     </row>
     <row r="67" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="156"/>
-      <c r="C67" s="156"/>
-      <c r="D67" s="156"/>
+      <c r="B67" s="161"/>
+      <c r="C67" s="161"/>
+      <c r="D67" s="161"/>
       <c r="E67" s="6" t="s">
         <v>109</v>
       </c>
@@ -16488,7 +16506,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K67" s="156"/>
+      <c r="K67" s="161"/>
       <c r="L67" s="45" t="s">
         <v>143</v>
       </c>
@@ -16533,9 +16551,9 @@
       </c>
     </row>
     <row r="68" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="156"/>
-      <c r="C68" s="156"/>
-      <c r="D68" s="156"/>
+      <c r="B68" s="161"/>
+      <c r="C68" s="161"/>
+      <c r="D68" s="161"/>
       <c r="E68" s="6" t="s">
         <v>106</v>
       </c>
@@ -16555,7 +16573,7 @@
         <f t="shared" si="3"/>
         <v>87.622966149242572</v>
       </c>
-      <c r="K68" s="156"/>
+      <c r="K68" s="161"/>
       <c r="L68" s="45" t="s">
         <v>147</v>
       </c>
@@ -16600,14 +16618,14 @@
       </c>
     </row>
     <row r="69" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="157"/>
-      <c r="C69" s="157"/>
-      <c r="D69" s="157"/>
+      <c r="B69" s="162"/>
+      <c r="C69" s="162"/>
+      <c r="D69" s="162"/>
       <c r="E69" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F69" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G69" s="38"/>
       <c r="H69" s="63" t="str">
@@ -16622,7 +16640,7 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="K69" s="157"/>
+      <c r="K69" s="162"/>
       <c r="L69" s="46"/>
       <c r="U69" s="119" t="str" cm="1">
         <f t="array" ref="U69">IF(C69="",INDEX(C65:C69,MATCH(TRUE,INDEX((C65:C69&lt;&gt;""),0),0)),C69)</f>
@@ -16668,13 +16686,13 @@
       <c r="A70" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B70" s="158">
+      <c r="B70" s="163">
         <v>13</v>
       </c>
-      <c r="C70" s="158" t="s">
+      <c r="C70" s="163" t="s">
         <v>28</v>
       </c>
-      <c r="D70" s="158" t="s">
+      <c r="D70" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E70" s="26" t="s">
@@ -16737,9 +16755,9 @@
       </c>
     </row>
     <row r="71" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="159"/>
-      <c r="C71" s="159"/>
-      <c r="D71" s="159"/>
+      <c r="B71" s="164"/>
+      <c r="C71" s="164"/>
+      <c r="D71" s="164"/>
       <c r="E71" s="3" t="s">
         <v>13</v>
       </c>
@@ -16802,9 +16820,9 @@
       </c>
     </row>
     <row r="72" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="159"/>
-      <c r="C72" s="159"/>
-      <c r="D72" s="159"/>
+      <c r="B72" s="164"/>
+      <c r="C72" s="164"/>
+      <c r="D72" s="164"/>
       <c r="E72" s="3" t="s">
         <v>103</v>
       </c>
@@ -16844,7 +16862,7 @@
       </c>
       <c r="Z72" s="121"/>
       <c r="AB72" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AC72" s="118">
         <v>5150</v>
@@ -16867,9 +16885,9 @@
       </c>
     </row>
     <row r="73" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="159"/>
-      <c r="C73" s="159"/>
-      <c r="D73" s="159"/>
+      <c r="B73" s="164"/>
+      <c r="C73" s="164"/>
+      <c r="D73" s="164"/>
       <c r="E73" s="3" t="s">
         <v>109</v>
       </c>
@@ -16932,9 +16950,9 @@
       </c>
     </row>
     <row r="74" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="159"/>
-      <c r="C74" s="159"/>
-      <c r="D74" s="159"/>
+      <c r="B74" s="164"/>
+      <c r="C74" s="164"/>
+      <c r="D74" s="164"/>
       <c r="E74" s="3" t="s">
         <v>106</v>
       </c>
@@ -16997,14 +17015,14 @@
       </c>
     </row>
     <row r="75" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="160"/>
-      <c r="C75" s="160"/>
-      <c r="D75" s="160"/>
+      <c r="B75" s="165"/>
+      <c r="C75" s="165"/>
+      <c r="D75" s="165"/>
       <c r="E75" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F75" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G75" s="35"/>
       <c r="H75" s="57" t="str">
@@ -17065,13 +17083,13 @@
       <c r="A76" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B76" s="155">
+      <c r="B76" s="160">
         <v>14</v>
       </c>
-      <c r="C76" s="155" t="s">
+      <c r="C76" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="D76" s="155" t="s">
+      <c r="D76" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E76" s="27" t="s">
@@ -17128,9 +17146,9 @@
       </c>
     </row>
     <row r="77" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="156"/>
-      <c r="C77" s="156"/>
-      <c r="D77" s="156"/>
+      <c r="B77" s="161"/>
+      <c r="C77" s="161"/>
+      <c r="D77" s="161"/>
       <c r="E77" s="6" t="s">
         <v>13</v>
       </c>
@@ -17187,9 +17205,9 @@
       </c>
     </row>
     <row r="78" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="156"/>
-      <c r="C78" s="156"/>
-      <c r="D78" s="156"/>
+      <c r="B78" s="161"/>
+      <c r="C78" s="161"/>
+      <c r="D78" s="161"/>
       <c r="E78" s="6" t="s">
         <v>109</v>
       </c>
@@ -17248,9 +17266,9 @@
       </c>
     </row>
     <row r="79" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="156"/>
-      <c r="C79" s="156"/>
-      <c r="D79" s="156"/>
+      <c r="B79" s="161"/>
+      <c r="C79" s="161"/>
+      <c r="D79" s="161"/>
       <c r="E79" s="6" t="s">
         <v>106</v>
       </c>
@@ -17307,14 +17325,14 @@
       </c>
     </row>
     <row r="80" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="157"/>
-      <c r="C80" s="157"/>
-      <c r="D80" s="157"/>
+      <c r="B80" s="162"/>
+      <c r="C80" s="162"/>
+      <c r="D80" s="162"/>
       <c r="E80" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G80" s="38"/>
       <c r="H80" s="63" t="str">
@@ -17369,13 +17387,13 @@
       <c r="A81" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B81" s="158">
+      <c r="B81" s="163">
         <v>15</v>
       </c>
-      <c r="C81" s="158" t="s">
+      <c r="C81" s="163" t="s">
         <v>30</v>
       </c>
-      <c r="D81" s="158" t="s">
+      <c r="D81" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E81" s="26" t="s">
@@ -17395,7 +17413,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K81" s="173" t="s">
+      <c r="K81" s="206" t="s">
         <v>169</v>
       </c>
       <c r="L81" s="41"/>
@@ -17434,9 +17452,9 @@
       </c>
     </row>
     <row r="82" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="159"/>
-      <c r="C82" s="159"/>
-      <c r="D82" s="159"/>
+      <c r="B82" s="164"/>
+      <c r="C82" s="164"/>
+      <c r="D82" s="164"/>
       <c r="E82" s="3" t="s">
         <v>13</v>
       </c>
@@ -17456,7 +17474,7 @@
         <f t="shared" si="15"/>
         <v>66.450720029923318</v>
       </c>
-      <c r="K82" s="159"/>
+      <c r="K82" s="164"/>
       <c r="L82" s="42"/>
       <c r="U82" s="119" t="str" cm="1">
         <f t="array" ref="U82">IF(C82="",INDEX(C78:C82,MATCH(TRUE,INDEX((C78:C82&lt;&gt;""),0),0)),C82)</f>
@@ -17493,9 +17511,9 @@
       </c>
     </row>
     <row r="83" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="159"/>
-      <c r="C83" s="159"/>
-      <c r="D83" s="159"/>
+      <c r="B83" s="164"/>
+      <c r="C83" s="164"/>
+      <c r="D83" s="164"/>
       <c r="E83" s="3" t="s">
         <v>109</v>
       </c>
@@ -17515,7 +17533,7 @@
         <f t="shared" si="15"/>
         <v>96.561202543482324</v>
       </c>
-      <c r="K83" s="159"/>
+      <c r="K83" s="164"/>
       <c r="L83" s="42" t="s">
         <v>174</v>
       </c>
@@ -17554,9 +17572,9 @@
       </c>
     </row>
     <row r="84" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="159"/>
-      <c r="C84" s="159"/>
-      <c r="D84" s="159"/>
+      <c r="B84" s="164"/>
+      <c r="C84" s="164"/>
+      <c r="D84" s="164"/>
       <c r="E84" s="3" t="s">
         <v>106</v>
       </c>
@@ -17576,7 +17594,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K84" s="159"/>
+      <c r="K84" s="164"/>
       <c r="L84" s="42"/>
       <c r="U84" s="119" t="str" cm="1">
         <f t="array" ref="U84">IF(C84="",INDEX(C80:C84,MATCH(TRUE,INDEX((C80:C84&lt;&gt;""),0),0)),C84)</f>
@@ -17613,14 +17631,14 @@
       </c>
     </row>
     <row r="85" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="160"/>
-      <c r="C85" s="160"/>
-      <c r="D85" s="160"/>
+      <c r="B85" s="165"/>
+      <c r="C85" s="165"/>
+      <c r="D85" s="165"/>
       <c r="E85" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F85" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G85" s="35"/>
       <c r="H85" s="57" t="str">
@@ -17635,7 +17653,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K85" s="160"/>
+      <c r="K85" s="165"/>
       <c r="L85" s="43"/>
       <c r="U85" s="119" t="str" cm="1">
         <f t="array" ref="U85">IF(C85="",INDEX(C81:C85,MATCH(TRUE,INDEX((C81:C85&lt;&gt;""),0),0)),C85)</f>
@@ -17675,13 +17693,13 @@
       <c r="A86" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B86" s="155">
+      <c r="B86" s="160">
         <v>16</v>
       </c>
-      <c r="C86" s="155" t="s">
+      <c r="C86" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="D86" s="155" t="s">
+      <c r="D86" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E86" s="27" t="s">
@@ -17701,7 +17719,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K86" s="155" t="s">
+      <c r="K86" s="160" t="s">
         <v>167</v>
       </c>
       <c r="L86" s="44"/>
@@ -17740,9 +17758,9 @@
       </c>
     </row>
     <row r="87" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="156"/>
-      <c r="C87" s="156"/>
-      <c r="D87" s="156"/>
+      <c r="B87" s="161"/>
+      <c r="C87" s="161"/>
+      <c r="D87" s="161"/>
       <c r="E87" s="6" t="s">
         <v>13</v>
       </c>
@@ -17764,7 +17782,7 @@
         <f t="shared" si="15"/>
         <v>66.450720029923318</v>
       </c>
-      <c r="K87" s="156"/>
+      <c r="K87" s="161"/>
       <c r="L87" s="45"/>
       <c r="U87" s="119" t="str" cm="1">
         <f t="array" ref="U87">IF(C87="",INDEX(C83:C87,MATCH(TRUE,INDEX((C83:C87&lt;&gt;""),0),0)),C87)</f>
@@ -17801,9 +17819,9 @@
       </c>
     </row>
     <row r="88" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="156"/>
-      <c r="C88" s="156"/>
-      <c r="D88" s="156"/>
+      <c r="B88" s="161"/>
+      <c r="C88" s="161"/>
+      <c r="D88" s="161"/>
       <c r="E88" s="6" t="s">
         <v>109</v>
       </c>
@@ -17823,7 +17841,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K88" s="156"/>
+      <c r="K88" s="161"/>
       <c r="L88" s="45"/>
       <c r="U88" s="119" t="str" cm="1">
         <f t="array" ref="U88">IF(C88="",INDEX(C84:C88,MATCH(TRUE,INDEX((C84:C88&lt;&gt;""),0),0)),C88)</f>
@@ -17860,9 +17878,9 @@
       </c>
     </row>
     <row r="89" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="156"/>
-      <c r="C89" s="156"/>
-      <c r="D89" s="156"/>
+      <c r="B89" s="161"/>
+      <c r="C89" s="161"/>
+      <c r="D89" s="161"/>
       <c r="E89" s="6" t="s">
         <v>106</v>
       </c>
@@ -17882,7 +17900,7 @@
         <f t="shared" si="15"/>
         <v>88.254862539741907</v>
       </c>
-      <c r="K89" s="156"/>
+      <c r="K89" s="161"/>
       <c r="L89" s="45"/>
       <c r="U89" s="119" t="str" cm="1">
         <f t="array" ref="U89">IF(C89="",INDEX(C85:C89,MATCH(TRUE,INDEX((C85:C89&lt;&gt;""),0),0)),C89)</f>
@@ -17919,9 +17937,9 @@
       </c>
     </row>
     <row r="90" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="157"/>
-      <c r="C90" s="157"/>
-      <c r="D90" s="157"/>
+      <c r="B90" s="162"/>
+      <c r="C90" s="162"/>
+      <c r="D90" s="162"/>
       <c r="E90" s="7" t="s">
         <v>14</v>
       </c>
@@ -17941,7 +17959,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K90" s="157"/>
+      <c r="K90" s="162"/>
       <c r="L90" s="46"/>
       <c r="U90" s="119" t="str" cm="1">
         <f t="array" ref="U90">IF(C90="",INDEX(C86:C90,MATCH(TRUE,INDEX((C86:C90&lt;&gt;""),0),0)),C90)</f>
@@ -17981,13 +17999,13 @@
       <c r="A91" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B91" s="158">
+      <c r="B91" s="163">
         <v>17</v>
       </c>
-      <c r="C91" s="158" t="s">
+      <c r="C91" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="D91" s="158" t="s">
+      <c r="D91" s="163" t="s">
         <v>34</v>
       </c>
       <c r="E91" s="26" t="s">
@@ -18007,7 +18025,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K91" s="158" t="s">
+      <c r="K91" s="163" t="s">
         <v>101</v>
       </c>
       <c r="L91" s="41"/>
@@ -18046,9 +18064,9 @@
       </c>
     </row>
     <row r="92" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="159"/>
-      <c r="C92" s="159"/>
-      <c r="D92" s="159"/>
+      <c r="B92" s="164"/>
+      <c r="C92" s="164"/>
+      <c r="D92" s="164"/>
       <c r="E92" s="3" t="s">
         <v>13</v>
       </c>
@@ -18070,7 +18088,7 @@
         <f t="shared" si="15"/>
         <v>73.144567046942214</v>
       </c>
-      <c r="K92" s="159"/>
+      <c r="K92" s="164"/>
       <c r="L92" s="42"/>
       <c r="U92" s="119" t="str" cm="1">
         <f t="array" ref="U92">IF(C92="",INDEX(C88:C92,MATCH(TRUE,INDEX((C88:C92&lt;&gt;""),0),0)),C92)</f>
@@ -18107,9 +18125,9 @@
       </c>
     </row>
     <row r="93" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="159"/>
-      <c r="C93" s="159"/>
-      <c r="D93" s="159"/>
+      <c r="B93" s="164"/>
+      <c r="C93" s="164"/>
+      <c r="D93" s="164"/>
       <c r="E93" s="3" t="s">
         <v>106</v>
       </c>
@@ -18129,7 +18147,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K93" s="159"/>
+      <c r="K93" s="164"/>
       <c r="L93" s="42"/>
       <c r="U93" s="119" t="str" cm="1">
         <f t="array" ref="U93">IF(C93="",INDEX(C89:C93,MATCH(TRUE,INDEX((C89:C93&lt;&gt;""),0),0)),C93)</f>
@@ -18166,9 +18184,9 @@
       </c>
     </row>
     <row r="94" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B94" s="159"/>
-      <c r="C94" s="159"/>
-      <c r="D94" s="159"/>
+      <c r="B94" s="164"/>
+      <c r="C94" s="164"/>
+      <c r="D94" s="164"/>
       <c r="E94" s="3" t="s">
         <v>109</v>
       </c>
@@ -18188,7 +18206,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K94" s="159"/>
+      <c r="K94" s="164"/>
       <c r="L94" s="42"/>
       <c r="U94" s="119" t="str" cm="1">
         <f t="array" ref="U94">IF(C94="",INDEX(C90:C94,MATCH(TRUE,INDEX((C90:C94&lt;&gt;""),0),0)),C94)</f>
@@ -18225,9 +18243,9 @@
       </c>
     </row>
     <row r="95" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="159"/>
-      <c r="C95" s="159"/>
-      <c r="D95" s="159"/>
+      <c r="B95" s="164"/>
+      <c r="C95" s="164"/>
+      <c r="D95" s="164"/>
       <c r="E95" s="3" t="s">
         <v>110</v>
       </c>
@@ -18247,7 +18265,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K95" s="159"/>
+      <c r="K95" s="164"/>
       <c r="L95" s="42"/>
       <c r="U95" s="119" t="str" cm="1">
         <f t="array" ref="U95">IF(C95="",INDEX(C90:C95,MATCH(TRUE,INDEX((C90:C95&lt;&gt;""),0),0)),C95)</f>
@@ -18267,7 +18285,7 @@
       </c>
       <c r="Z95" s="121"/>
       <c r="AB95" s="8" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="AC95" s="8">
         <v>5000</v>
@@ -18284,9 +18302,9 @@
       </c>
     </row>
     <row r="96" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B96" s="160"/>
-      <c r="C96" s="160"/>
-      <c r="D96" s="160"/>
+      <c r="B96" s="165"/>
+      <c r="C96" s="165"/>
+      <c r="D96" s="165"/>
       <c r="E96" s="4" t="s">
         <v>14</v>
       </c>
@@ -18308,7 +18326,7 @@
         <f t="shared" si="15"/>
         <v>9.1430708808677768</v>
       </c>
-      <c r="K96" s="160"/>
+      <c r="K96" s="165"/>
       <c r="L96" s="43"/>
       <c r="U96" s="119" t="str" cm="1">
         <f t="array" ref="U96">IF(C96="",INDEX(C91:C96,MATCH(TRUE,INDEX((C91:C96&lt;&gt;""),0),0)),C96)</f>
@@ -18328,7 +18346,7 @@
       </c>
       <c r="Z96" s="121"/>
       <c r="AB96" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AC96" s="8">
         <v>8000</v>
@@ -18348,13 +18366,13 @@
       <c r="A97" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B97" s="155">
+      <c r="B97" s="160">
         <v>18</v>
       </c>
-      <c r="C97" s="155" t="s">
+      <c r="C97" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="D97" s="155" t="s">
+      <c r="D97" s="160" t="s">
         <v>34</v>
       </c>
       <c r="E97" s="27" t="s">
@@ -18411,9 +18429,9 @@
       </c>
     </row>
     <row r="98" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="156"/>
-      <c r="C98" s="156"/>
-      <c r="D98" s="156"/>
+      <c r="B98" s="161"/>
+      <c r="C98" s="161"/>
+      <c r="D98" s="161"/>
       <c r="E98" s="6" t="s">
         <v>13</v>
       </c>
@@ -18472,9 +18490,9 @@
       </c>
     </row>
     <row r="99" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="156"/>
-      <c r="C99" s="156"/>
-      <c r="D99" s="156"/>
+      <c r="B99" s="161"/>
+      <c r="C99" s="161"/>
+      <c r="D99" s="161"/>
       <c r="E99" s="6" t="s">
         <v>103</v>
       </c>
@@ -18514,7 +18532,7 @@
       </c>
       <c r="Z99" s="121"/>
       <c r="AB99" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AC99" s="8">
         <v>7000</v>
@@ -18531,9 +18549,9 @@
       </c>
     </row>
     <row r="100" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B100" s="156"/>
-      <c r="C100" s="156"/>
-      <c r="D100" s="156"/>
+      <c r="B100" s="161"/>
+      <c r="C100" s="161"/>
+      <c r="D100" s="161"/>
       <c r="E100" s="6" t="s">
         <v>106</v>
       </c>
@@ -18575,7 +18593,7 @@
       </c>
       <c r="Z100" s="121"/>
       <c r="AB100" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AC100" s="8">
         <v>7000</v>
@@ -18592,9 +18610,9 @@
       </c>
     </row>
     <row r="101" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="156"/>
-      <c r="C101" s="156"/>
-      <c r="D101" s="156"/>
+      <c r="B101" s="161"/>
+      <c r="C101" s="161"/>
+      <c r="D101" s="161"/>
       <c r="E101" s="6" t="s">
         <v>109</v>
       </c>
@@ -18636,13 +18654,13 @@
       </c>
       <c r="Z101" s="121"/>
       <c r="AB101" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AC101" s="8">
         <v>7001</v>
       </c>
       <c r="AD101" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AE101" s="8" t="s">
         <v>235</v>
@@ -18653,9 +18671,9 @@
       </c>
     </row>
     <row r="102" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="156"/>
-      <c r="C102" s="156"/>
-      <c r="D102" s="156"/>
+      <c r="B102" s="161"/>
+      <c r="C102" s="161"/>
+      <c r="D102" s="161"/>
       <c r="E102" s="6" t="s">
         <v>110</v>
       </c>
@@ -18696,9 +18714,9 @@
       <c r="Z102" s="121"/>
     </row>
     <row r="103" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="157"/>
-      <c r="C103" s="157"/>
-      <c r="D103" s="157"/>
+      <c r="B103" s="162"/>
+      <c r="C103" s="162"/>
+      <c r="D103" s="162"/>
       <c r="E103" s="7" t="s">
         <v>14</v>
       </c>
@@ -18744,13 +18762,13 @@
       <c r="A104" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B104" s="158">
+      <c r="B104" s="163">
         <v>19</v>
       </c>
-      <c r="C104" s="158" t="s">
+      <c r="C104" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="D104" s="158" t="s">
+      <c r="D104" s="163" t="s">
         <v>34</v>
       </c>
       <c r="E104" s="26" t="s">
@@ -18770,7 +18788,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K104" s="158" t="s">
+      <c r="K104" s="163" t="s">
         <v>139</v>
       </c>
       <c r="L104" s="41"/>
@@ -18793,9 +18811,9 @@
       <c r="Z104" s="121"/>
     </row>
     <row r="105" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B105" s="159"/>
-      <c r="C105" s="159"/>
-      <c r="D105" s="159"/>
+      <c r="B105" s="164"/>
+      <c r="C105" s="164"/>
+      <c r="D105" s="164"/>
       <c r="E105" s="3" t="s">
         <v>13</v>
       </c>
@@ -18815,7 +18833,7 @@
         <f t="shared" si="15"/>
         <v>73.144567046942214</v>
       </c>
-      <c r="K105" s="159"/>
+      <c r="K105" s="164"/>
       <c r="L105" s="42"/>
       <c r="U105" s="119" t="str" cm="1">
         <f t="array" ref="U105">IF(C105="",INDEX(C101:C105,MATCH(TRUE,INDEX((C101:C105&lt;&gt;""),0),0)),C105)</f>
@@ -18836,9 +18854,9 @@
       <c r="Z105" s="121"/>
     </row>
     <row r="106" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B106" s="159"/>
-      <c r="C106" s="159"/>
-      <c r="D106" s="159"/>
+      <c r="B106" s="164"/>
+      <c r="C106" s="164"/>
+      <c r="D106" s="164"/>
       <c r="E106" s="3" t="s">
         <v>106</v>
       </c>
@@ -18858,7 +18876,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K106" s="159"/>
+      <c r="K106" s="164"/>
       <c r="L106" s="42"/>
       <c r="U106" s="119" t="str" cm="1">
         <f t="array" ref="U106">IF(C106="",INDEX(C102:C106,MATCH(TRUE,INDEX((C102:C106&lt;&gt;""),0),0)),C106)</f>
@@ -18879,9 +18897,9 @@
       <c r="Z106" s="121"/>
     </row>
     <row r="107" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B107" s="159"/>
-      <c r="C107" s="159"/>
-      <c r="D107" s="159"/>
+      <c r="B107" s="164"/>
+      <c r="C107" s="164"/>
+      <c r="D107" s="164"/>
       <c r="E107" s="3" t="s">
         <v>109</v>
       </c>
@@ -18901,7 +18919,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K107" s="159"/>
+      <c r="K107" s="164"/>
       <c r="L107" s="42"/>
       <c r="U107" s="119" t="str" cm="1">
         <f t="array" ref="U107">IF(C107="",INDEX(C103:C107,MATCH(TRUE,INDEX((C103:C107&lt;&gt;""),0),0)),C107)</f>
@@ -18922,9 +18940,9 @@
       <c r="Z107" s="121"/>
     </row>
     <row r="108" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="159"/>
-      <c r="C108" s="159"/>
-      <c r="D108" s="159"/>
+      <c r="B108" s="164"/>
+      <c r="C108" s="164"/>
+      <c r="D108" s="164"/>
       <c r="E108" s="3" t="s">
         <v>110</v>
       </c>
@@ -18944,7 +18962,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K108" s="159"/>
+      <c r="K108" s="164"/>
       <c r="L108" s="42"/>
       <c r="U108" s="119" t="str" cm="1">
         <f t="array" ref="U108">IF(C108="",INDEX(C102:C108,MATCH(TRUE,INDEX((C102:C108&lt;&gt;""),0),0)),C108)</f>
@@ -18965,9 +18983,9 @@
       <c r="Z108" s="121"/>
     </row>
     <row r="109" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B109" s="160"/>
-      <c r="C109" s="160"/>
-      <c r="D109" s="160"/>
+      <c r="B109" s="165"/>
+      <c r="C109" s="165"/>
+      <c r="D109" s="165"/>
       <c r="E109" s="4" t="s">
         <v>14</v>
       </c>
@@ -18987,7 +19005,7 @@
         <f t="shared" si="15"/>
         <v>9.1430708808677768</v>
       </c>
-      <c r="K109" s="160"/>
+      <c r="K109" s="165"/>
       <c r="L109" s="43"/>
       <c r="U109" s="119" t="str" cm="1">
         <f t="array" ref="U109">IF(C109="",INDEX(C103:C109,MATCH(TRUE,INDEX((C103:C109&lt;&gt;""),0),0)),C109)</f>
@@ -19011,13 +19029,13 @@
       <c r="A110" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B110" s="155">
+      <c r="B110" s="160">
         <v>20</v>
       </c>
-      <c r="C110" s="155" t="s">
+      <c r="C110" s="160" t="s">
         <v>37</v>
       </c>
-      <c r="D110" s="155" t="s">
+      <c r="D110" s="160" t="s">
         <v>38</v>
       </c>
       <c r="E110" s="27" t="s">
@@ -19037,7 +19055,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K110" s="155"/>
+      <c r="K110" s="160"/>
       <c r="L110" s="44"/>
       <c r="U110" s="119" t="str" cm="1">
         <f t="array" ref="U110">IF(C110="",INDEX(C104:C110,MATCH(TRUE,INDEX((C104:C110&lt;&gt;""),0),0)),C110)</f>
@@ -19060,9 +19078,9 @@
       <c r="Z110" s="121"/>
     </row>
     <row r="111" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B111" s="156"/>
-      <c r="C111" s="156"/>
-      <c r="D111" s="156"/>
+      <c r="B111" s="161"/>
+      <c r="C111" s="161"/>
+      <c r="D111" s="161"/>
       <c r="E111" s="6" t="s">
         <v>13</v>
       </c>
@@ -19082,7 +19100,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K111" s="156"/>
+      <c r="K111" s="161"/>
       <c r="L111" s="45"/>
       <c r="U111" s="119" t="str" cm="1">
         <f t="array" ref="U111">IF(C111="",INDEX(C105:C111,MATCH(TRUE,INDEX((C105:C111&lt;&gt;""),0),0)),C111)</f>
@@ -19103,9 +19121,9 @@
       <c r="Z111" s="121"/>
     </row>
     <row r="112" spans="1:34" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B112" s="156"/>
-      <c r="C112" s="156"/>
-      <c r="D112" s="156"/>
+      <c r="B112" s="161"/>
+      <c r="C112" s="161"/>
+      <c r="D112" s="161"/>
       <c r="E112" s="6" t="s">
         <v>103</v>
       </c>
@@ -19127,7 +19145,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K112" s="156"/>
+      <c r="K112" s="161"/>
       <c r="L112" s="45" t="s">
         <v>125</v>
       </c>
@@ -19159,9 +19177,9 @@
       </c>
     </row>
     <row r="113" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B113" s="156"/>
-      <c r="C113" s="156"/>
-      <c r="D113" s="156"/>
+      <c r="B113" s="161"/>
+      <c r="C113" s="161"/>
+      <c r="D113" s="161"/>
       <c r="E113" s="6" t="s">
         <v>109</v>
       </c>
@@ -19181,7 +19199,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K113" s="156"/>
+      <c r="K113" s="161"/>
       <c r="L113" s="45"/>
       <c r="U113" s="119" t="str" cm="1">
         <f t="array" ref="U113">IF(C113="",INDEX(C107:C113,MATCH(TRUE,INDEX((C107:C113&lt;&gt;""),0),0)),C113)</f>
@@ -19212,9 +19230,9 @@
       </c>
     </row>
     <row r="114" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="156"/>
-      <c r="C114" s="156"/>
-      <c r="D114" s="156"/>
+      <c r="B114" s="161"/>
+      <c r="C114" s="161"/>
+      <c r="D114" s="161"/>
       <c r="E114" s="6" t="s">
         <v>110</v>
       </c>
@@ -19234,7 +19252,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K114" s="156"/>
+      <c r="K114" s="161"/>
       <c r="L114" s="45"/>
       <c r="U114" s="119" t="str" cm="1">
         <f t="array" ref="U114">IF(C114="",INDEX(C108:C114,MATCH(TRUE,INDEX((C108:C114&lt;&gt;""),0),0)),C114)</f>
@@ -19264,9 +19282,9 @@
       </c>
     </row>
     <row r="115" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="156"/>
-      <c r="C115" s="156"/>
-      <c r="D115" s="156"/>
+      <c r="B115" s="161"/>
+      <c r="C115" s="161"/>
+      <c r="D115" s="161"/>
       <c r="E115" s="6" t="s">
         <v>106</v>
       </c>
@@ -19286,7 +19304,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K115" s="156"/>
+      <c r="K115" s="161"/>
       <c r="L115" s="45"/>
       <c r="U115" s="119" t="str" cm="1">
         <f t="array" ref="U115">IF(C115="",INDEX(C109:C115,MATCH(TRUE,INDEX((C109:C115&lt;&gt;""),0),0)),C115)</f>
@@ -19319,9 +19337,9 @@
       </c>
     </row>
     <row r="116" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B116" s="157"/>
-      <c r="C116" s="157"/>
-      <c r="D116" s="157"/>
+      <c r="B116" s="162"/>
+      <c r="C116" s="162"/>
+      <c r="D116" s="162"/>
       <c r="E116" s="7" t="s">
         <v>14</v>
       </c>
@@ -19341,7 +19359,7 @@
         <f t="shared" si="15"/>
         <v>10.4</v>
       </c>
-      <c r="K116" s="157"/>
+      <c r="K116" s="162"/>
       <c r="L116" s="46"/>
       <c r="U116" s="119" t="str" cm="1">
         <f t="array" ref="U116">IF(C116="",INDEX(C110:C116,MATCH(TRUE,INDEX((C110:C116&lt;&gt;""),0),0)),C116)</f>
@@ -19365,13 +19383,13 @@
       <c r="A117" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B117" s="158">
+      <c r="B117" s="163">
         <v>21</v>
       </c>
-      <c r="C117" s="158" t="s">
+      <c r="C117" s="163" t="s">
         <v>39</v>
       </c>
-      <c r="D117" s="158" t="s">
+      <c r="D117" s="163" t="s">
         <v>38</v>
       </c>
       <c r="E117" s="26" t="s">
@@ -19391,7 +19409,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K117" s="158" t="s">
+      <c r="K117" s="163" t="s">
         <v>144</v>
       </c>
       <c r="L117" s="41"/>
@@ -19415,7 +19433,7 @@
       </c>
       <c r="Z117" s="121"/>
       <c r="AC117" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AD117" s="8">
         <f>AD121*625</f>
@@ -19423,9 +19441,9 @@
       </c>
     </row>
     <row r="118" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B118" s="159"/>
-      <c r="C118" s="159"/>
-      <c r="D118" s="159"/>
+      <c r="B118" s="164"/>
+      <c r="C118" s="164"/>
+      <c r="D118" s="164"/>
       <c r="E118" s="3" t="s">
         <v>13</v>
       </c>
@@ -19445,7 +19463,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K118" s="159"/>
+      <c r="K118" s="164"/>
       <c r="L118" s="42"/>
       <c r="U118" s="119" t="str" cm="1">
         <f t="array" ref="U118">IF(C118="",INDEX(C112:C118,MATCH(TRUE,INDEX((C112:C118&lt;&gt;""),0),0)),C118)</f>
@@ -19465,7 +19483,7 @@
       </c>
       <c r="Z118" s="121"/>
       <c r="AC118" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AD118" s="8">
         <f>250000*A473</f>
@@ -19473,9 +19491,9 @@
       </c>
     </row>
     <row r="119" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="159"/>
-      <c r="C119" s="159"/>
-      <c r="D119" s="159"/>
+      <c r="B119" s="164"/>
+      <c r="C119" s="164"/>
+      <c r="D119" s="164"/>
       <c r="E119" s="3" t="s">
         <v>109</v>
       </c>
@@ -19495,7 +19513,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K119" s="159"/>
+      <c r="K119" s="164"/>
       <c r="L119" s="42"/>
       <c r="U119" s="119" t="str" cm="1">
         <f t="array" ref="U119">IF(C119="",INDEX(C113:C119,MATCH(TRUE,INDEX((C113:C119&lt;&gt;""),0),0)),C119)</f>
@@ -19515,7 +19533,7 @@
       </c>
       <c r="Z119" s="121"/>
       <c r="AC119" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AE119" s="8">
         <f>AD118+AD117</f>
@@ -19523,9 +19541,9 @@
       </c>
     </row>
     <row r="120" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="159"/>
-      <c r="C120" s="159"/>
-      <c r="D120" s="159"/>
+      <c r="B120" s="164"/>
+      <c r="C120" s="164"/>
+      <c r="D120" s="164"/>
       <c r="E120" s="3" t="s">
         <v>110</v>
       </c>
@@ -19545,7 +19563,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="K120" s="159"/>
+      <c r="K120" s="164"/>
       <c r="L120" s="42" t="s">
         <v>145</v>
       </c>
@@ -19568,9 +19586,9 @@
       <c r="Z120" s="121"/>
     </row>
     <row r="121" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="159"/>
-      <c r="C121" s="159"/>
-      <c r="D121" s="159"/>
+      <c r="B121" s="164"/>
+      <c r="C121" s="164"/>
+      <c r="D121" s="164"/>
       <c r="E121" s="3" t="s">
         <v>106</v>
       </c>
@@ -19590,7 +19608,7 @@
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K121" s="159"/>
+      <c r="K121" s="164"/>
       <c r="L121" s="42"/>
       <c r="U121" s="119" t="str" cm="1">
         <f t="array" ref="U121">IF(C121="",INDEX(C115:C121,MATCH(TRUE,INDEX((C115:C121&lt;&gt;""),0),0)),C121)</f>
@@ -19610,19 +19628,19 @@
       </c>
       <c r="Z121" s="121"/>
       <c r="AC121" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AD121" s="8">
         <v>22926</v>
       </c>
       <c r="AE121" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="122" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B122" s="160"/>
-      <c r="C122" s="160"/>
-      <c r="D122" s="160"/>
+      <c r="B122" s="165"/>
+      <c r="C122" s="165"/>
+      <c r="D122" s="165"/>
       <c r="E122" s="4" t="s">
         <v>14</v>
       </c>
@@ -19642,7 +19660,7 @@
         <f t="shared" si="15"/>
         <v>10.4</v>
       </c>
-      <c r="K122" s="160"/>
+      <c r="K122" s="165"/>
       <c r="L122" s="43"/>
       <c r="U122" s="119" t="str" cm="1">
         <f t="array" ref="U122">IF(C122="",INDEX(C116:C122,MATCH(TRUE,INDEX((C116:C122&lt;&gt;""),0),0)),C122)</f>
@@ -19666,13 +19684,13 @@
       <c r="A123" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B123" s="155">
+      <c r="B123" s="160">
         <v>22</v>
       </c>
-      <c r="C123" s="155" t="s">
+      <c r="C123" s="160" t="s">
         <v>40</v>
       </c>
-      <c r="D123" s="155" t="s">
+      <c r="D123" s="160" t="s">
         <v>41</v>
       </c>
       <c r="E123" s="27" t="s">
@@ -19712,17 +19730,17 @@
       </c>
       <c r="Z123" s="121"/>
       <c r="AC123" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AD123" s="154">
         <f>SUM(Tracker!H9:H491)/AD117</f>
-        <v>7.3261073197654084E-2</v>
+        <v>7.3772553683058351E-2</v>
       </c>
     </row>
     <row r="124" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="156"/>
-      <c r="C124" s="156"/>
-      <c r="D124" s="156"/>
+      <c r="B124" s="161"/>
+      <c r="C124" s="161"/>
+      <c r="D124" s="161"/>
       <c r="E124" s="6" t="s">
         <v>13</v>
       </c>
@@ -19763,9 +19781,9 @@
       <c r="Z124" s="121"/>
     </row>
     <row r="125" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="156"/>
-      <c r="C125" s="156"/>
-      <c r="D125" s="156"/>
+      <c r="B125" s="161"/>
+      <c r="C125" s="161"/>
+      <c r="D125" s="161"/>
       <c r="E125" s="6" t="s">
         <v>103</v>
       </c>
@@ -19806,9 +19824,9 @@
       <c r="Z125" s="121"/>
     </row>
     <row r="126" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B126" s="156"/>
-      <c r="C126" s="156"/>
-      <c r="D126" s="156"/>
+      <c r="B126" s="161"/>
+      <c r="C126" s="161"/>
+      <c r="D126" s="161"/>
       <c r="E126" s="6" t="s">
         <v>106</v>
       </c>
@@ -19849,9 +19867,9 @@
       <c r="Z126" s="121"/>
     </row>
     <row r="127" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B127" s="156"/>
-      <c r="C127" s="156"/>
-      <c r="D127" s="156"/>
+      <c r="B127" s="161"/>
+      <c r="C127" s="161"/>
+      <c r="D127" s="161"/>
       <c r="E127" s="6" t="s">
         <v>109</v>
       </c>
@@ -19892,9 +19910,9 @@
       <c r="Z127" s="121"/>
     </row>
     <row r="128" spans="1:31" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B128" s="156"/>
-      <c r="C128" s="156"/>
-      <c r="D128" s="156"/>
+      <c r="B128" s="161"/>
+      <c r="C128" s="161"/>
+      <c r="D128" s="161"/>
       <c r="E128" s="6" t="s">
         <v>290</v>
       </c>
@@ -19935,9 +19953,9 @@
       <c r="Z128" s="121"/>
     </row>
     <row r="129" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B129" s="156"/>
-      <c r="C129" s="156"/>
-      <c r="D129" s="156"/>
+      <c r="B129" s="161"/>
+      <c r="C129" s="161"/>
+      <c r="D129" s="161"/>
       <c r="E129" s="6" t="s">
         <v>110</v>
       </c>
@@ -19978,9 +19996,9 @@
       <c r="Z129" s="121"/>
     </row>
     <row r="130" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B130" s="157"/>
-      <c r="C130" s="157"/>
-      <c r="D130" s="157"/>
+      <c r="B130" s="162"/>
+      <c r="C130" s="162"/>
+      <c r="D130" s="162"/>
       <c r="E130" s="7" t="s">
         <v>14</v>
       </c>
@@ -20026,13 +20044,13 @@
       <c r="A131" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B131" s="158">
+      <c r="B131" s="163">
         <v>23</v>
       </c>
-      <c r="C131" s="158" t="s">
+      <c r="C131" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="D131" s="158" t="s">
+      <c r="D131" s="163" t="s">
         <v>41</v>
       </c>
       <c r="E131" s="26" t="s">
@@ -20075,9 +20093,9 @@
       <c r="Z131" s="121"/>
     </row>
     <row r="132" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B132" s="159"/>
-      <c r="C132" s="159"/>
-      <c r="D132" s="159"/>
+      <c r="B132" s="164"/>
+      <c r="C132" s="164"/>
+      <c r="D132" s="164"/>
       <c r="E132" s="3" t="s">
         <v>13</v>
       </c>
@@ -20118,9 +20136,9 @@
       <c r="Z132" s="121"/>
     </row>
     <row r="133" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B133" s="159"/>
-      <c r="C133" s="159"/>
-      <c r="D133" s="159"/>
+      <c r="B133" s="164"/>
+      <c r="C133" s="164"/>
+      <c r="D133" s="164"/>
       <c r="E133" s="3" t="s">
         <v>109</v>
       </c>
@@ -20161,9 +20179,9 @@
       <c r="Z133" s="121"/>
     </row>
     <row r="134" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B134" s="159"/>
-      <c r="C134" s="159"/>
-      <c r="D134" s="159"/>
+      <c r="B134" s="164"/>
+      <c r="C134" s="164"/>
+      <c r="D134" s="164"/>
       <c r="E134" s="3" t="s">
         <v>110</v>
       </c>
@@ -20204,9 +20222,9 @@
       <c r="Z134" s="121"/>
     </row>
     <row r="135" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B135" s="159"/>
-      <c r="C135" s="159"/>
-      <c r="D135" s="159"/>
+      <c r="B135" s="164"/>
+      <c r="C135" s="164"/>
+      <c r="D135" s="164"/>
       <c r="E135" s="3" t="s">
         <v>106</v>
       </c>
@@ -20247,9 +20265,9 @@
       <c r="Z135" s="121"/>
     </row>
     <row r="136" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B136" s="160"/>
-      <c r="C136" s="160"/>
-      <c r="D136" s="160"/>
+      <c r="B136" s="165"/>
+      <c r="C136" s="165"/>
+      <c r="D136" s="165"/>
       <c r="E136" s="4" t="s">
         <v>14</v>
       </c>
@@ -20295,13 +20313,13 @@
       <c r="A137" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B137" s="155">
+      <c r="B137" s="160">
         <v>24</v>
       </c>
-      <c r="C137" s="155" t="s">
+      <c r="C137" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="D137" s="155" t="s">
+      <c r="D137" s="160" t="s">
         <v>41</v>
       </c>
       <c r="E137" s="27" t="s">
@@ -20342,9 +20360,9 @@
       <c r="Z137" s="121"/>
     </row>
     <row r="138" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B138" s="156"/>
-      <c r="C138" s="156"/>
-      <c r="D138" s="156"/>
+      <c r="B138" s="161"/>
+      <c r="C138" s="161"/>
+      <c r="D138" s="161"/>
       <c r="E138" s="6" t="s">
         <v>13</v>
       </c>
@@ -20385,9 +20403,9 @@
       <c r="Z138" s="121"/>
     </row>
     <row r="139" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B139" s="156"/>
-      <c r="C139" s="156"/>
-      <c r="D139" s="156"/>
+      <c r="B139" s="161"/>
+      <c r="C139" s="161"/>
+      <c r="D139" s="161"/>
       <c r="E139" s="6" t="s">
         <v>103</v>
       </c>
@@ -20428,9 +20446,9 @@
       <c r="Z139" s="121"/>
     </row>
     <row r="140" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="156"/>
-      <c r="C140" s="156"/>
-      <c r="D140" s="156"/>
+      <c r="B140" s="161"/>
+      <c r="C140" s="161"/>
+      <c r="D140" s="161"/>
       <c r="E140" s="6" t="s">
         <v>106</v>
       </c>
@@ -20471,9 +20489,9 @@
       <c r="Z140" s="121"/>
     </row>
     <row r="141" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B141" s="156"/>
-      <c r="C141" s="156"/>
-      <c r="D141" s="156"/>
+      <c r="B141" s="161"/>
+      <c r="C141" s="161"/>
+      <c r="D141" s="161"/>
       <c r="E141" s="6" t="s">
         <v>109</v>
       </c>
@@ -20514,9 +20532,9 @@
       <c r="Z141" s="121"/>
     </row>
     <row r="142" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B142" s="156"/>
-      <c r="C142" s="156"/>
-      <c r="D142" s="156"/>
+      <c r="B142" s="161"/>
+      <c r="C142" s="161"/>
+      <c r="D142" s="161"/>
       <c r="E142" s="6" t="s">
         <v>280</v>
       </c>
@@ -20562,9 +20580,9 @@
       <c r="Z142" s="121"/>
     </row>
     <row r="143" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="156"/>
-      <c r="C143" s="156"/>
-      <c r="D143" s="156"/>
+      <c r="B143" s="161"/>
+      <c r="C143" s="161"/>
+      <c r="D143" s="161"/>
       <c r="E143" s="6" t="s">
         <v>110</v>
       </c>
@@ -20605,9 +20623,9 @@
       <c r="Z143" s="121"/>
     </row>
     <row r="144" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B144" s="156"/>
-      <c r="C144" s="156"/>
-      <c r="D144" s="156"/>
+      <c r="B144" s="161"/>
+      <c r="C144" s="161"/>
+      <c r="D144" s="161"/>
       <c r="E144" s="6" t="s">
         <v>290</v>
       </c>
@@ -20648,9 +20666,9 @@
       <c r="Z144" s="121"/>
     </row>
     <row r="145" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B145" s="156"/>
-      <c r="C145" s="156"/>
-      <c r="D145" s="156"/>
+      <c r="B145" s="161"/>
+      <c r="C145" s="161"/>
+      <c r="D145" s="161"/>
       <c r="E145" s="6" t="s">
         <v>185</v>
       </c>
@@ -20696,9 +20714,9 @@
       <c r="Z145" s="121"/>
     </row>
     <row r="146" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="157"/>
-      <c r="C146" s="157"/>
-      <c r="D146" s="157"/>
+      <c r="B146" s="162"/>
+      <c r="C146" s="162"/>
+      <c r="D146" s="162"/>
       <c r="E146" s="7" t="s">
         <v>14</v>
       </c>
@@ -20742,13 +20760,13 @@
       <c r="A147" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B147" s="158">
+      <c r="B147" s="163">
         <v>25</v>
       </c>
-      <c r="C147" s="158" t="s">
+      <c r="C147" s="163" t="s">
         <v>44</v>
       </c>
-      <c r="D147" s="158" t="s">
+      <c r="D147" s="163" t="s">
         <v>45</v>
       </c>
       <c r="E147" s="26" t="s">
@@ -20789,9 +20807,9 @@
       <c r="Z147" s="121"/>
     </row>
     <row r="148" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B148" s="159"/>
-      <c r="C148" s="159"/>
-      <c r="D148" s="159"/>
+      <c r="B148" s="164"/>
+      <c r="C148" s="164"/>
+      <c r="D148" s="164"/>
       <c r="E148" s="3" t="s">
         <v>13</v>
       </c>
@@ -20832,9 +20850,9 @@
       <c r="Z148" s="121"/>
     </row>
     <row r="149" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="159"/>
-      <c r="C149" s="159"/>
-      <c r="D149" s="159"/>
+      <c r="B149" s="164"/>
+      <c r="C149" s="164"/>
+      <c r="D149" s="164"/>
       <c r="E149" s="3" t="s">
         <v>110</v>
       </c>
@@ -20875,9 +20893,9 @@
       <c r="Z149" s="121"/>
     </row>
     <row r="150" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B150" s="159"/>
-      <c r="C150" s="159"/>
-      <c r="D150" s="159"/>
+      <c r="B150" s="164"/>
+      <c r="C150" s="164"/>
+      <c r="D150" s="164"/>
       <c r="E150" s="3" t="s">
         <v>109</v>
       </c>
@@ -20922,9 +20940,9 @@
       <c r="Z150" s="121"/>
     </row>
     <row r="151" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B151" s="159"/>
-      <c r="C151" s="159"/>
-      <c r="D151" s="159"/>
+      <c r="B151" s="164"/>
+      <c r="C151" s="164"/>
+      <c r="D151" s="164"/>
       <c r="E151" s="3" t="s">
         <v>106</v>
       </c>
@@ -20965,9 +20983,9 @@
       <c r="Z151" s="121"/>
     </row>
     <row r="152" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="160"/>
-      <c r="C152" s="160"/>
-      <c r="D152" s="160"/>
+      <c r="B152" s="165"/>
+      <c r="C152" s="165"/>
+      <c r="D152" s="165"/>
       <c r="E152" s="4" t="s">
         <v>14</v>
       </c>
@@ -21011,13 +21029,13 @@
       <c r="A153" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B153" s="155">
+      <c r="B153" s="160">
         <v>26</v>
       </c>
-      <c r="C153" s="155" t="s">
+      <c r="C153" s="160" t="s">
         <v>46</v>
       </c>
-      <c r="D153" s="175" t="s">
+      <c r="D153" s="193" t="s">
         <v>99</v>
       </c>
       <c r="E153" s="27" t="s">
@@ -21058,9 +21076,9 @@
       <c r="Z153" s="121"/>
     </row>
     <row r="154" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B154" s="156"/>
-      <c r="C154" s="156"/>
-      <c r="D154" s="176"/>
+      <c r="B154" s="161"/>
+      <c r="C154" s="161"/>
+      <c r="D154" s="194"/>
       <c r="E154" s="6" t="s">
         <v>13</v>
       </c>
@@ -21101,9 +21119,9 @@
       <c r="Z154" s="121"/>
     </row>
     <row r="155" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B155" s="156"/>
-      <c r="C155" s="156"/>
-      <c r="D155" s="156"/>
+      <c r="B155" s="161"/>
+      <c r="C155" s="161"/>
+      <c r="D155" s="161"/>
       <c r="E155" s="6" t="s">
         <v>110</v>
       </c>
@@ -21144,9 +21162,9 @@
       <c r="Z155" s="121"/>
     </row>
     <row r="156" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="156"/>
-      <c r="C156" s="156"/>
-      <c r="D156" s="156"/>
+      <c r="B156" s="161"/>
+      <c r="C156" s="161"/>
+      <c r="D156" s="161"/>
       <c r="E156" s="6" t="s">
         <v>109</v>
       </c>
@@ -21192,9 +21210,9 @@
       <c r="Z156" s="121"/>
     </row>
     <row r="157" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="156"/>
-      <c r="C157" s="156"/>
-      <c r="D157" s="156"/>
+      <c r="B157" s="161"/>
+      <c r="C157" s="161"/>
+      <c r="D157" s="161"/>
       <c r="E157" s="6" t="s">
         <v>106</v>
       </c>
@@ -21237,14 +21255,14 @@
       <c r="Z157" s="121"/>
     </row>
     <row r="158" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B158" s="157"/>
-      <c r="C158" s="157"/>
-      <c r="D158" s="157"/>
+      <c r="B158" s="162"/>
+      <c r="C158" s="162"/>
+      <c r="D158" s="162"/>
       <c r="E158" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F158" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G158" s="37"/>
       <c r="H158" s="61" t="str">
@@ -21283,13 +21301,13 @@
       <c r="A159" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B159" s="158">
+      <c r="B159" s="163">
         <v>27</v>
       </c>
-      <c r="C159" s="158" t="s">
+      <c r="C159" s="163" t="s">
         <v>47</v>
       </c>
-      <c r="D159" s="177" t="s">
+      <c r="D159" s="195" t="s">
         <v>99</v>
       </c>
       <c r="E159" s="26" t="s">
@@ -21330,9 +21348,9 @@
       <c r="Z159" s="121"/>
     </row>
     <row r="160" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B160" s="159"/>
-      <c r="C160" s="159"/>
-      <c r="D160" s="178"/>
+      <c r="B160" s="164"/>
+      <c r="C160" s="164"/>
+      <c r="D160" s="196"/>
       <c r="E160" s="3" t="s">
         <v>13</v>
       </c>
@@ -21373,9 +21391,9 @@
       <c r="Z160" s="121"/>
     </row>
     <row r="161" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B161" s="159"/>
-      <c r="C161" s="159"/>
-      <c r="D161" s="178"/>
+      <c r="B161" s="164"/>
+      <c r="C161" s="164"/>
+      <c r="D161" s="196"/>
       <c r="E161" s="3" t="s">
         <v>110</v>
       </c>
@@ -21416,9 +21434,9 @@
       <c r="Z161" s="121"/>
     </row>
     <row r="162" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B162" s="159"/>
-      <c r="C162" s="159"/>
-      <c r="D162" s="178"/>
+      <c r="B162" s="164"/>
+      <c r="C162" s="164"/>
+      <c r="D162" s="196"/>
       <c r="E162" s="3" t="s">
         <v>109</v>
       </c>
@@ -21466,9 +21484,9 @@
       <c r="Z162" s="121"/>
     </row>
     <row r="163" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B163" s="159"/>
-      <c r="C163" s="159"/>
-      <c r="D163" s="159"/>
+      <c r="B163" s="164"/>
+      <c r="C163" s="164"/>
+      <c r="D163" s="164"/>
       <c r="E163" s="3" t="s">
         <v>106</v>
       </c>
@@ -21511,14 +21529,14 @@
       <c r="Z163" s="121"/>
     </row>
     <row r="164" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B164" s="160"/>
-      <c r="C164" s="160"/>
-      <c r="D164" s="160"/>
+      <c r="B164" s="165"/>
+      <c r="C164" s="165"/>
+      <c r="D164" s="165"/>
       <c r="E164" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F164" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G164" s="39"/>
       <c r="H164" s="65" t="str">
@@ -21557,13 +21575,13 @@
       <c r="A165" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B165" s="155">
+      <c r="B165" s="160">
         <v>28</v>
       </c>
-      <c r="C165" s="155" t="s">
+      <c r="C165" s="160" t="s">
         <v>48</v>
       </c>
-      <c r="D165" s="175" t="s">
+      <c r="D165" s="193" t="s">
         <v>49</v>
       </c>
       <c r="E165" s="27" t="s">
@@ -21604,9 +21622,9 @@
       <c r="Z165" s="121"/>
     </row>
     <row r="166" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B166" s="156"/>
-      <c r="C166" s="156"/>
-      <c r="D166" s="176"/>
+      <c r="B166" s="161"/>
+      <c r="C166" s="161"/>
+      <c r="D166" s="194"/>
       <c r="E166" s="6" t="s">
         <v>13</v>
       </c>
@@ -21647,9 +21665,9 @@
       <c r="Z166" s="121"/>
     </row>
     <row r="167" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B167" s="156"/>
-      <c r="C167" s="156"/>
-      <c r="D167" s="176"/>
+      <c r="B167" s="161"/>
+      <c r="C167" s="161"/>
+      <c r="D167" s="194"/>
       <c r="E167" s="6" t="s">
         <v>110</v>
       </c>
@@ -21690,9 +21708,9 @@
       <c r="Z167" s="121"/>
     </row>
     <row r="168" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B168" s="156"/>
-      <c r="C168" s="156"/>
-      <c r="D168" s="176"/>
+      <c r="B168" s="161"/>
+      <c r="C168" s="161"/>
+      <c r="D168" s="194"/>
       <c r="E168" s="6" t="s">
         <v>109</v>
       </c>
@@ -21738,9 +21756,9 @@
       <c r="Z168" s="121"/>
     </row>
     <row r="169" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B169" s="156"/>
-      <c r="C169" s="156"/>
-      <c r="D169" s="156"/>
+      <c r="B169" s="161"/>
+      <c r="C169" s="161"/>
+      <c r="D169" s="161"/>
       <c r="E169" s="6" t="s">
         <v>106</v>
       </c>
@@ -21783,14 +21801,14 @@
       <c r="Z169" s="121"/>
     </row>
     <row r="170" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B170" s="157"/>
-      <c r="C170" s="157"/>
-      <c r="D170" s="157"/>
+      <c r="B170" s="162"/>
+      <c r="C170" s="162"/>
+      <c r="D170" s="162"/>
       <c r="E170" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F170" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G170" s="37"/>
       <c r="H170" s="61" t="str">
@@ -21829,13 +21847,13 @@
       <c r="A171" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B171" s="158">
+      <c r="B171" s="163">
         <v>29</v>
       </c>
-      <c r="C171" s="158" t="s">
+      <c r="C171" s="163" t="s">
         <v>50</v>
       </c>
-      <c r="D171" s="177" t="s">
+      <c r="D171" s="195" t="s">
         <v>49</v>
       </c>
       <c r="E171" s="26" t="s">
@@ -21876,9 +21894,9 @@
       <c r="Z171" s="121"/>
     </row>
     <row r="172" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B172" s="159"/>
-      <c r="C172" s="159"/>
-      <c r="D172" s="178"/>
+      <c r="B172" s="164"/>
+      <c r="C172" s="164"/>
+      <c r="D172" s="196"/>
       <c r="E172" s="3" t="s">
         <v>13</v>
       </c>
@@ -21919,9 +21937,9 @@
       <c r="Z172" s="121"/>
     </row>
     <row r="173" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B173" s="159"/>
-      <c r="C173" s="159"/>
-      <c r="D173" s="178"/>
+      <c r="B173" s="164"/>
+      <c r="C173" s="164"/>
+      <c r="D173" s="196"/>
       <c r="E173" s="3" t="s">
         <v>110</v>
       </c>
@@ -21962,9 +21980,9 @@
       <c r="Z173" s="121"/>
     </row>
     <row r="174" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B174" s="159"/>
-      <c r="C174" s="159"/>
-      <c r="D174" s="178"/>
+      <c r="B174" s="164"/>
+      <c r="C174" s="164"/>
+      <c r="D174" s="196"/>
       <c r="E174" s="3" t="s">
         <v>109</v>
       </c>
@@ -22010,9 +22028,9 @@
       <c r="Z174" s="121"/>
     </row>
     <row r="175" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B175" s="159"/>
-      <c r="C175" s="159"/>
-      <c r="D175" s="159"/>
+      <c r="B175" s="164"/>
+      <c r="C175" s="164"/>
+      <c r="D175" s="164"/>
       <c r="E175" s="3" t="s">
         <v>106</v>
       </c>
@@ -22055,14 +22073,14 @@
       <c r="Z175" s="121"/>
     </row>
     <row r="176" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B176" s="160"/>
-      <c r="C176" s="160"/>
-      <c r="D176" s="160"/>
+      <c r="B176" s="165"/>
+      <c r="C176" s="165"/>
+      <c r="D176" s="165"/>
       <c r="E176" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F176" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G176" s="39"/>
       <c r="H176" s="65" t="str">
@@ -22101,13 +22119,13 @@
       <c r="A177" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B177" s="155">
+      <c r="B177" s="160">
         <v>30</v>
       </c>
-      <c r="C177" s="155" t="s">
+      <c r="C177" s="160" t="s">
         <v>51</v>
       </c>
-      <c r="D177" s="175" t="s">
+      <c r="D177" s="193" t="s">
         <v>52</v>
       </c>
       <c r="E177" s="27" t="s">
@@ -22148,9 +22166,9 @@
       <c r="Z177" s="121"/>
     </row>
     <row r="178" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B178" s="156"/>
-      <c r="C178" s="156"/>
-      <c r="D178" s="176"/>
+      <c r="B178" s="161"/>
+      <c r="C178" s="161"/>
+      <c r="D178" s="194"/>
       <c r="E178" s="6" t="s">
         <v>13</v>
       </c>
@@ -22191,9 +22209,9 @@
       <c r="Z178" s="121"/>
     </row>
     <row r="179" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B179" s="156"/>
-      <c r="C179" s="156"/>
-      <c r="D179" s="176"/>
+      <c r="B179" s="161"/>
+      <c r="C179" s="161"/>
+      <c r="D179" s="194"/>
       <c r="E179" s="6" t="s">
         <v>110</v>
       </c>
@@ -22234,9 +22252,9 @@
       <c r="Z179" s="121"/>
     </row>
     <row r="180" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B180" s="156"/>
-      <c r="C180" s="156"/>
-      <c r="D180" s="176"/>
+      <c r="B180" s="161"/>
+      <c r="C180" s="161"/>
+      <c r="D180" s="194"/>
       <c r="E180" s="6" t="s">
         <v>109</v>
       </c>
@@ -22282,9 +22300,9 @@
       <c r="Z180" s="121"/>
     </row>
     <row r="181" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B181" s="156"/>
-      <c r="C181" s="156"/>
-      <c r="D181" s="156"/>
+      <c r="B181" s="161"/>
+      <c r="C181" s="161"/>
+      <c r="D181" s="161"/>
       <c r="E181" s="6" t="s">
         <v>106</v>
       </c>
@@ -22327,9 +22345,9 @@
       <c r="Z181" s="121"/>
     </row>
     <row r="182" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B182" s="157"/>
-      <c r="C182" s="157"/>
-      <c r="D182" s="157"/>
+      <c r="B182" s="162"/>
+      <c r="C182" s="162"/>
+      <c r="D182" s="162"/>
       <c r="E182" s="7" t="s">
         <v>14</v>
       </c>
@@ -22373,13 +22391,13 @@
       <c r="A183" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B183" s="158">
+      <c r="B183" s="163">
         <v>31</v>
       </c>
-      <c r="C183" s="158" t="s">
+      <c r="C183" s="163" t="s">
         <v>53</v>
       </c>
-      <c r="D183" s="177" t="s">
+      <c r="D183" s="195" t="s">
         <v>52</v>
       </c>
       <c r="E183" s="26" t="s">
@@ -22399,7 +22417,7 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K183" s="158" t="s">
+      <c r="K183" s="163" t="s">
         <v>175</v>
       </c>
       <c r="L183" s="41"/>
@@ -22422,9 +22440,9 @@
       <c r="Z183" s="121"/>
     </row>
     <row r="184" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B184" s="159"/>
-      <c r="C184" s="159"/>
-      <c r="D184" s="178"/>
+      <c r="B184" s="164"/>
+      <c r="C184" s="164"/>
+      <c r="D184" s="196"/>
       <c r="E184" s="3" t="s">
         <v>13</v>
       </c>
@@ -22446,7 +22464,7 @@
         <f t="shared" si="24"/>
         <v>59.430708808677764</v>
       </c>
-      <c r="K184" s="159"/>
+      <c r="K184" s="164"/>
       <c r="L184" s="42"/>
       <c r="U184" s="119" t="str" cm="1">
         <f t="array" ref="U184">IF(C184="",INDEX(C178:C184,MATCH(TRUE,INDEX((C178:C184&lt;&gt;""),0),0)),C184)</f>
@@ -22467,9 +22485,9 @@
       <c r="Z184" s="121"/>
     </row>
     <row r="185" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B185" s="159"/>
-      <c r="C185" s="159"/>
-      <c r="D185" s="178"/>
+      <c r="B185" s="164"/>
+      <c r="C185" s="164"/>
+      <c r="D185" s="196"/>
       <c r="E185" s="3" t="s">
         <v>110</v>
       </c>
@@ -22489,7 +22507,7 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K185" s="159"/>
+      <c r="K185" s="164"/>
       <c r="L185" s="42"/>
       <c r="U185" s="119" t="str" cm="1">
         <f t="array" ref="U185">IF(C185="",INDEX(C179:C185,MATCH(TRUE,INDEX((C179:C185&lt;&gt;""),0),0)),C185)</f>
@@ -22510,9 +22528,9 @@
       <c r="Z185" s="121"/>
     </row>
     <row r="186" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B186" s="159"/>
-      <c r="C186" s="159"/>
-      <c r="D186" s="178"/>
+      <c r="B186" s="164"/>
+      <c r="C186" s="164"/>
+      <c r="D186" s="196"/>
       <c r="E186" s="3" t="s">
         <v>109</v>
       </c>
@@ -22534,7 +22552,7 @@
         <f t="shared" si="24"/>
         <v>86.360248737609879</v>
       </c>
-      <c r="K186" s="159"/>
+      <c r="K186" s="164"/>
       <c r="L186" s="42" t="s">
         <v>274</v>
       </c>
@@ -22560,9 +22578,9 @@
       <c r="Z186" s="121"/>
     </row>
     <row r="187" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B187" s="159"/>
-      <c r="C187" s="159"/>
-      <c r="D187" s="159"/>
+      <c r="B187" s="164"/>
+      <c r="C187" s="164"/>
+      <c r="D187" s="164"/>
       <c r="E187" s="3" t="s">
         <v>106</v>
       </c>
@@ -22584,7 +22602,7 @@
         <f t="shared" si="24"/>
         <v>78.931410136525159</v>
       </c>
-      <c r="K187" s="159"/>
+      <c r="K187" s="164"/>
       <c r="L187" s="42"/>
       <c r="U187" s="119" t="str" cm="1">
         <f t="array" ref="U187">IF(C187="",INDEX(C181:C187,MATCH(TRUE,INDEX((C181:C187&lt;&gt;""),0),0)),C187)</f>
@@ -22605,9 +22623,9 @@
       <c r="Z187" s="121"/>
     </row>
     <row r="188" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B188" s="160"/>
-      <c r="C188" s="160"/>
-      <c r="D188" s="160"/>
+      <c r="B188" s="165"/>
+      <c r="C188" s="165"/>
+      <c r="D188" s="165"/>
       <c r="E188" s="4" t="s">
         <v>14</v>
       </c>
@@ -22627,7 +22645,7 @@
         <f t="shared" si="24"/>
         <v>7.4288386010847205</v>
       </c>
-      <c r="K188" s="160"/>
+      <c r="K188" s="165"/>
       <c r="L188" s="43"/>
       <c r="U188" s="119" t="str" cm="1">
         <f t="array" ref="U188">IF(C188="",INDEX(C182:C188,MATCH(TRUE,INDEX((C182:C188&lt;&gt;""),0),0)),C188)</f>
@@ -22651,13 +22669,13 @@
       <c r="A189" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B189" s="155">
+      <c r="B189" s="160">
         <v>32</v>
       </c>
-      <c r="C189" s="155" t="s">
+      <c r="C189" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="D189" s="155" t="s">
+      <c r="D189" s="160" t="s">
         <v>55</v>
       </c>
       <c r="E189" s="27" t="s">
@@ -22698,9 +22716,9 @@
       <c r="Z189" s="121"/>
     </row>
     <row r="190" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B190" s="156"/>
-      <c r="C190" s="156"/>
-      <c r="D190" s="156"/>
+      <c r="B190" s="161"/>
+      <c r="C190" s="161"/>
+      <c r="D190" s="161"/>
       <c r="E190" s="6" t="s">
         <v>13</v>
       </c>
@@ -22741,9 +22759,9 @@
       <c r="Z190" s="121"/>
     </row>
     <row r="191" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B191" s="156"/>
-      <c r="C191" s="156"/>
-      <c r="D191" s="156"/>
+      <c r="B191" s="161"/>
+      <c r="C191" s="161"/>
+      <c r="D191" s="161"/>
       <c r="E191" s="6" t="s">
         <v>110</v>
       </c>
@@ -22784,9 +22802,9 @@
       <c r="Z191" s="121"/>
     </row>
     <row r="192" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B192" s="156"/>
-      <c r="C192" s="156"/>
-      <c r="D192" s="156"/>
+      <c r="B192" s="161"/>
+      <c r="C192" s="161"/>
+      <c r="D192" s="161"/>
       <c r="E192" s="6" t="s">
         <v>109</v>
       </c>
@@ -22827,9 +22845,9 @@
       <c r="Z192" s="121"/>
     </row>
     <row r="193" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B193" s="156"/>
-      <c r="C193" s="156"/>
-      <c r="D193" s="156"/>
+      <c r="B193" s="161"/>
+      <c r="C193" s="161"/>
+      <c r="D193" s="161"/>
       <c r="E193" s="6" t="s">
         <v>106</v>
       </c>
@@ -22870,14 +22888,14 @@
       <c r="Z193" s="121"/>
     </row>
     <row r="194" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B194" s="157"/>
-      <c r="C194" s="157"/>
-      <c r="D194" s="157"/>
+      <c r="B194" s="162"/>
+      <c r="C194" s="162"/>
+      <c r="D194" s="162"/>
       <c r="E194" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F194" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G194" s="37"/>
       <c r="H194" s="61" t="str">
@@ -22916,13 +22934,13 @@
       <c r="A195" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B195" s="158">
+      <c r="B195" s="163">
         <v>33</v>
       </c>
-      <c r="C195" s="158" t="s">
+      <c r="C195" s="163" t="s">
         <v>56</v>
       </c>
-      <c r="D195" s="158" t="s">
+      <c r="D195" s="163" t="s">
         <v>163</v>
       </c>
       <c r="E195" s="26" t="s">
@@ -22942,7 +22960,7 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K195" s="173" t="s">
+      <c r="K195" s="206" t="s">
         <v>164</v>
       </c>
       <c r="L195" s="41"/>
@@ -22965,9 +22983,9 @@
       <c r="Z195" s="121"/>
     </row>
     <row r="196" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B196" s="159"/>
-      <c r="C196" s="159"/>
-      <c r="D196" s="159"/>
+      <c r="B196" s="164"/>
+      <c r="C196" s="164"/>
+      <c r="D196" s="164"/>
       <c r="E196" s="3" t="s">
         <v>13</v>
       </c>
@@ -22989,7 +23007,7 @@
         <f t="shared" si="24"/>
         <v>47.087338694595097</v>
       </c>
-      <c r="K196" s="159"/>
+      <c r="K196" s="164"/>
       <c r="L196" s="42"/>
       <c r="U196" s="119" t="str" cm="1">
         <f t="array" ref="U196">IF(C196="",INDEX(C190:C196,MATCH(TRUE,INDEX((C190:C196&lt;&gt;""),0),0)),C196)</f>
@@ -23010,9 +23028,9 @@
       <c r="Z196" s="121"/>
     </row>
     <row r="197" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B197" s="159"/>
-      <c r="C197" s="159"/>
-      <c r="D197" s="159"/>
+      <c r="B197" s="164"/>
+      <c r="C197" s="164"/>
+      <c r="D197" s="164"/>
       <c r="E197" s="3" t="s">
         <v>110</v>
       </c>
@@ -23032,7 +23050,7 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K197" s="159"/>
+      <c r="K197" s="164"/>
       <c r="L197" s="42"/>
       <c r="U197" s="119" t="str" cm="1">
         <f t="array" ref="U197">IF(C197="",INDEX(C191:C197,MATCH(TRUE,INDEX((C191:C197&lt;&gt;""),0),0)),C197)</f>
@@ -23053,9 +23071,9 @@
       <c r="Z197" s="121"/>
     </row>
     <row r="198" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B198" s="159"/>
-      <c r="C198" s="159"/>
-      <c r="D198" s="159"/>
+      <c r="B198" s="164"/>
+      <c r="C198" s="164"/>
+      <c r="D198" s="164"/>
       <c r="E198" s="3" t="s">
         <v>109</v>
       </c>
@@ -23077,7 +23095,7 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K198" s="159"/>
+      <c r="K198" s="164"/>
       <c r="L198" s="42"/>
       <c r="U198" s="119" t="str" cm="1">
         <f t="array" ref="U198">IF(C198="",INDEX(C192:C198,MATCH(TRUE,INDEX((C192:C198&lt;&gt;""),0),0)),C198)</f>
@@ -23098,9 +23116,9 @@
       <c r="Z198" s="121"/>
     </row>
     <row r="199" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B199" s="159"/>
-      <c r="C199" s="159"/>
-      <c r="D199" s="159"/>
+      <c r="B199" s="164"/>
+      <c r="C199" s="164"/>
+      <c r="D199" s="164"/>
       <c r="E199" s="3" t="s">
         <v>106</v>
       </c>
@@ -23122,7 +23140,7 @@
         <f t="shared" si="24"/>
         <v>62.537871703759116</v>
       </c>
-      <c r="K199" s="159"/>
+      <c r="K199" s="164"/>
       <c r="L199" s="42"/>
       <c r="U199" s="119" t="str" cm="1">
         <f t="array" ref="U199">IF(C199="",INDEX(C193:C199,MATCH(TRUE,INDEX((C193:C199&lt;&gt;""),0),0)),C199)</f>
@@ -23143,14 +23161,14 @@
       <c r="Z199" s="121"/>
     </row>
     <row r="200" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B200" s="160"/>
-      <c r="C200" s="160"/>
-      <c r="D200" s="160"/>
+      <c r="B200" s="165"/>
+      <c r="C200" s="165"/>
+      <c r="D200" s="165"/>
       <c r="E200" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F200" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G200" s="39"/>
       <c r="H200" s="65" t="str">
@@ -23165,7 +23183,7 @@
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K200" s="160"/>
+      <c r="K200" s="165"/>
       <c r="L200" s="43"/>
       <c r="U200" s="119" t="str" cm="1">
         <f t="array" ref="U200">IF(C200="",INDEX(C194:C200,MATCH(TRUE,INDEX((C194:C200&lt;&gt;""),0),0)),C200)</f>
@@ -23189,13 +23207,13 @@
       <c r="A201" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B201" s="155">
+      <c r="B201" s="160">
         <v>34</v>
       </c>
-      <c r="C201" s="155" t="s">
+      <c r="C201" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="D201" s="155" t="s">
+      <c r="D201" s="160" t="s">
         <v>55</v>
       </c>
       <c r="E201" s="27" t="s">
@@ -23236,9 +23254,9 @@
       <c r="Z201" s="121"/>
     </row>
     <row r="202" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B202" s="156"/>
-      <c r="C202" s="156"/>
-      <c r="D202" s="156"/>
+      <c r="B202" s="161"/>
+      <c r="C202" s="161"/>
+      <c r="D202" s="161"/>
       <c r="E202" s="6" t="s">
         <v>13</v>
       </c>
@@ -23279,9 +23297,9 @@
       <c r="Z202" s="121"/>
     </row>
     <row r="203" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B203" s="156"/>
-      <c r="C203" s="156"/>
-      <c r="D203" s="156"/>
+      <c r="B203" s="161"/>
+      <c r="C203" s="161"/>
+      <c r="D203" s="161"/>
       <c r="E203" s="6" t="s">
         <v>110</v>
       </c>
@@ -23322,9 +23340,9 @@
       <c r="Z203" s="121"/>
     </row>
     <row r="204" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B204" s="156"/>
-      <c r="C204" s="156"/>
-      <c r="D204" s="156"/>
+      <c r="B204" s="161"/>
+      <c r="C204" s="161"/>
+      <c r="D204" s="161"/>
       <c r="E204" s="6" t="s">
         <v>109</v>
       </c>
@@ -23365,11 +23383,11 @@
       <c r="Z204" s="121"/>
     </row>
     <row r="205" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B205" s="156"/>
-      <c r="C205" s="156"/>
-      <c r="D205" s="156"/>
+      <c r="B205" s="161"/>
+      <c r="C205" s="161"/>
+      <c r="D205" s="161"/>
       <c r="E205" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F205" s="32" t="s">
         <v>17</v>
@@ -23408,9 +23426,9 @@
       <c r="Z205" s="121"/>
     </row>
     <row r="206" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B206" s="156"/>
-      <c r="C206" s="156"/>
-      <c r="D206" s="156"/>
+      <c r="B206" s="161"/>
+      <c r="C206" s="161"/>
+      <c r="D206" s="161"/>
       <c r="E206" s="6" t="s">
         <v>106</v>
       </c>
@@ -23451,14 +23469,14 @@
       <c r="Z206" s="121"/>
     </row>
     <row r="207" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B207" s="157"/>
-      <c r="C207" s="157"/>
-      <c r="D207" s="157"/>
+      <c r="B207" s="162"/>
+      <c r="C207" s="162"/>
+      <c r="D207" s="162"/>
       <c r="E207" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F207" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G207" s="37"/>
       <c r="H207" s="61" t="str">
@@ -23497,13 +23515,13 @@
       <c r="A208" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B208" s="158">
+      <c r="B208" s="163">
         <v>35</v>
       </c>
-      <c r="C208" s="158" t="s">
+      <c r="C208" s="163" t="s">
         <v>58</v>
       </c>
-      <c r="D208" s="158" t="s">
+      <c r="D208" s="163" t="s">
         <v>59</v>
       </c>
       <c r="E208" s="26" t="s">
@@ -23544,9 +23562,9 @@
       <c r="Z208" s="121"/>
     </row>
     <row r="209" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B209" s="159"/>
-      <c r="C209" s="159"/>
-      <c r="D209" s="159"/>
+      <c r="B209" s="164"/>
+      <c r="C209" s="164"/>
+      <c r="D209" s="164"/>
       <c r="E209" s="3" t="s">
         <v>13</v>
       </c>
@@ -23587,9 +23605,9 @@
       <c r="Z209" s="121"/>
     </row>
     <row r="210" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B210" s="159"/>
-      <c r="C210" s="159"/>
-      <c r="D210" s="159"/>
+      <c r="B210" s="164"/>
+      <c r="C210" s="164"/>
+      <c r="D210" s="164"/>
       <c r="E210" s="3" t="s">
         <v>109</v>
       </c>
@@ -23630,9 +23648,9 @@
       <c r="Z210" s="121"/>
     </row>
     <row r="211" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B211" s="159"/>
-      <c r="C211" s="159"/>
-      <c r="D211" s="159"/>
+      <c r="B211" s="164"/>
+      <c r="C211" s="164"/>
+      <c r="D211" s="164"/>
       <c r="E211" s="3" t="s">
         <v>110</v>
       </c>
@@ -23673,9 +23691,9 @@
       <c r="Z211" s="121"/>
     </row>
     <row r="212" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B212" s="159"/>
-      <c r="C212" s="159"/>
-      <c r="D212" s="159"/>
+      <c r="B212" s="164"/>
+      <c r="C212" s="164"/>
+      <c r="D212" s="164"/>
       <c r="E212" s="3" t="s">
         <v>106</v>
       </c>
@@ -23718,9 +23736,9 @@
       <c r="Z212" s="121"/>
     </row>
     <row r="213" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B213" s="160"/>
-      <c r="C213" s="160"/>
-      <c r="D213" s="160"/>
+      <c r="B213" s="165"/>
+      <c r="C213" s="165"/>
+      <c r="D213" s="165"/>
       <c r="E213" s="4" t="s">
         <v>14</v>
       </c>
@@ -23764,13 +23782,13 @@
       <c r="A214" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B214" s="155">
+      <c r="B214" s="160">
         <v>36</v>
       </c>
-      <c r="C214" s="155" t="s">
+      <c r="C214" s="160" t="s">
         <v>60</v>
       </c>
-      <c r="D214" s="155" t="s">
+      <c r="D214" s="160" t="s">
         <v>59</v>
       </c>
       <c r="E214" s="27" t="s">
@@ -23811,9 +23829,9 @@
       <c r="Z214" s="121"/>
     </row>
     <row r="215" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B215" s="156"/>
-      <c r="C215" s="156"/>
-      <c r="D215" s="156"/>
+      <c r="B215" s="161"/>
+      <c r="C215" s="161"/>
+      <c r="D215" s="161"/>
       <c r="E215" s="6" t="s">
         <v>13</v>
       </c>
@@ -23854,9 +23872,9 @@
       <c r="Z215" s="121"/>
     </row>
     <row r="216" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B216" s="156"/>
-      <c r="C216" s="156"/>
-      <c r="D216" s="156"/>
+      <c r="B216" s="161"/>
+      <c r="C216" s="161"/>
+      <c r="D216" s="161"/>
       <c r="E216" s="6" t="s">
         <v>110</v>
       </c>
@@ -23897,9 +23915,9 @@
       <c r="Z216" s="121"/>
     </row>
     <row r="217" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B217" s="156"/>
-      <c r="C217" s="156"/>
-      <c r="D217" s="156"/>
+      <c r="B217" s="161"/>
+      <c r="C217" s="161"/>
+      <c r="D217" s="161"/>
       <c r="E217" s="6" t="s">
         <v>109</v>
       </c>
@@ -23940,9 +23958,9 @@
       <c r="Z217" s="121"/>
     </row>
     <row r="218" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B218" s="156"/>
-      <c r="C218" s="156"/>
-      <c r="D218" s="156"/>
+      <c r="B218" s="161"/>
+      <c r="C218" s="161"/>
+      <c r="D218" s="161"/>
       <c r="E218" s="6" t="s">
         <v>106</v>
       </c>
@@ -23983,9 +24001,9 @@
       <c r="Z218" s="121"/>
     </row>
     <row r="219" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B219" s="157"/>
-      <c r="C219" s="157"/>
-      <c r="D219" s="157"/>
+      <c r="B219" s="162"/>
+      <c r="C219" s="162"/>
+      <c r="D219" s="162"/>
       <c r="E219" s="7" t="s">
         <v>14</v>
       </c>
@@ -24029,13 +24047,13 @@
       <c r="A220" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B220" s="158">
+      <c r="B220" s="163">
         <v>37</v>
       </c>
-      <c r="C220" s="158" t="s">
+      <c r="C220" s="163" t="s">
         <v>61</v>
       </c>
-      <c r="D220" s="158" t="s">
+      <c r="D220" s="163" t="s">
         <v>62</v>
       </c>
       <c r="E220" s="26" t="s">
@@ -24076,9 +24094,9 @@
       <c r="Z220" s="121"/>
     </row>
     <row r="221" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B221" s="159"/>
-      <c r="C221" s="159"/>
-      <c r="D221" s="159"/>
+      <c r="B221" s="164"/>
+      <c r="C221" s="164"/>
+      <c r="D221" s="164"/>
       <c r="E221" s="3" t="s">
         <v>13</v>
       </c>
@@ -24121,9 +24139,9 @@
       <c r="Z221" s="121"/>
     </row>
     <row r="222" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B222" s="159"/>
-      <c r="C222" s="159"/>
-      <c r="D222" s="159"/>
+      <c r="B222" s="164"/>
+      <c r="C222" s="164"/>
+      <c r="D222" s="164"/>
       <c r="E222" s="3" t="s">
         <v>110</v>
       </c>
@@ -24164,9 +24182,9 @@
       <c r="Z222" s="121"/>
     </row>
     <row r="223" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B223" s="159"/>
-      <c r="C223" s="159"/>
-      <c r="D223" s="159"/>
+      <c r="B223" s="164"/>
+      <c r="C223" s="164"/>
+      <c r="D223" s="164"/>
       <c r="E223" s="3" t="s">
         <v>109</v>
       </c>
@@ -24209,9 +24227,9 @@
       <c r="Z223" s="121"/>
     </row>
     <row r="224" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B224" s="159"/>
-      <c r="C224" s="159"/>
-      <c r="D224" s="159"/>
+      <c r="B224" s="164"/>
+      <c r="C224" s="164"/>
+      <c r="D224" s="164"/>
       <c r="E224" s="3" t="s">
         <v>106</v>
       </c>
@@ -24254,14 +24272,14 @@
       <c r="Z224" s="121"/>
     </row>
     <row r="225" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B225" s="160"/>
-      <c r="C225" s="160"/>
-      <c r="D225" s="160"/>
+      <c r="B225" s="165"/>
+      <c r="C225" s="165"/>
+      <c r="D225" s="165"/>
       <c r="E225" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F225" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G225" s="39"/>
       <c r="H225" s="65" t="str">
@@ -24300,13 +24318,13 @@
       <c r="A226" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B226" s="155">
+      <c r="B226" s="160">
         <v>38</v>
       </c>
-      <c r="C226" s="155" t="s">
+      <c r="C226" s="160" t="s">
         <v>63</v>
       </c>
-      <c r="D226" s="155" t="s">
+      <c r="D226" s="160" t="s">
         <v>64</v>
       </c>
       <c r="E226" s="27" t="s">
@@ -24347,9 +24365,9 @@
       <c r="Z226" s="121"/>
     </row>
     <row r="227" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B227" s="156"/>
-      <c r="C227" s="156"/>
-      <c r="D227" s="156"/>
+      <c r="B227" s="161"/>
+      <c r="C227" s="161"/>
+      <c r="D227" s="161"/>
       <c r="E227" s="6" t="s">
         <v>13</v>
       </c>
@@ -24392,9 +24410,9 @@
       <c r="Z227" s="121"/>
     </row>
     <row r="228" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B228" s="156"/>
-      <c r="C228" s="156"/>
-      <c r="D228" s="156"/>
+      <c r="B228" s="161"/>
+      <c r="C228" s="161"/>
+      <c r="D228" s="161"/>
       <c r="E228" s="6" t="s">
         <v>110</v>
       </c>
@@ -24435,9 +24453,9 @@
       <c r="Z228" s="121"/>
     </row>
     <row r="229" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B229" s="156"/>
-      <c r="C229" s="156"/>
-      <c r="D229" s="156"/>
+      <c r="B229" s="161"/>
+      <c r="C229" s="161"/>
+      <c r="D229" s="161"/>
       <c r="E229" s="6" t="s">
         <v>109</v>
       </c>
@@ -24480,9 +24498,9 @@
       <c r="Z229" s="121"/>
     </row>
     <row r="230" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B230" s="156"/>
-      <c r="C230" s="156"/>
-      <c r="D230" s="156"/>
+      <c r="B230" s="161"/>
+      <c r="C230" s="161"/>
+      <c r="D230" s="161"/>
       <c r="E230" s="6" t="s">
         <v>106</v>
       </c>
@@ -24523,14 +24541,14 @@
       <c r="Z230" s="121"/>
     </row>
     <row r="231" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B231" s="157"/>
-      <c r="C231" s="157"/>
-      <c r="D231" s="157"/>
+      <c r="B231" s="162"/>
+      <c r="C231" s="162"/>
+      <c r="D231" s="162"/>
       <c r="E231" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F231" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G231" s="37"/>
       <c r="H231" s="61" t="str">
@@ -24569,13 +24587,13 @@
       <c r="A232" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B232" s="158">
+      <c r="B232" s="163">
         <v>39</v>
       </c>
-      <c r="C232" s="158" t="s">
+      <c r="C232" s="163" t="s">
         <v>65</v>
       </c>
-      <c r="D232" s="158" t="s">
+      <c r="D232" s="163" t="s">
         <v>64</v>
       </c>
       <c r="E232" s="26" t="s">
@@ -24616,9 +24634,9 @@
       <c r="Z232" s="121"/>
     </row>
     <row r="233" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B233" s="159"/>
-      <c r="C233" s="159"/>
-      <c r="D233" s="159"/>
+      <c r="B233" s="164"/>
+      <c r="C233" s="164"/>
+      <c r="D233" s="164"/>
       <c r="E233" s="3" t="s">
         <v>13</v>
       </c>
@@ -24659,9 +24677,9 @@
       <c r="Z233" s="121"/>
     </row>
     <row r="234" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B234" s="159"/>
-      <c r="C234" s="159"/>
-      <c r="D234" s="159"/>
+      <c r="B234" s="164"/>
+      <c r="C234" s="164"/>
+      <c r="D234" s="164"/>
       <c r="E234" s="3" t="s">
         <v>110</v>
       </c>
@@ -24702,9 +24720,9 @@
       <c r="Z234" s="121"/>
     </row>
     <row r="235" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B235" s="159"/>
-      <c r="C235" s="159"/>
-      <c r="D235" s="159"/>
+      <c r="B235" s="164"/>
+      <c r="C235" s="164"/>
+      <c r="D235" s="164"/>
       <c r="E235" s="3" t="s">
         <v>109</v>
       </c>
@@ -24747,11 +24765,11 @@
       <c r="Z235" s="121"/>
     </row>
     <row r="236" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B236" s="159"/>
-      <c r="C236" s="159"/>
-      <c r="D236" s="159"/>
+      <c r="B236" s="164"/>
+      <c r="C236" s="164"/>
+      <c r="D236" s="164"/>
       <c r="E236" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F236" s="31" t="s">
         <v>17</v>
@@ -24790,9 +24808,9 @@
       <c r="Z236" s="121"/>
     </row>
     <row r="237" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B237" s="159"/>
-      <c r="C237" s="159"/>
-      <c r="D237" s="159"/>
+      <c r="B237" s="164"/>
+      <c r="C237" s="164"/>
+      <c r="D237" s="164"/>
       <c r="E237" s="3" t="s">
         <v>106</v>
       </c>
@@ -24833,14 +24851,14 @@
       <c r="Z237" s="121"/>
     </row>
     <row r="238" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B238" s="160"/>
-      <c r="C238" s="160"/>
-      <c r="D238" s="160"/>
+      <c r="B238" s="165"/>
+      <c r="C238" s="165"/>
+      <c r="D238" s="165"/>
       <c r="E238" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F238" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G238" s="39"/>
       <c r="H238" s="65" t="str">
@@ -24879,13 +24897,13 @@
       <c r="A239" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B239" s="155">
+      <c r="B239" s="160">
         <v>40</v>
       </c>
-      <c r="C239" s="155" t="s">
+      <c r="C239" s="160" t="s">
         <v>66</v>
       </c>
-      <c r="D239" s="155" t="s">
+      <c r="D239" s="160" t="s">
         <v>136</v>
       </c>
       <c r="E239" s="27" t="s">
@@ -24926,9 +24944,9 @@
       <c r="Z239" s="121"/>
     </row>
     <row r="240" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B240" s="156"/>
-      <c r="C240" s="156"/>
-      <c r="D240" s="156"/>
+      <c r="B240" s="161"/>
+      <c r="C240" s="161"/>
+      <c r="D240" s="161"/>
       <c r="E240" s="6" t="s">
         <v>13</v>
       </c>
@@ -24969,9 +24987,9 @@
       <c r="Z240" s="121"/>
     </row>
     <row r="241" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B241" s="156"/>
-      <c r="C241" s="156"/>
-      <c r="D241" s="156"/>
+      <c r="B241" s="161"/>
+      <c r="C241" s="161"/>
+      <c r="D241" s="161"/>
       <c r="E241" s="6" t="s">
         <v>110</v>
       </c>
@@ -25012,9 +25030,9 @@
       <c r="Z241" s="121"/>
     </row>
     <row r="242" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B242" s="156"/>
-      <c r="C242" s="156"/>
-      <c r="D242" s="156"/>
+      <c r="B242" s="161"/>
+      <c r="C242" s="161"/>
+      <c r="D242" s="161"/>
       <c r="E242" s="6" t="s">
         <v>109</v>
       </c>
@@ -25057,9 +25075,9 @@
       <c r="Z242" s="121"/>
     </row>
     <row r="243" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B243" s="156"/>
-      <c r="C243" s="156"/>
-      <c r="D243" s="156"/>
+      <c r="B243" s="161"/>
+      <c r="C243" s="161"/>
+      <c r="D243" s="161"/>
       <c r="E243" s="6" t="s">
         <v>106</v>
       </c>
@@ -25100,14 +25118,14 @@
       <c r="Z243" s="121"/>
     </row>
     <row r="244" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B244" s="157"/>
-      <c r="C244" s="157"/>
-      <c r="D244" s="157"/>
+      <c r="B244" s="162"/>
+      <c r="C244" s="162"/>
+      <c r="D244" s="162"/>
       <c r="E244" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F244" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G244" s="37"/>
       <c r="H244" s="61" t="str">
@@ -25146,13 +25164,13 @@
       <c r="A245" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B245" s="158">
+      <c r="B245" s="163">
         <v>41</v>
       </c>
-      <c r="C245" s="158" t="s">
+      <c r="C245" s="163" t="s">
         <v>67</v>
       </c>
-      <c r="D245" s="158" t="s">
+      <c r="D245" s="163" t="s">
         <v>64</v>
       </c>
       <c r="E245" s="26" t="s">
@@ -25193,9 +25211,9 @@
       <c r="Z245" s="121"/>
     </row>
     <row r="246" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B246" s="159"/>
-      <c r="C246" s="159"/>
-      <c r="D246" s="159"/>
+      <c r="B246" s="164"/>
+      <c r="C246" s="164"/>
+      <c r="D246" s="164"/>
       <c r="E246" s="3" t="s">
         <v>13</v>
       </c>
@@ -25236,9 +25254,9 @@
       <c r="Z246" s="121"/>
     </row>
     <row r="247" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B247" s="159"/>
-      <c r="C247" s="159"/>
-      <c r="D247" s="159"/>
+      <c r="B247" s="164"/>
+      <c r="C247" s="164"/>
+      <c r="D247" s="164"/>
       <c r="E247" s="3" t="s">
         <v>110</v>
       </c>
@@ -25279,9 +25297,9 @@
       <c r="Z247" s="121"/>
     </row>
     <row r="248" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B248" s="159"/>
-      <c r="C248" s="159"/>
-      <c r="D248" s="159"/>
+      <c r="B248" s="164"/>
+      <c r="C248" s="164"/>
+      <c r="D248" s="164"/>
       <c r="E248" s="3" t="s">
         <v>109</v>
       </c>
@@ -25322,9 +25340,9 @@
       <c r="Z248" s="121"/>
     </row>
     <row r="249" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B249" s="159"/>
-      <c r="C249" s="159"/>
-      <c r="D249" s="159"/>
+      <c r="B249" s="164"/>
+      <c r="C249" s="164"/>
+      <c r="D249" s="164"/>
       <c r="E249" s="3" t="s">
         <v>106</v>
       </c>
@@ -25365,14 +25383,14 @@
       <c r="Z249" s="121"/>
     </row>
     <row r="250" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B250" s="160"/>
-      <c r="C250" s="160"/>
-      <c r="D250" s="160"/>
+      <c r="B250" s="165"/>
+      <c r="C250" s="165"/>
+      <c r="D250" s="165"/>
       <c r="E250" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F250" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G250" s="39"/>
       <c r="H250" s="65" t="str">
@@ -25411,13 +25429,13 @@
       <c r="A251" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B251" s="155">
+      <c r="B251" s="160">
         <v>42</v>
       </c>
-      <c r="C251" s="155" t="s">
+      <c r="C251" s="160" t="s">
         <v>68</v>
       </c>
-      <c r="D251" s="155" t="s">
+      <c r="D251" s="160" t="s">
         <v>69</v>
       </c>
       <c r="E251" s="27" t="s">
@@ -25458,9 +25476,9 @@
       <c r="Z251" s="121"/>
     </row>
     <row r="252" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B252" s="156"/>
-      <c r="C252" s="156"/>
-      <c r="D252" s="156"/>
+      <c r="B252" s="161"/>
+      <c r="C252" s="161"/>
+      <c r="D252" s="161"/>
       <c r="E252" s="6" t="s">
         <v>13</v>
       </c>
@@ -25501,9 +25519,9 @@
       <c r="Z252" s="121"/>
     </row>
     <row r="253" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B253" s="156"/>
-      <c r="C253" s="156"/>
-      <c r="D253" s="156"/>
+      <c r="B253" s="161"/>
+      <c r="C253" s="161"/>
+      <c r="D253" s="161"/>
       <c r="E253" s="6" t="s">
         <v>103</v>
       </c>
@@ -25548,9 +25566,9 @@
       <c r="Z253" s="121"/>
     </row>
     <row r="254" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B254" s="156"/>
-      <c r="C254" s="156"/>
-      <c r="D254" s="156"/>
+      <c r="B254" s="161"/>
+      <c r="C254" s="161"/>
+      <c r="D254" s="161"/>
       <c r="E254" s="6" t="s">
         <v>110</v>
       </c>
@@ -25591,9 +25609,9 @@
       <c r="Z254" s="121"/>
     </row>
     <row r="255" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B255" s="156"/>
-      <c r="C255" s="156"/>
-      <c r="D255" s="156"/>
+      <c r="B255" s="161"/>
+      <c r="C255" s="161"/>
+      <c r="D255" s="161"/>
       <c r="E255" s="6" t="s">
         <v>109</v>
       </c>
@@ -25636,9 +25654,9 @@
       <c r="Z255" s="121"/>
     </row>
     <row r="256" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B256" s="156"/>
-      <c r="C256" s="156"/>
-      <c r="D256" s="156"/>
+      <c r="B256" s="161"/>
+      <c r="C256" s="161"/>
+      <c r="D256" s="161"/>
       <c r="E256" s="6" t="s">
         <v>106</v>
       </c>
@@ -25679,14 +25697,14 @@
       <c r="Z256" s="121"/>
     </row>
     <row r="257" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B257" s="157"/>
-      <c r="C257" s="157"/>
-      <c r="D257" s="157"/>
+      <c r="B257" s="162"/>
+      <c r="C257" s="162"/>
+      <c r="D257" s="162"/>
       <c r="E257" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F257" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G257" s="37"/>
       <c r="H257" s="61" t="str">
@@ -25725,13 +25743,13 @@
       <c r="A258" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B258" s="158">
+      <c r="B258" s="163">
         <v>43</v>
       </c>
-      <c r="C258" s="158" t="s">
+      <c r="C258" s="163" t="s">
         <v>70</v>
       </c>
-      <c r="D258" s="158" t="s">
+      <c r="D258" s="163" t="s">
         <v>69</v>
       </c>
       <c r="E258" s="26" t="s">
@@ -25772,9 +25790,9 @@
       <c r="Z258" s="121"/>
     </row>
     <row r="259" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B259" s="159"/>
-      <c r="C259" s="159"/>
-      <c r="D259" s="159"/>
+      <c r="B259" s="164"/>
+      <c r="C259" s="164"/>
+      <c r="D259" s="164"/>
       <c r="E259" s="3" t="s">
         <v>13</v>
       </c>
@@ -25815,9 +25833,9 @@
       <c r="Z259" s="121"/>
     </row>
     <row r="260" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B260" s="159"/>
-      <c r="C260" s="159"/>
-      <c r="D260" s="159"/>
+      <c r="B260" s="164"/>
+      <c r="C260" s="164"/>
+      <c r="D260" s="164"/>
       <c r="E260" s="3" t="s">
         <v>103</v>
       </c>
@@ -25862,9 +25880,9 @@
       <c r="Z260" s="121"/>
     </row>
     <row r="261" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B261" s="159"/>
-      <c r="C261" s="159"/>
-      <c r="D261" s="159"/>
+      <c r="B261" s="164"/>
+      <c r="C261" s="164"/>
+      <c r="D261" s="164"/>
       <c r="E261" s="3" t="s">
         <v>110</v>
       </c>
@@ -25905,9 +25923,9 @@
       <c r="Z261" s="121"/>
     </row>
     <row r="262" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B262" s="159"/>
-      <c r="C262" s="159"/>
-      <c r="D262" s="159"/>
+      <c r="B262" s="164"/>
+      <c r="C262" s="164"/>
+      <c r="D262" s="164"/>
       <c r="E262" s="3" t="s">
         <v>109</v>
       </c>
@@ -25950,9 +25968,9 @@
       <c r="Z262" s="121"/>
     </row>
     <row r="263" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B263" s="159"/>
-      <c r="C263" s="159"/>
-      <c r="D263" s="159"/>
+      <c r="B263" s="164"/>
+      <c r="C263" s="164"/>
+      <c r="D263" s="164"/>
       <c r="E263" s="3" t="s">
         <v>106</v>
       </c>
@@ -25993,9 +26011,9 @@
       <c r="Z263" s="121"/>
     </row>
     <row r="264" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B264" s="160"/>
-      <c r="C264" s="160"/>
-      <c r="D264" s="160"/>
+      <c r="B264" s="165"/>
+      <c r="C264" s="165"/>
+      <c r="D264" s="165"/>
       <c r="E264" s="4" t="s">
         <v>14</v>
       </c>
@@ -26041,13 +26059,13 @@
       <c r="A265" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B265" s="155">
+      <c r="B265" s="160">
         <v>44</v>
       </c>
-      <c r="C265" s="155" t="s">
+      <c r="C265" s="160" t="s">
         <v>71</v>
       </c>
-      <c r="D265" s="155" t="s">
+      <c r="D265" s="160" t="s">
         <v>72</v>
       </c>
       <c r="E265" s="27" t="s">
@@ -26088,9 +26106,9 @@
       <c r="Z265" s="121"/>
     </row>
     <row r="266" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B266" s="156"/>
-      <c r="C266" s="156"/>
-      <c r="D266" s="156"/>
+      <c r="B266" s="161"/>
+      <c r="C266" s="161"/>
+      <c r="D266" s="161"/>
       <c r="E266" s="6" t="s">
         <v>13</v>
       </c>
@@ -26131,9 +26149,9 @@
       <c r="Z266" s="121"/>
     </row>
     <row r="267" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B267" s="156"/>
-      <c r="C267" s="156"/>
-      <c r="D267" s="156"/>
+      <c r="B267" s="161"/>
+      <c r="C267" s="161"/>
+      <c r="D267" s="161"/>
       <c r="E267" s="6" t="s">
         <v>103</v>
       </c>
@@ -26174,9 +26192,9 @@
       <c r="Z267" s="121"/>
     </row>
     <row r="268" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B268" s="156"/>
-      <c r="C268" s="156"/>
-      <c r="D268" s="156"/>
+      <c r="B268" s="161"/>
+      <c r="C268" s="161"/>
+      <c r="D268" s="161"/>
       <c r="E268" s="6" t="s">
         <v>290</v>
       </c>
@@ -26217,9 +26235,9 @@
       <c r="Z268" s="121"/>
     </row>
     <row r="269" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B269" s="156"/>
-      <c r="C269" s="156"/>
-      <c r="D269" s="156"/>
+      <c r="B269" s="161"/>
+      <c r="C269" s="161"/>
+      <c r="D269" s="161"/>
       <c r="E269" s="6" t="s">
         <v>106</v>
       </c>
@@ -26260,9 +26278,9 @@
       <c r="Z269" s="121"/>
     </row>
     <row r="270" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B270" s="156"/>
-      <c r="C270" s="156"/>
-      <c r="D270" s="156"/>
+      <c r="B270" s="161"/>
+      <c r="C270" s="161"/>
+      <c r="D270" s="161"/>
       <c r="E270" s="6" t="s">
         <v>109</v>
       </c>
@@ -26305,11 +26323,11 @@
       <c r="Z270" s="121"/>
     </row>
     <row r="271" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B271" s="156"/>
-      <c r="C271" s="156"/>
-      <c r="D271" s="156"/>
+      <c r="B271" s="161"/>
+      <c r="C271" s="161"/>
+      <c r="D271" s="161"/>
       <c r="E271" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F271" s="32" t="s">
         <v>21</v>
@@ -26348,11 +26366,11 @@
       <c r="Z271" s="121"/>
     </row>
     <row r="272" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B272" s="156"/>
-      <c r="C272" s="156"/>
-      <c r="D272" s="156"/>
+      <c r="B272" s="161"/>
+      <c r="C272" s="161"/>
+      <c r="D272" s="161"/>
       <c r="E272" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F272" s="32" t="s">
         <v>21</v>
@@ -26391,9 +26409,9 @@
       <c r="Z272" s="121"/>
     </row>
     <row r="273" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B273" s="156"/>
-      <c r="C273" s="156"/>
-      <c r="D273" s="156"/>
+      <c r="B273" s="161"/>
+      <c r="C273" s="161"/>
+      <c r="D273" s="161"/>
       <c r="E273" s="6" t="s">
         <v>110</v>
       </c>
@@ -26434,9 +26452,9 @@
       <c r="Z273" s="121"/>
     </row>
     <row r="274" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B274" s="157"/>
-      <c r="C274" s="157"/>
-      <c r="D274" s="157"/>
+      <c r="B274" s="162"/>
+      <c r="C274" s="162"/>
+      <c r="D274" s="162"/>
       <c r="E274" s="7" t="s">
         <v>14</v>
       </c>
@@ -26480,13 +26498,13 @@
       <c r="A275" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B275" s="158">
+      <c r="B275" s="163">
         <v>45</v>
       </c>
-      <c r="C275" s="158" t="s">
+      <c r="C275" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="D275" s="158" t="s">
+      <c r="D275" s="163" t="s">
         <v>72</v>
       </c>
       <c r="E275" s="26" t="s">
@@ -26527,9 +26545,9 @@
       <c r="Z275" s="121"/>
     </row>
     <row r="276" spans="1:26" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B276" s="159"/>
-      <c r="C276" s="159"/>
-      <c r="D276" s="159"/>
+      <c r="B276" s="164"/>
+      <c r="C276" s="164"/>
+      <c r="D276" s="164"/>
       <c r="E276" s="3" t="s">
         <v>190</v>
       </c>
@@ -26573,9 +26591,9 @@
       <c r="Z276" s="121"/>
     </row>
     <row r="277" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B277" s="159"/>
-      <c r="C277" s="159"/>
-      <c r="D277" s="159"/>
+      <c r="B277" s="164"/>
+      <c r="C277" s="164"/>
+      <c r="D277" s="164"/>
       <c r="E277" s="3" t="s">
         <v>13</v>
       </c>
@@ -26616,9 +26634,9 @@
       <c r="Z277" s="121"/>
     </row>
     <row r="278" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B278" s="159"/>
-      <c r="C278" s="159"/>
-      <c r="D278" s="159"/>
+      <c r="B278" s="164"/>
+      <c r="C278" s="164"/>
+      <c r="D278" s="164"/>
       <c r="E278" s="3" t="s">
         <v>110</v>
       </c>
@@ -26659,9 +26677,9 @@
       <c r="Z278" s="121"/>
     </row>
     <row r="279" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B279" s="159"/>
-      <c r="C279" s="159"/>
-      <c r="D279" s="159"/>
+      <c r="B279" s="164"/>
+      <c r="C279" s="164"/>
+      <c r="D279" s="164"/>
       <c r="E279" s="3" t="s">
         <v>109</v>
       </c>
@@ -26702,11 +26720,11 @@
       <c r="Z279" s="121"/>
     </row>
     <row r="280" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B280" s="159"/>
-      <c r="C280" s="159"/>
-      <c r="D280" s="159"/>
+      <c r="B280" s="164"/>
+      <c r="C280" s="164"/>
+      <c r="D280" s="164"/>
       <c r="E280" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F280" s="31" t="s">
         <v>21</v>
@@ -26745,9 +26763,9 @@
       <c r="Z280" s="121"/>
     </row>
     <row r="281" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B281" s="159"/>
-      <c r="C281" s="159"/>
-      <c r="D281" s="159"/>
+      <c r="B281" s="164"/>
+      <c r="C281" s="164"/>
+      <c r="D281" s="164"/>
       <c r="E281" s="3" t="s">
         <v>106</v>
       </c>
@@ -26788,9 +26806,9 @@
       <c r="Z281" s="121"/>
     </row>
     <row r="282" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B282" s="160"/>
-      <c r="C282" s="160"/>
-      <c r="D282" s="160"/>
+      <c r="B282" s="165"/>
+      <c r="C282" s="165"/>
+      <c r="D282" s="165"/>
       <c r="E282" s="4" t="s">
         <v>14</v>
       </c>
@@ -26834,13 +26852,13 @@
       <c r="A283" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B283" s="155">
+      <c r="B283" s="160">
         <v>46</v>
       </c>
-      <c r="C283" s="155" t="s">
+      <c r="C283" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="D283" s="155" t="s">
+      <c r="D283" s="160" t="s">
         <v>72</v>
       </c>
       <c r="E283" s="27" t="s">
@@ -26881,9 +26899,9 @@
       <c r="Z283" s="121"/>
     </row>
     <row r="284" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B284" s="156"/>
-      <c r="C284" s="156"/>
-      <c r="D284" s="156"/>
+      <c r="B284" s="161"/>
+      <c r="C284" s="161"/>
+      <c r="D284" s="161"/>
       <c r="E284" s="6" t="s">
         <v>13</v>
       </c>
@@ -26926,9 +26944,9 @@
       <c r="Z284" s="121"/>
     </row>
     <row r="285" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B285" s="156"/>
-      <c r="C285" s="156"/>
-      <c r="D285" s="156"/>
+      <c r="B285" s="161"/>
+      <c r="C285" s="161"/>
+      <c r="D285" s="161"/>
       <c r="E285" s="6" t="s">
         <v>110</v>
       </c>
@@ -26969,9 +26987,9 @@
       <c r="Z285" s="121"/>
     </row>
     <row r="286" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B286" s="156"/>
-      <c r="C286" s="156"/>
-      <c r="D286" s="156"/>
+      <c r="B286" s="161"/>
+      <c r="C286" s="161"/>
+      <c r="D286" s="161"/>
       <c r="E286" s="6" t="s">
         <v>109</v>
       </c>
@@ -27014,11 +27032,11 @@
       <c r="Z286" s="121"/>
     </row>
     <row r="287" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B287" s="156"/>
-      <c r="C287" s="156"/>
-      <c r="D287" s="156"/>
+      <c r="B287" s="161"/>
+      <c r="C287" s="161"/>
+      <c r="D287" s="161"/>
       <c r="E287" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F287" s="32" t="s">
         <v>21</v>
@@ -27057,9 +27075,9 @@
       <c r="Z287" s="121"/>
     </row>
     <row r="288" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B288" s="156"/>
-      <c r="C288" s="156"/>
-      <c r="D288" s="156"/>
+      <c r="B288" s="161"/>
+      <c r="C288" s="161"/>
+      <c r="D288" s="161"/>
       <c r="E288" s="6" t="s">
         <v>106</v>
       </c>
@@ -27102,14 +27120,14 @@
       <c r="Z288" s="121"/>
     </row>
     <row r="289" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B289" s="157"/>
-      <c r="C289" s="157"/>
-      <c r="D289" s="157"/>
+      <c r="B289" s="162"/>
+      <c r="C289" s="162"/>
+      <c r="D289" s="162"/>
       <c r="E289" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F289" s="32" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G289" s="37"/>
       <c r="H289" s="61" t="str">
@@ -27125,7 +27143,9 @@
         <v/>
       </c>
       <c r="K289" s="6"/>
-      <c r="L289" s="46"/>
+      <c r="L289" s="46" t="s">
+        <v>317</v>
+      </c>
       <c r="U289" s="119" t="str" cm="1">
         <f t="array" ref="U289">IF(C289="",INDEX(C282:C289,MATCH(TRUE,INDEX((C282:C289&lt;&gt;""),0),0)),C289)</f>
         <v>BOS Pool</v>
@@ -27148,13 +27168,13 @@
       <c r="A290" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B290" s="158">
+      <c r="B290" s="163">
         <v>47</v>
       </c>
-      <c r="C290" s="158" t="s">
+      <c r="C290" s="163" t="s">
         <v>75</v>
       </c>
-      <c r="D290" s="158" t="s">
+      <c r="D290" s="163" t="s">
         <v>76</v>
       </c>
       <c r="E290" s="26" t="s">
@@ -27195,9 +27215,9 @@
       <c r="Z290" s="121"/>
     </row>
     <row r="291" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B291" s="159"/>
-      <c r="C291" s="159"/>
-      <c r="D291" s="159"/>
+      <c r="B291" s="164"/>
+      <c r="C291" s="164"/>
+      <c r="D291" s="164"/>
       <c r="E291" s="3" t="s">
         <v>13</v>
       </c>
@@ -27238,9 +27258,9 @@
       <c r="Z291" s="121"/>
     </row>
     <row r="292" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B292" s="159"/>
-      <c r="C292" s="159"/>
-      <c r="D292" s="159"/>
+      <c r="B292" s="164"/>
+      <c r="C292" s="164"/>
+      <c r="D292" s="164"/>
       <c r="E292" s="3" t="s">
         <v>109</v>
       </c>
@@ -27281,9 +27301,9 @@
       <c r="Z292" s="121"/>
     </row>
     <row r="293" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B293" s="159"/>
-      <c r="C293" s="159"/>
-      <c r="D293" s="159"/>
+      <c r="B293" s="164"/>
+      <c r="C293" s="164"/>
+      <c r="D293" s="164"/>
       <c r="E293" s="3" t="s">
         <v>110</v>
       </c>
@@ -27324,9 +27344,9 @@
       <c r="Z293" s="121"/>
     </row>
     <row r="294" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B294" s="159"/>
-      <c r="C294" s="159"/>
-      <c r="D294" s="159"/>
+      <c r="B294" s="164"/>
+      <c r="C294" s="164"/>
+      <c r="D294" s="164"/>
       <c r="E294" s="3" t="s">
         <v>106</v>
       </c>
@@ -27367,14 +27387,14 @@
       <c r="Z294" s="121"/>
     </row>
     <row r="295" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B295" s="160"/>
-      <c r="C295" s="160"/>
-      <c r="D295" s="160"/>
+      <c r="B295" s="165"/>
+      <c r="C295" s="165"/>
+      <c r="D295" s="165"/>
       <c r="E295" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F295" s="31" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G295" s="39"/>
       <c r="H295" s="65" t="str">
@@ -27390,7 +27410,9 @@
         <v/>
       </c>
       <c r="K295" s="4"/>
-      <c r="L295" s="43"/>
+      <c r="L295" s="43" t="s">
+        <v>318</v>
+      </c>
       <c r="U295" s="119" t="str" cm="1">
         <f t="array" ref="U295">IF(C295="",INDEX(C289:C295,MATCH(TRUE,INDEX((C289:C295&lt;&gt;""),0),0)),C295)</f>
         <v>BOS Base</v>
@@ -27413,13 +27435,13 @@
       <c r="A296" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B296" s="155">
+      <c r="B296" s="160">
         <v>48</v>
       </c>
-      <c r="C296" s="155" t="s">
+      <c r="C296" s="160" t="s">
         <v>77</v>
       </c>
-      <c r="D296" s="155" t="s">
+      <c r="D296" s="160" t="s">
         <v>72</v>
       </c>
       <c r="E296" s="27" t="s">
@@ -27460,9 +27482,9 @@
       <c r="Z296" s="121"/>
     </row>
     <row r="297" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B297" s="156"/>
-      <c r="C297" s="156"/>
-      <c r="D297" s="156"/>
+      <c r="B297" s="161"/>
+      <c r="C297" s="161"/>
+      <c r="D297" s="161"/>
       <c r="E297" s="6" t="s">
         <v>13</v>
       </c>
@@ -27505,9 +27527,9 @@
       <c r="Z297" s="121"/>
     </row>
     <row r="298" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B298" s="156"/>
-      <c r="C298" s="156"/>
-      <c r="D298" s="156"/>
+      <c r="B298" s="161"/>
+      <c r="C298" s="161"/>
+      <c r="D298" s="161"/>
       <c r="E298" s="6" t="s">
         <v>110</v>
       </c>
@@ -27548,9 +27570,9 @@
       <c r="Z298" s="121"/>
     </row>
     <row r="299" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B299" s="156"/>
-      <c r="C299" s="156"/>
-      <c r="D299" s="156"/>
+      <c r="B299" s="161"/>
+      <c r="C299" s="161"/>
+      <c r="D299" s="161"/>
       <c r="E299" s="6" t="s">
         <v>109</v>
       </c>
@@ -27595,11 +27617,11 @@
       <c r="Z299" s="121"/>
     </row>
     <row r="300" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B300" s="156"/>
-      <c r="C300" s="156"/>
-      <c r="D300" s="156"/>
+      <c r="B300" s="161"/>
+      <c r="C300" s="161"/>
+      <c r="D300" s="161"/>
       <c r="E300" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F300" s="32" t="s">
         <v>21</v>
@@ -27638,9 +27660,9 @@
       <c r="Z300" s="121"/>
     </row>
     <row r="301" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B301" s="156"/>
-      <c r="C301" s="156"/>
-      <c r="D301" s="156"/>
+      <c r="B301" s="161"/>
+      <c r="C301" s="161"/>
+      <c r="D301" s="161"/>
       <c r="E301" s="6" t="s">
         <v>106</v>
       </c>
@@ -27685,14 +27707,14 @@
       <c r="Z301" s="121"/>
     </row>
     <row r="302" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B302" s="157"/>
-      <c r="C302" s="157"/>
-      <c r="D302" s="157"/>
+      <c r="B302" s="162"/>
+      <c r="C302" s="162"/>
+      <c r="D302" s="162"/>
       <c r="E302" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F302" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G302" s="37"/>
       <c r="H302" s="61" t="str">
@@ -27731,13 +27753,13 @@
       <c r="A303" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B303" s="158">
+      <c r="B303" s="163">
         <v>49</v>
       </c>
-      <c r="C303" s="158" t="s">
+      <c r="C303" s="163" t="s">
         <v>78</v>
       </c>
-      <c r="D303" s="158" t="s">
+      <c r="D303" s="163" t="s">
         <v>72</v>
       </c>
       <c r="E303" s="26" t="s">
@@ -27778,9 +27800,9 @@
       <c r="Z303" s="121"/>
     </row>
     <row r="304" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B304" s="159"/>
-      <c r="C304" s="159"/>
-      <c r="D304" s="159"/>
+      <c r="B304" s="164"/>
+      <c r="C304" s="164"/>
+      <c r="D304" s="164"/>
       <c r="E304" s="3" t="s">
         <v>13</v>
       </c>
@@ -27823,9 +27845,9 @@
       <c r="Z304" s="121"/>
     </row>
     <row r="305" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B305" s="159"/>
-      <c r="C305" s="159"/>
-      <c r="D305" s="159"/>
+      <c r="B305" s="164"/>
+      <c r="C305" s="164"/>
+      <c r="D305" s="164"/>
       <c r="E305" s="3" t="s">
         <v>110</v>
       </c>
@@ -27866,9 +27888,9 @@
       <c r="Z305" s="121"/>
     </row>
     <row r="306" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B306" s="159"/>
-      <c r="C306" s="159"/>
-      <c r="D306" s="159"/>
+      <c r="B306" s="164"/>
+      <c r="C306" s="164"/>
+      <c r="D306" s="164"/>
       <c r="E306" s="3" t="s">
         <v>109</v>
       </c>
@@ -27909,11 +27931,11 @@
       <c r="Z306" s="121"/>
     </row>
     <row r="307" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B307" s="159"/>
-      <c r="C307" s="159"/>
-      <c r="D307" s="159"/>
+      <c r="B307" s="164"/>
+      <c r="C307" s="164"/>
+      <c r="D307" s="164"/>
       <c r="E307" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F307" s="31" t="s">
         <v>21</v>
@@ -27952,9 +27974,9 @@
       <c r="Z307" s="121"/>
     </row>
     <row r="308" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B308" s="159"/>
-      <c r="C308" s="159"/>
-      <c r="D308" s="159"/>
+      <c r="B308" s="164"/>
+      <c r="C308" s="164"/>
+      <c r="D308" s="164"/>
       <c r="E308" s="3" t="s">
         <v>106</v>
       </c>
@@ -27997,14 +28019,14 @@
       <c r="Z308" s="121"/>
     </row>
     <row r="309" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B309" s="160"/>
-      <c r="C309" s="160"/>
-      <c r="D309" s="160"/>
+      <c r="B309" s="165"/>
+      <c r="C309" s="165"/>
+      <c r="D309" s="165"/>
       <c r="E309" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F309" s="31" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G309" s="39"/>
       <c r="H309" s="65" t="str">
@@ -28043,13 +28065,13 @@
       <c r="A310" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B310" s="155">
+      <c r="B310" s="160">
         <v>50</v>
       </c>
-      <c r="C310" s="155" t="s">
+      <c r="C310" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="D310" s="155" t="s">
+      <c r="D310" s="160" t="s">
         <v>72</v>
       </c>
       <c r="E310" s="27" t="s">
@@ -28090,9 +28112,9 @@
       <c r="Z310" s="121"/>
     </row>
     <row r="311" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B311" s="156"/>
-      <c r="C311" s="156"/>
-      <c r="D311" s="156"/>
+      <c r="B311" s="161"/>
+      <c r="C311" s="161"/>
+      <c r="D311" s="161"/>
       <c r="E311" s="6" t="s">
         <v>13</v>
       </c>
@@ -28133,9 +28155,9 @@
       <c r="Z311" s="121"/>
     </row>
     <row r="312" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B312" s="156"/>
-      <c r="C312" s="156"/>
-      <c r="D312" s="156"/>
+      <c r="B312" s="161"/>
+      <c r="C312" s="161"/>
+      <c r="D312" s="161"/>
       <c r="E312" s="6" t="s">
         <v>110</v>
       </c>
@@ -28176,9 +28198,9 @@
       <c r="Z312" s="121"/>
     </row>
     <row r="313" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B313" s="156"/>
-      <c r="C313" s="156"/>
-      <c r="D313" s="156"/>
+      <c r="B313" s="161"/>
+      <c r="C313" s="161"/>
+      <c r="D313" s="161"/>
       <c r="E313" s="6" t="s">
         <v>109</v>
       </c>
@@ -28221,11 +28243,11 @@
       <c r="Z313" s="121"/>
     </row>
     <row r="314" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B314" s="156"/>
-      <c r="C314" s="156"/>
-      <c r="D314" s="156"/>
+      <c r="B314" s="161"/>
+      <c r="C314" s="161"/>
+      <c r="D314" s="161"/>
       <c r="E314" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F314" s="32" t="s">
         <v>21</v>
@@ -28264,9 +28286,9 @@
       <c r="Z314" s="121"/>
     </row>
     <row r="315" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B315" s="156"/>
-      <c r="C315" s="156"/>
-      <c r="D315" s="156"/>
+      <c r="B315" s="161"/>
+      <c r="C315" s="161"/>
+      <c r="D315" s="161"/>
       <c r="E315" s="6" t="s">
         <v>106</v>
       </c>
@@ -28307,14 +28329,14 @@
       <c r="Z315" s="121"/>
     </row>
     <row r="316" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B316" s="157"/>
-      <c r="C316" s="157"/>
-      <c r="D316" s="157"/>
+      <c r="B316" s="162"/>
+      <c r="C316" s="162"/>
+      <c r="D316" s="162"/>
       <c r="E316" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F316" s="32" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G316" s="37"/>
       <c r="H316" s="61" t="str">
@@ -28353,13 +28375,13 @@
       <c r="A317" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B317" s="158">
+      <c r="B317" s="163">
         <v>51</v>
       </c>
-      <c r="C317" s="158" t="s">
+      <c r="C317" s="163" t="s">
         <v>80</v>
       </c>
-      <c r="D317" s="158" t="s">
+      <c r="D317" s="163" t="s">
         <v>72</v>
       </c>
       <c r="E317" s="26" t="s">
@@ -28400,9 +28422,9 @@
       <c r="Z317" s="121"/>
     </row>
     <row r="318" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B318" s="159"/>
-      <c r="C318" s="159"/>
-      <c r="D318" s="159"/>
+      <c r="B318" s="164"/>
+      <c r="C318" s="164"/>
+      <c r="D318" s="164"/>
       <c r="E318" s="3" t="s">
         <v>13</v>
       </c>
@@ -28443,9 +28465,9 @@
       <c r="Z318" s="121"/>
     </row>
     <row r="319" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B319" s="159"/>
-      <c r="C319" s="159"/>
-      <c r="D319" s="159"/>
+      <c r="B319" s="164"/>
+      <c r="C319" s="164"/>
+      <c r="D319" s="164"/>
       <c r="E319" s="3" t="s">
         <v>110</v>
       </c>
@@ -28486,9 +28508,9 @@
       <c r="Z319" s="121"/>
     </row>
     <row r="320" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B320" s="159"/>
-      <c r="C320" s="159"/>
-      <c r="D320" s="159"/>
+      <c r="B320" s="164"/>
+      <c r="C320" s="164"/>
+      <c r="D320" s="164"/>
       <c r="E320" s="3" t="s">
         <v>109</v>
       </c>
@@ -28531,9 +28553,9 @@
       <c r="Z320" s="121"/>
     </row>
     <row r="321" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B321" s="159"/>
-      <c r="C321" s="159"/>
-      <c r="D321" s="159"/>
+      <c r="B321" s="164"/>
+      <c r="C321" s="164"/>
+      <c r="D321" s="164"/>
       <c r="E321" s="3" t="s">
         <v>299</v>
       </c>
@@ -28574,9 +28596,9 @@
       <c r="Z321" s="121"/>
     </row>
     <row r="322" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B322" s="159"/>
-      <c r="C322" s="159"/>
-      <c r="D322" s="159"/>
+      <c r="B322" s="164"/>
+      <c r="C322" s="164"/>
+      <c r="D322" s="164"/>
       <c r="E322" s="3" t="s">
         <v>106</v>
       </c>
@@ -28617,14 +28639,14 @@
       <c r="Z322" s="121"/>
     </row>
     <row r="323" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B323" s="160"/>
-      <c r="C323" s="160"/>
-      <c r="D323" s="160"/>
+      <c r="B323" s="165"/>
+      <c r="C323" s="165"/>
+      <c r="D323" s="165"/>
       <c r="E323" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F323" s="31" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G323" s="39"/>
       <c r="H323" s="65" t="str">
@@ -28663,13 +28685,13 @@
       <c r="A324" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B324" s="155">
+      <c r="B324" s="160">
         <v>52</v>
       </c>
-      <c r="C324" s="155" t="s">
+      <c r="C324" s="160" t="s">
         <v>81</v>
       </c>
-      <c r="D324" s="155" t="s">
+      <c r="D324" s="160" t="s">
         <v>72</v>
       </c>
       <c r="E324" s="27" t="s">
@@ -28710,9 +28732,9 @@
       <c r="Z324" s="121"/>
     </row>
     <row r="325" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B325" s="156"/>
-      <c r="C325" s="156"/>
-      <c r="D325" s="156"/>
+      <c r="B325" s="161"/>
+      <c r="C325" s="161"/>
+      <c r="D325" s="161"/>
       <c r="E325" s="6" t="s">
         <v>13</v>
       </c>
@@ -28753,9 +28775,9 @@
       <c r="Z325" s="121"/>
     </row>
     <row r="326" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B326" s="156"/>
-      <c r="C326" s="156"/>
-      <c r="D326" s="156"/>
+      <c r="B326" s="161"/>
+      <c r="C326" s="161"/>
+      <c r="D326" s="161"/>
       <c r="E326" s="6" t="s">
         <v>110</v>
       </c>
@@ -28796,9 +28818,9 @@
       <c r="Z326" s="121"/>
     </row>
     <row r="327" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B327" s="156"/>
-      <c r="C327" s="156"/>
-      <c r="D327" s="156"/>
+      <c r="B327" s="161"/>
+      <c r="C327" s="161"/>
+      <c r="D327" s="161"/>
       <c r="E327" s="6" t="s">
         <v>290</v>
       </c>
@@ -28839,9 +28861,9 @@
       <c r="Z327" s="121"/>
     </row>
     <row r="328" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B328" s="156"/>
-      <c r="C328" s="156"/>
-      <c r="D328" s="156"/>
+      <c r="B328" s="161"/>
+      <c r="C328" s="161"/>
+      <c r="D328" s="161"/>
       <c r="E328" s="6" t="s">
         <v>109</v>
       </c>
@@ -28884,14 +28906,14 @@
       <c r="Z328" s="121"/>
     </row>
     <row r="329" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B329" s="156"/>
-      <c r="C329" s="156"/>
-      <c r="D329" s="156"/>
+      <c r="B329" s="161"/>
+      <c r="C329" s="161"/>
+      <c r="D329" s="161"/>
       <c r="E329" s="6" t="s">
         <v>299</v>
       </c>
       <c r="F329" s="32" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G329" s="37"/>
       <c r="H329" s="61" t="str">
@@ -28927,9 +28949,9 @@
       <c r="Z329" s="121"/>
     </row>
     <row r="330" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B330" s="156"/>
-      <c r="C330" s="156"/>
-      <c r="D330" s="156"/>
+      <c r="B330" s="161"/>
+      <c r="C330" s="161"/>
+      <c r="D330" s="161"/>
       <c r="E330" s="6" t="s">
         <v>106</v>
       </c>
@@ -28970,9 +28992,9 @@
       <c r="Z330" s="121"/>
     </row>
     <row r="331" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B331" s="157"/>
-      <c r="C331" s="157"/>
-      <c r="D331" s="157"/>
+      <c r="B331" s="162"/>
+      <c r="C331" s="162"/>
+      <c r="D331" s="162"/>
       <c r="E331" s="7" t="s">
         <v>14</v>
       </c>
@@ -29016,13 +29038,13 @@
       <c r="A332" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B332" s="158">
+      <c r="B332" s="163">
         <v>53</v>
       </c>
-      <c r="C332" s="158" t="s">
+      <c r="C332" s="163" t="s">
         <v>82</v>
       </c>
-      <c r="D332" s="158" t="s">
+      <c r="D332" s="163" t="s">
         <v>72</v>
       </c>
       <c r="E332" s="26" t="s">
@@ -29042,7 +29064,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K332" s="158" t="s">
+      <c r="K332" s="163" t="s">
         <v>140</v>
       </c>
       <c r="L332" s="41"/>
@@ -29065,9 +29087,9 @@
       <c r="Z332" s="121"/>
     </row>
     <row r="333" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B333" s="159"/>
-      <c r="C333" s="159"/>
-      <c r="D333" s="159"/>
+      <c r="B333" s="164"/>
+      <c r="C333" s="164"/>
+      <c r="D333" s="164"/>
       <c r="E333" s="3" t="s">
         <v>13</v>
       </c>
@@ -29087,7 +29109,7 @@
         <f t="shared" si="61"/>
         <v>64</v>
       </c>
-      <c r="K333" s="159"/>
+      <c r="K333" s="164"/>
       <c r="L333" s="42"/>
       <c r="U333" s="119" t="str" cm="1">
         <f t="array" ref="U333">IF(C333="",INDEX(C325:C333,MATCH(TRUE,INDEX((C325:C333&lt;&gt;""),0),0)),C333)</f>
@@ -29108,9 +29130,9 @@
       <c r="Z333" s="121"/>
     </row>
     <row r="334" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B334" s="159"/>
-      <c r="C334" s="159"/>
-      <c r="D334" s="159"/>
+      <c r="B334" s="164"/>
+      <c r="C334" s="164"/>
+      <c r="D334" s="164"/>
       <c r="E334" s="3" t="s">
         <v>110</v>
       </c>
@@ -29130,7 +29152,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K334" s="159"/>
+      <c r="K334" s="164"/>
       <c r="L334" s="42"/>
       <c r="U334" s="119" t="str" cm="1">
         <f t="array" ref="U334">IF(C334="",INDEX(C326:C334,MATCH(TRUE,INDEX((C326:C334&lt;&gt;""),0),0)),C334)</f>
@@ -29151,9 +29173,9 @@
       <c r="Z334" s="121"/>
     </row>
     <row r="335" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B335" s="159"/>
-      <c r="C335" s="159"/>
-      <c r="D335" s="159"/>
+      <c r="B335" s="164"/>
+      <c r="C335" s="164"/>
+      <c r="D335" s="164"/>
       <c r="E335" s="3" t="s">
         <v>290</v>
       </c>
@@ -29173,7 +29195,7 @@
         <f t="shared" si="61"/>
         <v>14</v>
       </c>
-      <c r="K335" s="159"/>
+      <c r="K335" s="164"/>
       <c r="L335" s="42"/>
       <c r="U335" s="119" t="str" cm="1">
         <f t="array" ref="U335">IF(C335="",INDEX(C327:C335,MATCH(TRUE,INDEX((C327:C335&lt;&gt;""),0),0)),C335)</f>
@@ -29194,9 +29216,9 @@
       <c r="Z335" s="121"/>
     </row>
     <row r="336" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B336" s="159"/>
-      <c r="C336" s="159"/>
-      <c r="D336" s="159"/>
+      <c r="B336" s="164"/>
+      <c r="C336" s="164"/>
+      <c r="D336" s="164"/>
       <c r="E336" s="3" t="s">
         <v>109</v>
       </c>
@@ -29216,7 +29238,7 @@
         <f t="shared" si="61"/>
         <v>93</v>
       </c>
-      <c r="K336" s="159"/>
+      <c r="K336" s="164"/>
       <c r="L336" s="42" t="s">
         <v>138</v>
       </c>
@@ -29239,9 +29261,9 @@
       <c r="Z336" s="121"/>
     </row>
     <row r="337" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B337" s="159"/>
-      <c r="C337" s="159"/>
-      <c r="D337" s="159"/>
+      <c r="B337" s="164"/>
+      <c r="C337" s="164"/>
+      <c r="D337" s="164"/>
       <c r="E337" s="3" t="s">
         <v>106</v>
       </c>
@@ -29261,7 +29283,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K337" s="159"/>
+      <c r="K337" s="164"/>
       <c r="L337" s="42"/>
       <c r="U337" s="119" t="str" cm="1">
         <f t="array" ref="U337">IF(C337="",INDEX(C330:C337,MATCH(TRUE,INDEX((C330:C337&lt;&gt;""),0),0)),C337)</f>
@@ -29282,9 +29304,9 @@
       <c r="Z337" s="121"/>
     </row>
     <row r="338" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B338" s="160"/>
-      <c r="C338" s="160"/>
-      <c r="D338" s="160"/>
+      <c r="B338" s="165"/>
+      <c r="C338" s="165"/>
+      <c r="D338" s="165"/>
       <c r="E338" s="4" t="s">
         <v>14</v>
       </c>
@@ -29304,7 +29326,7 @@
         <f t="shared" si="61"/>
         <v>8</v>
       </c>
-      <c r="K338" s="160"/>
+      <c r="K338" s="165"/>
       <c r="L338" s="43"/>
       <c r="U338" s="119" t="str" cm="1">
         <f t="array" ref="U338">IF(C338="",INDEX(C331:C338,MATCH(TRUE,INDEX((C331:C338&lt;&gt;""),0),0)),C338)</f>
@@ -29328,13 +29350,13 @@
       <c r="A339" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B339" s="155">
+      <c r="B339" s="160">
         <v>54</v>
       </c>
-      <c r="C339" s="155" t="s">
+      <c r="C339" s="160" t="s">
         <v>83</v>
       </c>
-      <c r="D339" s="155" t="s">
+      <c r="D339" s="160" t="s">
         <v>72</v>
       </c>
       <c r="E339" s="27" t="s">
@@ -29354,7 +29376,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K339" s="155" t="s">
+      <c r="K339" s="160" t="s">
         <v>173</v>
       </c>
       <c r="L339" s="44"/>
@@ -29377,9 +29399,9 @@
       <c r="Z339" s="121"/>
     </row>
     <row r="340" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B340" s="156"/>
-      <c r="C340" s="156"/>
-      <c r="D340" s="156"/>
+      <c r="B340" s="161"/>
+      <c r="C340" s="161"/>
+      <c r="D340" s="161"/>
       <c r="E340" s="6" t="s">
         <v>13</v>
       </c>
@@ -29399,7 +29421,7 @@
         <f t="shared" si="61"/>
         <v>64</v>
       </c>
-      <c r="K340" s="156"/>
+      <c r="K340" s="161"/>
       <c r="L340" s="45"/>
       <c r="U340" s="119" t="str" cm="1">
         <f t="array" ref="U340">IF(C340="",INDEX(C333:C340,MATCH(TRUE,INDEX((C333:C340&lt;&gt;""),0),0)),C340)</f>
@@ -29420,9 +29442,9 @@
       <c r="Z340" s="121"/>
     </row>
     <row r="341" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B341" s="156"/>
-      <c r="C341" s="156"/>
-      <c r="D341" s="156"/>
+      <c r="B341" s="161"/>
+      <c r="C341" s="161"/>
+      <c r="D341" s="161"/>
       <c r="E341" s="6" t="s">
         <v>110</v>
       </c>
@@ -29442,7 +29464,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K341" s="156"/>
+      <c r="K341" s="161"/>
       <c r="L341" s="45"/>
       <c r="U341" s="119" t="str" cm="1">
         <f t="array" ref="U341">IF(C341="",INDEX(C334:C341,MATCH(TRUE,INDEX((C334:C341&lt;&gt;""),0),0)),C341)</f>
@@ -29463,9 +29485,9 @@
       <c r="Z341" s="121"/>
     </row>
     <row r="342" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B342" s="156"/>
-      <c r="C342" s="156"/>
-      <c r="D342" s="156"/>
+      <c r="B342" s="161"/>
+      <c r="C342" s="161"/>
+      <c r="D342" s="161"/>
       <c r="E342" s="6" t="s">
         <v>109</v>
       </c>
@@ -29485,7 +29507,7 @@
         <f t="shared" si="61"/>
         <v>93</v>
       </c>
-      <c r="K342" s="156"/>
+      <c r="K342" s="161"/>
       <c r="L342" s="45" t="s">
         <v>289</v>
       </c>
@@ -29508,11 +29530,11 @@
       <c r="Z342" s="121"/>
     </row>
     <row r="343" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B343" s="156"/>
-      <c r="C343" s="156"/>
-      <c r="D343" s="156"/>
+      <c r="B343" s="161"/>
+      <c r="C343" s="161"/>
+      <c r="D343" s="161"/>
       <c r="E343" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F343" s="32" t="s">
         <v>21</v>
@@ -29530,7 +29552,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K343" s="156"/>
+      <c r="K343" s="161"/>
       <c r="L343" s="45"/>
       <c r="U343" s="119" t="str" cm="1">
         <f t="array" ref="U343">IF(C343="",INDEX(C337:C343,MATCH(TRUE,INDEX((C337:C343&lt;&gt;""),0),0)),C343)</f>
@@ -29551,14 +29573,14 @@
       <c r="Z343" s="121"/>
     </row>
     <row r="344" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B344" s="156"/>
-      <c r="C344" s="156"/>
-      <c r="D344" s="156"/>
+      <c r="B344" s="161"/>
+      <c r="C344" s="161"/>
+      <c r="D344" s="161"/>
       <c r="E344" s="6" t="s">
         <v>299</v>
       </c>
       <c r="F344" s="32" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="G344" s="37"/>
       <c r="H344" s="61" t="str">
@@ -29573,7 +29595,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K344" s="156"/>
+      <c r="K344" s="161"/>
       <c r="L344" s="45"/>
       <c r="U344" s="119" t="str" cm="1">
         <f t="array" ref="U344">IF(C344="",INDEX(C338:C344,MATCH(TRUE,INDEX((C338:C344&lt;&gt;""),0),0)),C344)</f>
@@ -29594,9 +29616,9 @@
       <c r="Z344" s="121"/>
     </row>
     <row r="345" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B345" s="156"/>
-      <c r="C345" s="156"/>
-      <c r="D345" s="156"/>
+      <c r="B345" s="161"/>
+      <c r="C345" s="161"/>
+      <c r="D345" s="161"/>
       <c r="E345" s="6" t="s">
         <v>106</v>
       </c>
@@ -29616,7 +29638,7 @@
         <f t="shared" si="61"/>
         <v/>
       </c>
-      <c r="K345" s="156"/>
+      <c r="K345" s="161"/>
       <c r="L345" s="45"/>
       <c r="U345" s="119" t="str" cm="1">
         <f t="array" ref="U345">IF(C345="",INDEX(C337:C345,MATCH(TRUE,INDEX((C337:C345&lt;&gt;""),0),0)),C345)</f>
@@ -29637,9 +29659,9 @@
       <c r="Z345" s="121"/>
     </row>
     <row r="346" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B346" s="157"/>
-      <c r="C346" s="157"/>
-      <c r="D346" s="157"/>
+      <c r="B346" s="162"/>
+      <c r="C346" s="162"/>
+      <c r="D346" s="162"/>
       <c r="E346" s="7" t="s">
         <v>14</v>
       </c>
@@ -29661,7 +29683,7 @@
         <f t="shared" si="61"/>
         <v>8</v>
       </c>
-      <c r="K346" s="157"/>
+      <c r="K346" s="162"/>
       <c r="L346" s="46"/>
       <c r="U346" s="119" t="str" cm="1">
         <f t="array" ref="U346">IF(C346="",INDEX(C338:C346,MATCH(TRUE,INDEX((C338:C346&lt;&gt;""),0),0)),C346)</f>
@@ -29685,13 +29707,13 @@
       <c r="A347" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B347" s="158">
+      <c r="B347" s="163">
         <v>55</v>
       </c>
-      <c r="C347" s="158" t="s">
+      <c r="C347" s="163" t="s">
         <v>84</v>
       </c>
-      <c r="D347" s="158" t="s">
+      <c r="D347" s="163" t="s">
         <v>72</v>
       </c>
       <c r="E347" s="26" t="s">
@@ -29732,9 +29754,9 @@
       <c r="Z347" s="121"/>
     </row>
     <row r="348" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B348" s="159"/>
-      <c r="C348" s="159"/>
-      <c r="D348" s="159"/>
+      <c r="B348" s="164"/>
+      <c r="C348" s="164"/>
+      <c r="D348" s="164"/>
       <c r="E348" s="3" t="s">
         <v>13</v>
       </c>
@@ -29777,9 +29799,9 @@
       <c r="Z348" s="121"/>
     </row>
     <row r="349" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B349" s="159"/>
-      <c r="C349" s="159"/>
-      <c r="D349" s="159"/>
+      <c r="B349" s="164"/>
+      <c r="C349" s="164"/>
+      <c r="D349" s="164"/>
       <c r="E349" s="3" t="s">
         <v>110</v>
       </c>
@@ -29820,9 +29842,9 @@
       <c r="Z349" s="121"/>
     </row>
     <row r="350" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B350" s="159"/>
-      <c r="C350" s="159"/>
-      <c r="D350" s="159"/>
+      <c r="B350" s="164"/>
+      <c r="C350" s="164"/>
+      <c r="D350" s="164"/>
       <c r="E350" s="3" t="s">
         <v>109</v>
       </c>
@@ -29865,9 +29887,9 @@
       <c r="Z350" s="121"/>
     </row>
     <row r="351" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B351" s="159"/>
-      <c r="C351" s="159"/>
-      <c r="D351" s="159"/>
+      <c r="B351" s="164"/>
+      <c r="C351" s="164"/>
+      <c r="D351" s="164"/>
       <c r="E351" s="3" t="s">
         <v>106</v>
       </c>
@@ -29908,9 +29930,9 @@
       <c r="Z351" s="121"/>
     </row>
     <row r="352" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B352" s="160"/>
-      <c r="C352" s="160"/>
-      <c r="D352" s="160"/>
+      <c r="B352" s="165"/>
+      <c r="C352" s="165"/>
+      <c r="D352" s="165"/>
       <c r="E352" s="4" t="s">
         <v>14</v>
       </c>
@@ -29958,13 +29980,13 @@
       <c r="A353" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B353" s="155">
+      <c r="B353" s="160">
         <v>56</v>
       </c>
-      <c r="C353" s="155" t="s">
+      <c r="C353" s="160" t="s">
         <v>85</v>
       </c>
-      <c r="D353" s="155" t="s">
+      <c r="D353" s="160" t="s">
         <v>72</v>
       </c>
       <c r="E353" s="27" t="s">
@@ -30005,9 +30027,9 @@
       <c r="Z353" s="121"/>
     </row>
     <row r="354" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B354" s="156"/>
-      <c r="C354" s="156"/>
-      <c r="D354" s="156"/>
+      <c r="B354" s="161"/>
+      <c r="C354" s="161"/>
+      <c r="D354" s="161"/>
       <c r="E354" s="6" t="s">
         <v>13</v>
       </c>
@@ -30048,9 +30070,9 @@
       <c r="Z354" s="121"/>
     </row>
     <row r="355" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B355" s="156"/>
-      <c r="C355" s="156"/>
-      <c r="D355" s="156"/>
+      <c r="B355" s="161"/>
+      <c r="C355" s="161"/>
+      <c r="D355" s="161"/>
       <c r="E355" s="6" t="s">
         <v>110</v>
       </c>
@@ -30091,9 +30113,9 @@
       <c r="Z355" s="121"/>
     </row>
     <row r="356" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B356" s="156"/>
-      <c r="C356" s="156"/>
-      <c r="D356" s="156"/>
+      <c r="B356" s="161"/>
+      <c r="C356" s="161"/>
+      <c r="D356" s="161"/>
       <c r="E356" s="6" t="s">
         <v>109</v>
       </c>
@@ -30136,11 +30158,11 @@
       <c r="Z356" s="121"/>
     </row>
     <row r="357" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B357" s="156"/>
-      <c r="C357" s="156"/>
-      <c r="D357" s="156"/>
+      <c r="B357" s="161"/>
+      <c r="C357" s="161"/>
+      <c r="D357" s="161"/>
       <c r="E357" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F357" s="32" t="s">
         <v>21</v>
@@ -30179,11 +30201,11 @@
       <c r="Z357" s="121"/>
     </row>
     <row r="358" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B358" s="156"/>
-      <c r="C358" s="156"/>
-      <c r="D358" s="156"/>
+      <c r="B358" s="161"/>
+      <c r="C358" s="161"/>
+      <c r="D358" s="161"/>
       <c r="E358" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F358" s="32" t="s">
         <v>105</v>
@@ -30222,9 +30244,9 @@
       <c r="Z358" s="121"/>
     </row>
     <row r="359" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B359" s="156"/>
-      <c r="C359" s="156"/>
-      <c r="D359" s="156"/>
+      <c r="B359" s="161"/>
+      <c r="C359" s="161"/>
+      <c r="D359" s="161"/>
       <c r="E359" s="6" t="s">
         <v>299</v>
       </c>
@@ -30265,9 +30287,9 @@
       <c r="Z359" s="121"/>
     </row>
     <row r="360" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B360" s="156"/>
-      <c r="C360" s="156"/>
-      <c r="D360" s="156"/>
+      <c r="B360" s="161"/>
+      <c r="C360" s="161"/>
+      <c r="D360" s="161"/>
       <c r="E360" s="6" t="s">
         <v>106</v>
       </c>
@@ -30310,9 +30332,9 @@
       <c r="Z360" s="121"/>
     </row>
     <row r="361" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B361" s="157"/>
-      <c r="C361" s="157"/>
-      <c r="D361" s="157"/>
+      <c r="B361" s="162"/>
+      <c r="C361" s="162"/>
+      <c r="D361" s="162"/>
       <c r="E361" s="7" t="s">
         <v>14</v>
       </c>
@@ -30358,13 +30380,13 @@
       <c r="A362" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B362" s="158">
+      <c r="B362" s="163">
         <v>57</v>
       </c>
-      <c r="C362" s="158" t="s">
+      <c r="C362" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="D362" s="158" t="s">
+      <c r="D362" s="163" t="s">
         <v>87</v>
       </c>
       <c r="E362" s="26" t="s">
@@ -30405,9 +30427,9 @@
       <c r="Z362" s="121"/>
     </row>
     <row r="363" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B363" s="159"/>
-      <c r="C363" s="159"/>
-      <c r="D363" s="159"/>
+      <c r="B363" s="164"/>
+      <c r="C363" s="164"/>
+      <c r="D363" s="164"/>
       <c r="E363" s="3" t="s">
         <v>13</v>
       </c>
@@ -30450,9 +30472,9 @@
       <c r="Z363" s="121"/>
     </row>
     <row r="364" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B364" s="159"/>
-      <c r="C364" s="159"/>
-      <c r="D364" s="159"/>
+      <c r="B364" s="164"/>
+      <c r="C364" s="164"/>
+      <c r="D364" s="164"/>
       <c r="E364" s="3" t="s">
         <v>110</v>
       </c>
@@ -30495,9 +30517,9 @@
       <c r="Z364" s="121"/>
     </row>
     <row r="365" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B365" s="159"/>
-      <c r="C365" s="159"/>
-      <c r="D365" s="159"/>
+      <c r="B365" s="164"/>
+      <c r="C365" s="164"/>
+      <c r="D365" s="164"/>
       <c r="E365" s="3" t="s">
         <v>109</v>
       </c>
@@ -30540,9 +30562,9 @@
       <c r="Z365" s="121"/>
     </row>
     <row r="366" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B366" s="159"/>
-      <c r="C366" s="159"/>
-      <c r="D366" s="159"/>
+      <c r="B366" s="164"/>
+      <c r="C366" s="164"/>
+      <c r="D366" s="164"/>
       <c r="E366" s="3" t="s">
         <v>290</v>
       </c>
@@ -30583,9 +30605,9 @@
       <c r="Z366" s="121"/>
     </row>
     <row r="367" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B367" s="159"/>
-      <c r="C367" s="159"/>
-      <c r="D367" s="159"/>
+      <c r="B367" s="164"/>
+      <c r="C367" s="164"/>
+      <c r="D367" s="164"/>
       <c r="E367" s="3" t="s">
         <v>106</v>
       </c>
@@ -30628,9 +30650,9 @@
       <c r="Z367" s="121"/>
     </row>
     <row r="368" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B368" s="160"/>
-      <c r="C368" s="160"/>
-      <c r="D368" s="160"/>
+      <c r="B368" s="165"/>
+      <c r="C368" s="165"/>
+      <c r="D368" s="165"/>
       <c r="E368" s="4" t="s">
         <v>14</v>
       </c>
@@ -30676,13 +30698,13 @@
       <c r="A369" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B369" s="155">
+      <c r="B369" s="160">
         <v>58</v>
       </c>
-      <c r="C369" s="155" t="s">
+      <c r="C369" s="160" t="s">
         <v>255</v>
       </c>
-      <c r="D369" s="155" t="s">
+      <c r="D369" s="160" t="s">
         <v>88</v>
       </c>
       <c r="E369" s="27" t="s">
@@ -30723,9 +30745,9 @@
       <c r="Z369" s="121"/>
     </row>
     <row r="370" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B370" s="156"/>
-      <c r="C370" s="156"/>
-      <c r="D370" s="156"/>
+      <c r="B370" s="161"/>
+      <c r="C370" s="161"/>
+      <c r="D370" s="161"/>
       <c r="E370" s="6" t="s">
         <v>13</v>
       </c>
@@ -30766,9 +30788,9 @@
       <c r="Z370" s="121"/>
     </row>
     <row r="371" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B371" s="156"/>
-      <c r="C371" s="156"/>
-      <c r="D371" s="156"/>
+      <c r="B371" s="161"/>
+      <c r="C371" s="161"/>
+      <c r="D371" s="161"/>
       <c r="E371" s="6" t="s">
         <v>110</v>
       </c>
@@ -30809,9 +30831,9 @@
       <c r="Z371" s="121"/>
     </row>
     <row r="372" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B372" s="156"/>
-      <c r="C372" s="156"/>
-      <c r="D372" s="156"/>
+      <c r="B372" s="161"/>
+      <c r="C372" s="161"/>
+      <c r="D372" s="161"/>
       <c r="E372" s="6" t="s">
         <v>290</v>
       </c>
@@ -30852,9 +30874,9 @@
       <c r="Z372" s="121"/>
     </row>
     <row r="373" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B373" s="156"/>
-      <c r="C373" s="156"/>
-      <c r="D373" s="156"/>
+      <c r="B373" s="161"/>
+      <c r="C373" s="161"/>
+      <c r="D373" s="161"/>
       <c r="E373" s="6" t="s">
         <v>109</v>
       </c>
@@ -30895,9 +30917,9 @@
       <c r="Z373" s="121"/>
     </row>
     <row r="374" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B374" s="156"/>
-      <c r="C374" s="156"/>
-      <c r="D374" s="156"/>
+      <c r="B374" s="161"/>
+      <c r="C374" s="161"/>
+      <c r="D374" s="161"/>
       <c r="E374" s="6" t="s">
         <v>106</v>
       </c>
@@ -30938,9 +30960,9 @@
       <c r="Z374" s="121"/>
     </row>
     <row r="375" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B375" s="157"/>
-      <c r="C375" s="157"/>
-      <c r="D375" s="157"/>
+      <c r="B375" s="162"/>
+      <c r="C375" s="162"/>
+      <c r="D375" s="162"/>
       <c r="E375" s="7" t="s">
         <v>14</v>
       </c>
@@ -30984,13 +31006,13 @@
       <c r="A376" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B376" s="158">
+      <c r="B376" s="163">
         <v>59</v>
       </c>
-      <c r="C376" s="158" t="s">
+      <c r="C376" s="163" t="s">
         <v>89</v>
       </c>
-      <c r="D376" s="158" t="s">
+      <c r="D376" s="163" t="s">
         <v>88</v>
       </c>
       <c r="E376" s="26" t="s">
@@ -31031,9 +31053,9 @@
       <c r="Z376" s="121"/>
     </row>
     <row r="377" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B377" s="159"/>
-      <c r="C377" s="159"/>
-      <c r="D377" s="159"/>
+      <c r="B377" s="164"/>
+      <c r="C377" s="164"/>
+      <c r="D377" s="164"/>
       <c r="E377" s="3" t="s">
         <v>13</v>
       </c>
@@ -31074,9 +31096,9 @@
       <c r="Z377" s="121"/>
     </row>
     <row r="378" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B378" s="159"/>
-      <c r="C378" s="159"/>
-      <c r="D378" s="159"/>
+      <c r="B378" s="164"/>
+      <c r="C378" s="164"/>
+      <c r="D378" s="164"/>
       <c r="E378" s="3" t="s">
         <v>110</v>
       </c>
@@ -31117,9 +31139,9 @@
       <c r="Z378" s="121"/>
     </row>
     <row r="379" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B379" s="159"/>
-      <c r="C379" s="159"/>
-      <c r="D379" s="159"/>
+      <c r="B379" s="164"/>
+      <c r="C379" s="164"/>
+      <c r="D379" s="164"/>
       <c r="E379" s="3" t="s">
         <v>109</v>
       </c>
@@ -31160,9 +31182,9 @@
       <c r="Z379" s="121"/>
     </row>
     <row r="380" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B380" s="159"/>
-      <c r="C380" s="159"/>
-      <c r="D380" s="159"/>
+      <c r="B380" s="164"/>
+      <c r="C380" s="164"/>
+      <c r="D380" s="164"/>
       <c r="E380" s="3" t="s">
         <v>106</v>
       </c>
@@ -31203,9 +31225,9 @@
       <c r="Z380" s="121"/>
     </row>
     <row r="381" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B381" s="160"/>
-      <c r="C381" s="160"/>
-      <c r="D381" s="160"/>
+      <c r="B381" s="165"/>
+      <c r="C381" s="165"/>
+      <c r="D381" s="165"/>
       <c r="E381" s="4" t="s">
         <v>14</v>
       </c>
@@ -31249,13 +31271,13 @@
       <c r="A382" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B382" s="155">
+      <c r="B382" s="160">
         <v>60</v>
       </c>
-      <c r="C382" s="155" t="s">
+      <c r="C382" s="160" t="s">
         <v>90</v>
       </c>
-      <c r="D382" s="155" t="s">
+      <c r="D382" s="160" t="s">
         <v>88</v>
       </c>
       <c r="E382" s="27" t="s">
@@ -31296,9 +31318,9 @@
       <c r="Z382" s="121"/>
     </row>
     <row r="383" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B383" s="156"/>
-      <c r="C383" s="156"/>
-      <c r="D383" s="156"/>
+      <c r="B383" s="161"/>
+      <c r="C383" s="161"/>
+      <c r="D383" s="161"/>
       <c r="E383" s="6" t="s">
         <v>13</v>
       </c>
@@ -31339,9 +31361,9 @@
       <c r="Z383" s="121"/>
     </row>
     <row r="384" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B384" s="156"/>
-      <c r="C384" s="156"/>
-      <c r="D384" s="156"/>
+      <c r="B384" s="161"/>
+      <c r="C384" s="161"/>
+      <c r="D384" s="161"/>
       <c r="E384" s="6" t="s">
         <v>110</v>
       </c>
@@ -31382,9 +31404,9 @@
       <c r="Z384" s="121"/>
     </row>
     <row r="385" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B385" s="156"/>
-      <c r="C385" s="156"/>
-      <c r="D385" s="156"/>
+      <c r="B385" s="161"/>
+      <c r="C385" s="161"/>
+      <c r="D385" s="161"/>
       <c r="E385" s="6" t="s">
         <v>109</v>
       </c>
@@ -31425,9 +31447,9 @@
       <c r="Z385" s="121"/>
     </row>
     <row r="386" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B386" s="156"/>
-      <c r="C386" s="156"/>
-      <c r="D386" s="156"/>
+      <c r="B386" s="161"/>
+      <c r="C386" s="161"/>
+      <c r="D386" s="161"/>
       <c r="E386" s="6" t="s">
         <v>106</v>
       </c>
@@ -31468,9 +31490,9 @@
       <c r="Z386" s="121"/>
     </row>
     <row r="387" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B387" s="157"/>
-      <c r="C387" s="157"/>
-      <c r="D387" s="157"/>
+      <c r="B387" s="162"/>
+      <c r="C387" s="162"/>
+      <c r="D387" s="162"/>
       <c r="E387" s="7" t="s">
         <v>14</v>
       </c>
@@ -31514,13 +31536,13 @@
       <c r="A388" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B388" s="158">
+      <c r="B388" s="163">
         <v>61</v>
       </c>
-      <c r="C388" s="158" t="s">
+      <c r="C388" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="D388" s="158" t="s">
+      <c r="D388" s="163" t="s">
         <v>88</v>
       </c>
       <c r="E388" s="26" t="s">
@@ -31561,9 +31583,9 @@
       <c r="Z388" s="121"/>
     </row>
     <row r="389" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B389" s="159"/>
-      <c r="C389" s="159"/>
-      <c r="D389" s="159"/>
+      <c r="B389" s="164"/>
+      <c r="C389" s="164"/>
+      <c r="D389" s="164"/>
       <c r="E389" s="3" t="s">
         <v>13</v>
       </c>
@@ -31604,9 +31626,9 @@
       <c r="Z389" s="121"/>
     </row>
     <row r="390" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B390" s="159"/>
-      <c r="C390" s="159"/>
-      <c r="D390" s="159"/>
+      <c r="B390" s="164"/>
+      <c r="C390" s="164"/>
+      <c r="D390" s="164"/>
       <c r="E390" s="3" t="s">
         <v>110</v>
       </c>
@@ -31647,9 +31669,9 @@
       <c r="Z390" s="121"/>
     </row>
     <row r="391" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B391" s="159"/>
-      <c r="C391" s="159"/>
-      <c r="D391" s="159"/>
+      <c r="B391" s="164"/>
+      <c r="C391" s="164"/>
+      <c r="D391" s="164"/>
       <c r="E391" s="3" t="s">
         <v>109</v>
       </c>
@@ -31692,9 +31714,9 @@
       <c r="Z391" s="121"/>
     </row>
     <row r="392" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B392" s="159"/>
-      <c r="C392" s="159"/>
-      <c r="D392" s="159"/>
+      <c r="B392" s="164"/>
+      <c r="C392" s="164"/>
+      <c r="D392" s="164"/>
       <c r="E392" s="3" t="s">
         <v>106</v>
       </c>
@@ -31735,9 +31757,9 @@
       <c r="Z392" s="121"/>
     </row>
     <row r="393" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B393" s="160"/>
-      <c r="C393" s="160"/>
-      <c r="D393" s="160"/>
+      <c r="B393" s="165"/>
+      <c r="C393" s="165"/>
+      <c r="D393" s="165"/>
       <c r="E393" s="4" t="s">
         <v>14</v>
       </c>
@@ -31781,13 +31803,13 @@
       <c r="A394" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B394" s="155">
+      <c r="B394" s="160">
         <v>62</v>
       </c>
-      <c r="C394" s="155" t="s">
+      <c r="C394" s="160" t="s">
         <v>96</v>
       </c>
-      <c r="D394" s="155" t="s">
+      <c r="D394" s="160" t="s">
         <v>88</v>
       </c>
       <c r="E394" s="27" t="s">
@@ -31828,9 +31850,9 @@
       <c r="Z394" s="121"/>
     </row>
     <row r="395" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B395" s="156"/>
-      <c r="C395" s="156"/>
-      <c r="D395" s="156"/>
+      <c r="B395" s="161"/>
+      <c r="C395" s="161"/>
+      <c r="D395" s="161"/>
       <c r="E395" s="6" t="s">
         <v>13</v>
       </c>
@@ -31871,9 +31893,9 @@
       <c r="Z395" s="121"/>
     </row>
     <row r="396" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B396" s="156"/>
-      <c r="C396" s="156"/>
-      <c r="D396" s="156"/>
+      <c r="B396" s="161"/>
+      <c r="C396" s="161"/>
+      <c r="D396" s="161"/>
       <c r="E396" s="6" t="s">
         <v>110</v>
       </c>
@@ -31914,9 +31936,9 @@
       <c r="Z396" s="121"/>
     </row>
     <row r="397" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B397" s="156"/>
-      <c r="C397" s="156"/>
-      <c r="D397" s="156"/>
+      <c r="B397" s="161"/>
+      <c r="C397" s="161"/>
+      <c r="D397" s="161"/>
       <c r="E397" s="6" t="s">
         <v>109</v>
       </c>
@@ -31957,14 +31979,14 @@
       <c r="Z397" s="121"/>
     </row>
     <row r="398" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B398" s="156"/>
-      <c r="C398" s="156"/>
-      <c r="D398" s="156"/>
+      <c r="B398" s="161"/>
+      <c r="C398" s="161"/>
+      <c r="D398" s="161"/>
       <c r="E398" s="6" t="s">
         <v>106</v>
       </c>
       <c r="F398" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G398" s="37"/>
       <c r="H398" s="61" t="str">
@@ -32000,14 +32022,14 @@
       <c r="Z398" s="121"/>
     </row>
     <row r="399" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B399" s="157"/>
-      <c r="C399" s="157"/>
-      <c r="D399" s="157"/>
+      <c r="B399" s="162"/>
+      <c r="C399" s="162"/>
+      <c r="D399" s="162"/>
       <c r="E399" s="7" t="s">
         <v>14</v>
       </c>
       <c r="F399" s="32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G399" s="37"/>
       <c r="H399" s="61" t="str">
@@ -32046,13 +32068,13 @@
       <c r="A400" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B400" s="158">
+      <c r="B400" s="163">
         <v>63</v>
       </c>
-      <c r="C400" s="158" t="s">
-        <v>301</v>
-      </c>
-      <c r="D400" s="158" t="s">
+      <c r="C400" s="163" t="s">
+        <v>319</v>
+      </c>
+      <c r="D400" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E400" s="26" t="s">
@@ -32076,7 +32098,7 @@
       <c r="L400" s="41"/>
       <c r="U400" s="119" t="str" cm="1">
         <f t="array" ref="U400">IF(C400="",INDEX(C394:C400,MATCH(TRUE,INDEX((C394:C400&lt;&gt;""),0),0)),C400)</f>
-        <v>BOS Express</v>
+        <v>Britoil Courage</v>
       </c>
       <c r="V400" s="120">
         <f t="shared" si="69"/>
@@ -32093,9 +32115,9 @@
       <c r="Z400" s="121"/>
     </row>
     <row r="401" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B401" s="159"/>
-      <c r="C401" s="159"/>
-      <c r="D401" s="159"/>
+      <c r="B401" s="164"/>
+      <c r="C401" s="164"/>
+      <c r="D401" s="164"/>
       <c r="E401" s="3" t="s">
         <v>13</v>
       </c>
@@ -32119,7 +32141,7 @@
       <c r="L401" s="42"/>
       <c r="U401" s="119" t="str" cm="1">
         <f t="array" ref="U401">IF(C401="",INDEX(C395:C401,MATCH(TRUE,INDEX((C395:C401&lt;&gt;""),0),0)),C401)</f>
-        <v>BOS Express</v>
+        <v>Britoil Courage</v>
       </c>
       <c r="V401" s="120">
         <f t="shared" si="69"/>
@@ -32136,9 +32158,9 @@
       <c r="Z401" s="121"/>
     </row>
     <row r="402" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B402" s="159"/>
-      <c r="C402" s="159"/>
-      <c r="D402" s="159"/>
+      <c r="B402" s="164"/>
+      <c r="C402" s="164"/>
+      <c r="D402" s="164"/>
       <c r="E402" s="3" t="s">
         <v>110</v>
       </c>
@@ -32162,7 +32184,7 @@
       <c r="L402" s="42"/>
       <c r="U402" s="119" t="str" cm="1">
         <f t="array" ref="U402">IF(C402="",INDEX(C396:C402,MATCH(TRUE,INDEX((C396:C402&lt;&gt;""),0),0)),C402)</f>
-        <v>BOS Express</v>
+        <v>Britoil Courage</v>
       </c>
       <c r="V402" s="120">
         <f t="shared" si="69"/>
@@ -32179,9 +32201,9 @@
       <c r="Z402" s="121"/>
     </row>
     <row r="403" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B403" s="159"/>
-      <c r="C403" s="159"/>
-      <c r="D403" s="159"/>
+      <c r="B403" s="164"/>
+      <c r="C403" s="164"/>
+      <c r="D403" s="164"/>
       <c r="E403" s="3" t="s">
         <v>109</v>
       </c>
@@ -32205,7 +32227,7 @@
       <c r="L403" s="42"/>
       <c r="U403" s="119" t="str" cm="1">
         <f t="array" ref="U403">IF(C403="",INDEX(C397:C403,MATCH(TRUE,INDEX((C397:C403&lt;&gt;""),0),0)),C403)</f>
-        <v>BOS Express</v>
+        <v>Britoil Courage</v>
       </c>
       <c r="V403" s="120">
         <f t="shared" si="69"/>
@@ -32222,9 +32244,9 @@
       <c r="Z403" s="121"/>
     </row>
     <row r="404" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B404" s="159"/>
-      <c r="C404" s="159"/>
-      <c r="D404" s="159"/>
+      <c r="B404" s="164"/>
+      <c r="C404" s="164"/>
+      <c r="D404" s="164"/>
       <c r="E404" s="3" t="s">
         <v>106</v>
       </c>
@@ -32248,7 +32270,7 @@
       <c r="L404" s="42"/>
       <c r="U404" s="119" t="str" cm="1">
         <f t="array" ref="U404">IF(C404="",INDEX(C398:C404,MATCH(TRUE,INDEX((C398:C404&lt;&gt;""),0),0)),C404)</f>
-        <v>BOS Express</v>
+        <v>Britoil Courage</v>
       </c>
       <c r="V404" s="120">
         <f t="shared" si="69"/>
@@ -32265,9 +32287,9 @@
       <c r="Z404" s="121"/>
     </row>
     <row r="405" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B405" s="160"/>
-      <c r="C405" s="160"/>
-      <c r="D405" s="160"/>
+      <c r="B405" s="165"/>
+      <c r="C405" s="165"/>
+      <c r="D405" s="165"/>
       <c r="E405" s="4" t="s">
         <v>14</v>
       </c>
@@ -32291,7 +32313,7 @@
       <c r="L405" s="43"/>
       <c r="U405" s="119" t="str" cm="1">
         <f t="array" ref="U405">IF(C405="",INDEX(C399:C405,MATCH(TRUE,INDEX((C399:C405&lt;&gt;""),0),0)),C405)</f>
-        <v>BOS Express</v>
+        <v>Britoil Courage</v>
       </c>
       <c r="V405" s="120">
         <f t="shared" si="69"/>
@@ -32311,13 +32333,13 @@
       <c r="A406" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B406" s="155">
+      <c r="B406" s="160">
         <v>64</v>
       </c>
-      <c r="C406" s="155" t="s">
-        <v>306</v>
-      </c>
-      <c r="D406" s="155" t="s">
+      <c r="C406" s="160" t="s">
+        <v>305</v>
+      </c>
+      <c r="D406" s="160" t="s">
         <v>92</v>
       </c>
       <c r="E406" s="27" t="s">
@@ -32360,9 +32382,9 @@
       <c r="Z406" s="121"/>
     </row>
     <row r="407" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B407" s="156"/>
-      <c r="C407" s="156"/>
-      <c r="D407" s="156"/>
+      <c r="B407" s="161"/>
+      <c r="C407" s="161"/>
+      <c r="D407" s="161"/>
       <c r="E407" s="6" t="s">
         <v>13</v>
       </c>
@@ -32403,31 +32425,33 @@
       <c r="Z407" s="121"/>
     </row>
     <row r="408" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B408" s="156"/>
-      <c r="C408" s="156"/>
-      <c r="D408" s="156"/>
+      <c r="B408" s="161"/>
+      <c r="C408" s="161"/>
+      <c r="D408" s="161"/>
       <c r="E408" s="6" t="s">
         <v>103</v>
       </c>
       <c r="F408" s="32" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G408" s="37">
         <v>45708</v>
       </c>
-      <c r="H408" s="61">
+      <c r="H408" s="61" t="str">
         <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="I408" s="61">
+        <v/>
+      </c>
+      <c r="I408" s="61" t="str">
         <f t="shared" si="79"/>
-        <v>3428.6515803254165</v>
-      </c>
-      <c r="J408" s="62">
+        <v/>
+      </c>
+      <c r="J408" s="62" t="str">
         <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="K408" s="6"/>
+        <v/>
+      </c>
+      <c r="K408" s="6" t="s">
+        <v>320</v>
+      </c>
       <c r="L408" s="45" t="s">
         <v>124</v>
       </c>
@@ -32450,9 +32474,9 @@
       <c r="Z408" s="121"/>
     </row>
     <row r="409" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B409" s="156"/>
-      <c r="C409" s="156"/>
-      <c r="D409" s="156"/>
+      <c r="B409" s="161"/>
+      <c r="C409" s="161"/>
+      <c r="D409" s="161"/>
       <c r="E409" s="6" t="s">
         <v>106</v>
       </c>
@@ -32493,9 +32517,9 @@
       <c r="Z409" s="121"/>
     </row>
     <row r="410" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B410" s="156"/>
-      <c r="C410" s="156"/>
-      <c r="D410" s="156"/>
+      <c r="B410" s="161"/>
+      <c r="C410" s="161"/>
+      <c r="D410" s="161"/>
       <c r="E410" s="6" t="s">
         <v>93</v>
       </c>
@@ -32538,9 +32562,9 @@
       <c r="Z410" s="121"/>
     </row>
     <row r="411" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B411" s="156"/>
-      <c r="C411" s="156"/>
-      <c r="D411" s="156"/>
+      <c r="B411" s="161"/>
+      <c r="C411" s="161"/>
+      <c r="D411" s="161"/>
       <c r="E411" s="6" t="s">
         <v>109</v>
       </c>
@@ -32586,11 +32610,11 @@
       <c r="Z411" s="121"/>
     </row>
     <row r="412" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B412" s="156"/>
-      <c r="C412" s="156"/>
-      <c r="D412" s="156"/>
+      <c r="B412" s="161"/>
+      <c r="C412" s="161"/>
+      <c r="D412" s="161"/>
       <c r="E412" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F412" s="32" t="s">
         <v>21</v>
@@ -32629,9 +32653,9 @@
       <c r="Z412" s="121"/>
     </row>
     <row r="413" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B413" s="156"/>
-      <c r="C413" s="156"/>
-      <c r="D413" s="156"/>
+      <c r="B413" s="161"/>
+      <c r="C413" s="161"/>
+      <c r="D413" s="161"/>
       <c r="E413" s="6" t="s">
         <v>299</v>
       </c>
@@ -32672,9 +32696,9 @@
       <c r="Z413" s="121"/>
     </row>
     <row r="414" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B414" s="156"/>
-      <c r="C414" s="156"/>
-      <c r="D414" s="156"/>
+      <c r="B414" s="161"/>
+      <c r="C414" s="161"/>
+      <c r="D414" s="161"/>
       <c r="E414" s="6" t="s">
         <v>110</v>
       </c>
@@ -32715,9 +32739,9 @@
       <c r="Z414" s="121"/>
     </row>
     <row r="415" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B415" s="157"/>
-      <c r="C415" s="157"/>
-      <c r="D415" s="157"/>
+      <c r="B415" s="162"/>
+      <c r="C415" s="162"/>
+      <c r="D415" s="162"/>
       <c r="E415" s="7" t="s">
         <v>14</v>
       </c>
@@ -32740,7 +32764,7 @@
       <c r="K415" s="6"/>
       <c r="L415" s="46"/>
       <c r="U415" s="119" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="V415" s="120">
         <f t="shared" si="69"/>
@@ -32760,13 +32784,13 @@
       <c r="A416" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B416" s="158">
+      <c r="B416" s="163">
         <v>65</v>
       </c>
-      <c r="C416" s="158" t="s">
-        <v>307</v>
-      </c>
-      <c r="D416" s="158" t="s">
+      <c r="C416" s="163" t="s">
+        <v>306</v>
+      </c>
+      <c r="D416" s="163" t="s">
         <v>92</v>
       </c>
       <c r="E416" s="26" t="s">
@@ -32807,9 +32831,9 @@
       <c r="Z416" s="121"/>
     </row>
     <row r="417" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B417" s="159"/>
-      <c r="C417" s="159"/>
-      <c r="D417" s="159"/>
+      <c r="B417" s="164"/>
+      <c r="C417" s="164"/>
+      <c r="D417" s="164"/>
       <c r="E417" s="3" t="s">
         <v>13</v>
       </c>
@@ -32850,9 +32874,9 @@
       <c r="Z417" s="121"/>
     </row>
     <row r="418" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B418" s="159"/>
-      <c r="C418" s="159"/>
-      <c r="D418" s="159"/>
+      <c r="B418" s="164"/>
+      <c r="C418" s="164"/>
+      <c r="D418" s="164"/>
       <c r="E418" s="3" t="s">
         <v>103</v>
       </c>
@@ -32893,9 +32917,9 @@
       <c r="Z418" s="121"/>
     </row>
     <row r="419" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B419" s="159"/>
-      <c r="C419" s="159"/>
-      <c r="D419" s="159"/>
+      <c r="B419" s="164"/>
+      <c r="C419" s="164"/>
+      <c r="D419" s="164"/>
       <c r="E419" s="3" t="s">
         <v>106</v>
       </c>
@@ -32936,9 +32960,9 @@
       <c r="Z419" s="121"/>
     </row>
     <row r="420" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B420" s="159"/>
-      <c r="C420" s="159"/>
-      <c r="D420" s="159"/>
+      <c r="B420" s="164"/>
+      <c r="C420" s="164"/>
+      <c r="D420" s="164"/>
       <c r="E420" s="3" t="s">
         <v>93</v>
       </c>
@@ -32979,11 +33003,11 @@
       <c r="Z420" s="121"/>
     </row>
     <row r="421" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B421" s="159"/>
-      <c r="C421" s="159"/>
-      <c r="D421" s="159"/>
+      <c r="B421" s="164"/>
+      <c r="C421" s="164"/>
+      <c r="D421" s="164"/>
       <c r="E421" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F421" s="31" t="s">
         <v>21</v>
@@ -33022,9 +33046,9 @@
       <c r="Z421" s="121"/>
     </row>
     <row r="422" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B422" s="159"/>
-      <c r="C422" s="159"/>
-      <c r="D422" s="159"/>
+      <c r="B422" s="164"/>
+      <c r="C422" s="164"/>
+      <c r="D422" s="164"/>
       <c r="E422" s="3" t="s">
         <v>109</v>
       </c>
@@ -33065,9 +33089,9 @@
       <c r="Z422" s="121"/>
     </row>
     <row r="423" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B423" s="159"/>
-      <c r="C423" s="159"/>
-      <c r="D423" s="159"/>
+      <c r="B423" s="164"/>
+      <c r="C423" s="164"/>
+      <c r="D423" s="164"/>
       <c r="E423" s="3" t="s">
         <v>110</v>
       </c>
@@ -33108,9 +33132,9 @@
       <c r="Z423" s="121"/>
     </row>
     <row r="424" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B424" s="160"/>
-      <c r="C424" s="160"/>
-      <c r="D424" s="160"/>
+      <c r="B424" s="165"/>
+      <c r="C424" s="165"/>
+      <c r="D424" s="165"/>
       <c r="E424" s="4" t="s">
         <v>14</v>
       </c>
@@ -33133,7 +33157,7 @@
       <c r="K424" s="4"/>
       <c r="L424" s="43"/>
       <c r="U424" s="119" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="V424" s="120">
         <f t="shared" ref="V424:V451" si="91">MIN(Y424/21388,1.3)</f>
@@ -33153,13 +33177,13 @@
       <c r="A425" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B425" s="155">
+      <c r="B425" s="160">
         <v>66</v>
       </c>
-      <c r="C425" s="155" t="s">
+      <c r="C425" s="160" t="s">
         <v>94</v>
       </c>
-      <c r="D425" s="155" t="s">
+      <c r="D425" s="160" t="s">
         <v>88</v>
       </c>
       <c r="E425" s="27" t="s">
@@ -33200,9 +33224,9 @@
       <c r="Z425" s="121"/>
     </row>
     <row r="426" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B426" s="156"/>
-      <c r="C426" s="156"/>
-      <c r="D426" s="156"/>
+      <c r="B426" s="161"/>
+      <c r="C426" s="161"/>
+      <c r="D426" s="161"/>
       <c r="E426" s="6" t="s">
         <v>13</v>
       </c>
@@ -33243,9 +33267,9 @@
       <c r="Z426" s="121"/>
     </row>
     <row r="427" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B427" s="156"/>
-      <c r="C427" s="156"/>
-      <c r="D427" s="156"/>
+      <c r="B427" s="161"/>
+      <c r="C427" s="161"/>
+      <c r="D427" s="161"/>
       <c r="E427" s="6" t="s">
         <v>106</v>
       </c>
@@ -33286,9 +33310,9 @@
       <c r="Z427" s="121"/>
     </row>
     <row r="428" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B428" s="156"/>
-      <c r="C428" s="156"/>
-      <c r="D428" s="156"/>
+      <c r="B428" s="161"/>
+      <c r="C428" s="161"/>
+      <c r="D428" s="161"/>
       <c r="E428" s="6" t="s">
         <v>109</v>
       </c>
@@ -33329,11 +33353,11 @@
       <c r="Z428" s="121"/>
     </row>
     <row r="429" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B429" s="156"/>
-      <c r="C429" s="156"/>
-      <c r="D429" s="156"/>
+      <c r="B429" s="161"/>
+      <c r="C429" s="161"/>
+      <c r="D429" s="161"/>
       <c r="E429" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F429" s="32" t="s">
         <v>21</v>
@@ -33372,9 +33396,9 @@
       <c r="Z429" s="121"/>
     </row>
     <row r="430" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B430" s="156"/>
-      <c r="C430" s="156"/>
-      <c r="D430" s="156"/>
+      <c r="B430" s="161"/>
+      <c r="C430" s="161"/>
+      <c r="D430" s="161"/>
       <c r="E430" s="6" t="s">
         <v>110</v>
       </c>
@@ -33415,9 +33439,9 @@
       <c r="Z430" s="121"/>
     </row>
     <row r="431" spans="1:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B431" s="157"/>
-      <c r="C431" s="157"/>
-      <c r="D431" s="157"/>
+      <c r="B431" s="162"/>
+      <c r="C431" s="162"/>
+      <c r="D431" s="162"/>
       <c r="E431" s="7" t="s">
         <v>14</v>
       </c>
@@ -33461,13 +33485,13 @@
       <c r="A432" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="B432" s="158">
+      <c r="B432" s="163">
         <v>67</v>
       </c>
-      <c r="C432" s="158" t="s">
+      <c r="C432" s="163" t="s">
         <v>95</v>
       </c>
-      <c r="D432" s="158" t="s">
+      <c r="D432" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E432" s="26" t="s">
@@ -33508,9 +33532,9 @@
       <c r="Z432" s="121"/>
     </row>
     <row r="433" spans="2:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B433" s="159"/>
-      <c r="C433" s="159"/>
-      <c r="D433" s="159"/>
+      <c r="B433" s="164"/>
+      <c r="C433" s="164"/>
+      <c r="D433" s="164"/>
       <c r="E433" s="3" t="s">
         <v>13</v>
       </c>
@@ -33551,9 +33575,9 @@
       <c r="Z433" s="121"/>
     </row>
     <row r="434" spans="2:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B434" s="159"/>
-      <c r="C434" s="159"/>
-      <c r="D434" s="159"/>
+      <c r="B434" s="164"/>
+      <c r="C434" s="164"/>
+      <c r="D434" s="164"/>
       <c r="E434" s="3" t="s">
         <v>109</v>
       </c>
@@ -33594,9 +33618,9 @@
       <c r="Z434" s="121"/>
     </row>
     <row r="435" spans="2:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B435" s="159"/>
-      <c r="C435" s="159"/>
-      <c r="D435" s="159"/>
+      <c r="B435" s="164"/>
+      <c r="C435" s="164"/>
+      <c r="D435" s="164"/>
       <c r="E435" s="3" t="s">
         <v>106</v>
       </c>
@@ -33637,9 +33661,9 @@
       <c r="Z435" s="121"/>
     </row>
     <row r="436" spans="2:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B436" s="159"/>
-      <c r="C436" s="159"/>
-      <c r="D436" s="159"/>
+      <c r="B436" s="164"/>
+      <c r="C436" s="164"/>
+      <c r="D436" s="164"/>
       <c r="E436" s="3" t="s">
         <v>110</v>
       </c>
@@ -33680,9 +33704,9 @@
       <c r="Z436" s="121"/>
     </row>
     <row r="437" spans="2:26" ht="25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="B437" s="160"/>
-      <c r="C437" s="160"/>
-      <c r="D437" s="160"/>
+      <c r="B437" s="165"/>
+      <c r="C437" s="165"/>
+      <c r="D437" s="165"/>
       <c r="E437" s="4" t="s">
         <v>14</v>
       </c>
@@ -33723,13 +33747,13 @@
       <c r="Z437" s="121"/>
     </row>
     <row r="438" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B438" s="155">
+      <c r="B438" s="160">
         <v>68</v>
       </c>
-      <c r="C438" s="155" t="s">
-        <v>309</v>
-      </c>
-      <c r="D438" s="155" t="s">
+      <c r="C438" s="160" t="s">
+        <v>308</v>
+      </c>
+      <c r="D438" s="160" t="s">
         <v>88</v>
       </c>
       <c r="E438" s="27" t="s">
@@ -33770,9 +33794,9 @@
       <c r="Z438" s="138"/>
     </row>
     <row r="439" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B439" s="156"/>
-      <c r="C439" s="156"/>
-      <c r="D439" s="156"/>
+      <c r="B439" s="161"/>
+      <c r="C439" s="161"/>
+      <c r="D439" s="161"/>
       <c r="E439" s="6" t="s">
         <v>13</v>
       </c>
@@ -33811,9 +33835,9 @@
       <c r="Z439" s="138"/>
     </row>
     <row r="440" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B440" s="156"/>
-      <c r="C440" s="156"/>
-      <c r="D440" s="156"/>
+      <c r="B440" s="161"/>
+      <c r="C440" s="161"/>
+      <c r="D440" s="161"/>
       <c r="E440" s="6" t="s">
         <v>103</v>
       </c>
@@ -33852,9 +33876,9 @@
       <c r="Z440" s="138"/>
     </row>
     <row r="441" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B441" s="156"/>
-      <c r="C441" s="156"/>
-      <c r="D441" s="156"/>
+      <c r="B441" s="161"/>
+      <c r="C441" s="161"/>
+      <c r="D441" s="161"/>
       <c r="E441" s="6" t="s">
         <v>106</v>
       </c>
@@ -33893,9 +33917,9 @@
       <c r="Z441" s="138"/>
     </row>
     <row r="442" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B442" s="156"/>
-      <c r="C442" s="156"/>
-      <c r="D442" s="156"/>
+      <c r="B442" s="161"/>
+      <c r="C442" s="161"/>
+      <c r="D442" s="161"/>
       <c r="E442" s="6" t="s">
         <v>109</v>
       </c>
@@ -33934,9 +33958,9 @@
       <c r="Z442" s="138"/>
     </row>
     <row r="443" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B443" s="156"/>
-      <c r="C443" s="156"/>
-      <c r="D443" s="156"/>
+      <c r="B443" s="161"/>
+      <c r="C443" s="161"/>
+      <c r="D443" s="161"/>
       <c r="E443" s="6" t="s">
         <v>290</v>
       </c>
@@ -33977,9 +34001,9 @@
       <c r="Z443" s="138"/>
     </row>
     <row r="444" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B444" s="156"/>
-      <c r="C444" s="156"/>
-      <c r="D444" s="156"/>
+      <c r="B444" s="161"/>
+      <c r="C444" s="161"/>
+      <c r="D444" s="161"/>
       <c r="E444" s="6" t="s">
         <v>110</v>
       </c>
@@ -34018,9 +34042,9 @@
       <c r="Z444" s="138"/>
     </row>
     <row r="445" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B445" s="157"/>
-      <c r="C445" s="157"/>
-      <c r="D445" s="157"/>
+      <c r="B445" s="162"/>
+      <c r="C445" s="162"/>
+      <c r="D445" s="162"/>
       <c r="E445" s="7" t="s">
         <v>14</v>
       </c>
@@ -34061,13 +34085,13 @@
       <c r="Z445" s="138"/>
     </row>
     <row r="446" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B446" s="158">
+      <c r="B446" s="163">
         <v>69</v>
       </c>
-      <c r="C446" s="158" t="s">
-        <v>308</v>
-      </c>
-      <c r="D446" s="158" t="s">
+      <c r="C446" s="163" t="s">
+        <v>307</v>
+      </c>
+      <c r="D446" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E446" s="26" t="s">
@@ -34108,9 +34132,9 @@
       <c r="Z446" s="138"/>
     </row>
     <row r="447" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B447" s="159"/>
-      <c r="C447" s="159"/>
-      <c r="D447" s="159"/>
+      <c r="B447" s="164"/>
+      <c r="C447" s="164"/>
+      <c r="D447" s="164"/>
       <c r="E447" s="3" t="s">
         <v>13</v>
       </c>
@@ -34149,9 +34173,9 @@
       <c r="Z447" s="138"/>
     </row>
     <row r="448" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B448" s="159"/>
-      <c r="C448" s="159"/>
-      <c r="D448" s="159"/>
+      <c r="B448" s="164"/>
+      <c r="C448" s="164"/>
+      <c r="D448" s="164"/>
       <c r="E448" s="3" t="s">
         <v>109</v>
       </c>
@@ -34190,9 +34214,9 @@
       <c r="Z448" s="138"/>
     </row>
     <row r="449" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B449" s="159"/>
-      <c r="C449" s="159"/>
-      <c r="D449" s="159"/>
+      <c r="B449" s="164"/>
+      <c r="C449" s="164"/>
+      <c r="D449" s="164"/>
       <c r="E449" s="3" t="s">
         <v>106</v>
       </c>
@@ -34231,9 +34255,9 @@
       <c r="Z449" s="138"/>
     </row>
     <row r="450" spans="2:26" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B450" s="159"/>
-      <c r="C450" s="159"/>
-      <c r="D450" s="159"/>
+      <c r="B450" s="164"/>
+      <c r="C450" s="164"/>
+      <c r="D450" s="164"/>
       <c r="E450" s="3" t="s">
         <v>110</v>
       </c>
@@ -34272,9 +34296,9 @@
       <c r="Z450" s="138"/>
     </row>
     <row r="451" spans="2:26" ht="41" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B451" s="160"/>
-      <c r="C451" s="160"/>
-      <c r="D451" s="160"/>
+      <c r="B451" s="165"/>
+      <c r="C451" s="165"/>
+      <c r="D451" s="165"/>
       <c r="E451" s="4" t="s">
         <v>14</v>
       </c>
@@ -34315,13 +34339,13 @@
       <c r="Z451" s="138"/>
     </row>
     <row r="452" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B452" s="155">
+      <c r="B452" s="160">
         <v>70</v>
       </c>
-      <c r="C452" s="155" t="s">
-        <v>302</v>
-      </c>
-      <c r="D452" s="155" t="s">
+      <c r="C452" s="160" t="s">
+        <v>301</v>
+      </c>
+      <c r="D452" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E452" s="27" t="s">
@@ -34362,9 +34386,9 @@
       <c r="Z452" s="138"/>
     </row>
     <row r="453" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B453" s="156"/>
-      <c r="C453" s="156"/>
-      <c r="D453" s="156"/>
+      <c r="B453" s="161"/>
+      <c r="C453" s="161"/>
+      <c r="D453" s="161"/>
       <c r="E453" s="6" t="s">
         <v>13</v>
       </c>
@@ -34403,9 +34427,9 @@
       <c r="Z453" s="138"/>
     </row>
     <row r="454" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B454" s="156"/>
-      <c r="C454" s="156"/>
-      <c r="D454" s="156"/>
+      <c r="B454" s="161"/>
+      <c r="C454" s="161"/>
+      <c r="D454" s="161"/>
       <c r="E454" s="6" t="s">
         <v>103</v>
       </c>
@@ -34444,9 +34468,9 @@
       <c r="Z454" s="138"/>
     </row>
     <row r="455" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B455" s="156"/>
-      <c r="C455" s="156"/>
-      <c r="D455" s="156"/>
+      <c r="B455" s="161"/>
+      <c r="C455" s="161"/>
+      <c r="D455" s="161"/>
       <c r="E455" s="6" t="s">
         <v>106</v>
       </c>
@@ -34485,9 +34509,9 @@
       <c r="Z455" s="138"/>
     </row>
     <row r="456" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B456" s="156"/>
-      <c r="C456" s="156"/>
-      <c r="D456" s="156"/>
+      <c r="B456" s="161"/>
+      <c r="C456" s="161"/>
+      <c r="D456" s="161"/>
       <c r="E456" s="6" t="s">
         <v>109</v>
       </c>
@@ -34526,9 +34550,9 @@
       <c r="Z456" s="138"/>
     </row>
     <row r="457" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B457" s="156"/>
-      <c r="C457" s="156"/>
-      <c r="D457" s="156"/>
+      <c r="B457" s="161"/>
+      <c r="C457" s="161"/>
+      <c r="D457" s="161"/>
       <c r="E457" s="6" t="s">
         <v>110</v>
       </c>
@@ -34567,9 +34591,9 @@
       <c r="Z457" s="138"/>
     </row>
     <row r="458" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B458" s="157"/>
-      <c r="C458" s="157"/>
-      <c r="D458" s="157"/>
+      <c r="B458" s="162"/>
+      <c r="C458" s="162"/>
+      <c r="D458" s="162"/>
       <c r="E458" s="7" t="s">
         <v>14</v>
       </c>
@@ -34610,13 +34634,13 @@
       <c r="Z458" s="138"/>
     </row>
     <row r="459" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B459" s="158">
+      <c r="B459" s="163">
         <v>71</v>
       </c>
-      <c r="C459" s="158" t="s">
-        <v>303</v>
-      </c>
-      <c r="D459" s="158" t="s">
+      <c r="C459" s="163" t="s">
+        <v>302</v>
+      </c>
+      <c r="D459" s="163" t="s">
         <v>12</v>
       </c>
       <c r="E459" s="26" t="s">
@@ -34657,9 +34681,9 @@
       <c r="Z459" s="138"/>
     </row>
     <row r="460" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B460" s="159"/>
-      <c r="C460" s="159"/>
-      <c r="D460" s="159"/>
+      <c r="B460" s="164"/>
+      <c r="C460" s="164"/>
+      <c r="D460" s="164"/>
       <c r="E460" s="3" t="s">
         <v>13</v>
       </c>
@@ -34698,9 +34722,9 @@
       <c r="Z460" s="138"/>
     </row>
     <row r="461" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B461" s="159"/>
-      <c r="C461" s="159"/>
-      <c r="D461" s="159"/>
+      <c r="B461" s="164"/>
+      <c r="C461" s="164"/>
+      <c r="D461" s="164"/>
       <c r="E461" s="3" t="s">
         <v>109</v>
       </c>
@@ -34739,9 +34763,9 @@
       <c r="Z461" s="138"/>
     </row>
     <row r="462" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B462" s="159"/>
-      <c r="C462" s="159"/>
-      <c r="D462" s="159"/>
+      <c r="B462" s="164"/>
+      <c r="C462" s="164"/>
+      <c r="D462" s="164"/>
       <c r="E462" s="3" t="s">
         <v>106</v>
       </c>
@@ -34780,9 +34804,9 @@
       <c r="Z462" s="138"/>
     </row>
     <row r="463" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B463" s="159"/>
-      <c r="C463" s="159"/>
-      <c r="D463" s="159"/>
+      <c r="B463" s="164"/>
+      <c r="C463" s="164"/>
+      <c r="D463" s="164"/>
       <c r="E463" s="3" t="s">
         <v>110</v>
       </c>
@@ -34821,9 +34845,9 @@
       <c r="Z463" s="138"/>
     </row>
     <row r="464" spans="2:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B464" s="160"/>
-      <c r="C464" s="160"/>
-      <c r="D464" s="160"/>
+      <c r="B464" s="165"/>
+      <c r="C464" s="165"/>
+      <c r="D464" s="165"/>
       <c r="E464" s="4" t="s">
         <v>14</v>
       </c>
@@ -34864,13 +34888,13 @@
       <c r="Z464" s="138"/>
     </row>
     <row r="465" spans="1:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B465" s="155">
+      <c r="B465" s="160">
         <v>72</v>
       </c>
-      <c r="C465" s="155" t="s">
-        <v>304</v>
-      </c>
-      <c r="D465" s="155" t="s">
+      <c r="C465" s="160" t="s">
+        <v>303</v>
+      </c>
+      <c r="D465" s="160" t="s">
         <v>12</v>
       </c>
       <c r="E465" s="27" t="s">
@@ -34911,9 +34935,9 @@
       <c r="Z465" s="138"/>
     </row>
     <row r="466" spans="1:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B466" s="156"/>
-      <c r="C466" s="156"/>
-      <c r="D466" s="156"/>
+      <c r="B466" s="161"/>
+      <c r="C466" s="161"/>
+      <c r="D466" s="161"/>
       <c r="E466" s="6" t="s">
         <v>13</v>
       </c>
@@ -34952,9 +34976,9 @@
       <c r="Z466" s="138"/>
     </row>
     <row r="467" spans="1:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B467" s="156"/>
-      <c r="C467" s="156"/>
-      <c r="D467" s="156"/>
+      <c r="B467" s="161"/>
+      <c r="C467" s="161"/>
+      <c r="D467" s="161"/>
       <c r="E467" s="6" t="s">
         <v>103</v>
       </c>
@@ -34993,9 +35017,9 @@
       <c r="Z467" s="138"/>
     </row>
     <row r="468" spans="1:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B468" s="156"/>
-      <c r="C468" s="156"/>
-      <c r="D468" s="156"/>
+      <c r="B468" s="161"/>
+      <c r="C468" s="161"/>
+      <c r="D468" s="161"/>
       <c r="E468" s="6" t="s">
         <v>106</v>
       </c>
@@ -35034,9 +35058,9 @@
       <c r="Z468" s="138"/>
     </row>
     <row r="469" spans="1:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B469" s="156"/>
-      <c r="C469" s="156"/>
-      <c r="D469" s="156"/>
+      <c r="B469" s="161"/>
+      <c r="C469" s="161"/>
+      <c r="D469" s="161"/>
       <c r="E469" s="6" t="s">
         <v>109</v>
       </c>
@@ -35075,9 +35099,9 @@
       <c r="Z469" s="138"/>
     </row>
     <row r="470" spans="1:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B470" s="156"/>
-      <c r="C470" s="156"/>
-      <c r="D470" s="156"/>
+      <c r="B470" s="161"/>
+      <c r="C470" s="161"/>
+      <c r="D470" s="161"/>
       <c r="E470" s="6" t="s">
         <v>110</v>
       </c>
@@ -35116,9 +35140,9 @@
       <c r="Z470" s="138"/>
     </row>
     <row r="471" spans="1:26" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B471" s="157"/>
-      <c r="C471" s="157"/>
-      <c r="D471" s="157"/>
+      <c r="B471" s="162"/>
+      <c r="C471" s="162"/>
+      <c r="D471" s="162"/>
       <c r="E471" s="7" t="s">
         <v>14</v>
       </c>
@@ -38484,6 +38508,225 @@
   </sheetData>
   <autoFilter ref="B8:K471" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="243">
+    <mergeCell ref="B452:B458"/>
+    <mergeCell ref="C452:C458"/>
+    <mergeCell ref="D452:D458"/>
+    <mergeCell ref="B459:B464"/>
+    <mergeCell ref="C459:C464"/>
+    <mergeCell ref="D459:D464"/>
+    <mergeCell ref="B465:B471"/>
+    <mergeCell ref="C465:C471"/>
+    <mergeCell ref="D465:D471"/>
+    <mergeCell ref="AB1:AE1"/>
+    <mergeCell ref="K183:K188"/>
+    <mergeCell ref="K14:K18"/>
+    <mergeCell ref="K332:K338"/>
+    <mergeCell ref="K110:K116"/>
+    <mergeCell ref="K117:K122"/>
+    <mergeCell ref="K65:K69"/>
+    <mergeCell ref="T2:T6"/>
+    <mergeCell ref="U2:W6"/>
+    <mergeCell ref="K195:K200"/>
+    <mergeCell ref="K2:K6"/>
+    <mergeCell ref="K81:K85"/>
+    <mergeCell ref="K104:K109"/>
+    <mergeCell ref="K60:K64"/>
+    <mergeCell ref="K86:K90"/>
+    <mergeCell ref="C332:C338"/>
+    <mergeCell ref="D332:D338"/>
+    <mergeCell ref="D117:D122"/>
+    <mergeCell ref="D123:D130"/>
+    <mergeCell ref="D131:D136"/>
+    <mergeCell ref="D137:D146"/>
+    <mergeCell ref="D147:D152"/>
+    <mergeCell ref="D153:D158"/>
+    <mergeCell ref="D159:D164"/>
+    <mergeCell ref="D165:D170"/>
+    <mergeCell ref="D171:D176"/>
+    <mergeCell ref="D177:D182"/>
+    <mergeCell ref="D183:D188"/>
+    <mergeCell ref="D189:D194"/>
+    <mergeCell ref="D195:D200"/>
+    <mergeCell ref="D201:D207"/>
+    <mergeCell ref="D290:D295"/>
+    <mergeCell ref="D296:D302"/>
+    <mergeCell ref="D303:D309"/>
+    <mergeCell ref="D310:D316"/>
+    <mergeCell ref="D208:D213"/>
+    <mergeCell ref="D214:D219"/>
+    <mergeCell ref="D324:D331"/>
+    <mergeCell ref="D283:D289"/>
+    <mergeCell ref="C275:C282"/>
+    <mergeCell ref="C283:C289"/>
+    <mergeCell ref="C290:C295"/>
+    <mergeCell ref="C159:C164"/>
+    <mergeCell ref="D220:D225"/>
+    <mergeCell ref="D226:D231"/>
+    <mergeCell ref="D232:D238"/>
+    <mergeCell ref="D239:D244"/>
+    <mergeCell ref="D245:D250"/>
+    <mergeCell ref="D251:D257"/>
+    <mergeCell ref="D258:D264"/>
+    <mergeCell ref="D265:D274"/>
+    <mergeCell ref="D275:D282"/>
+    <mergeCell ref="C208:C213"/>
+    <mergeCell ref="C214:C219"/>
+    <mergeCell ref="C303:C309"/>
+    <mergeCell ref="C317:C323"/>
+    <mergeCell ref="C324:C331"/>
+    <mergeCell ref="K24:K28"/>
+    <mergeCell ref="K91:K96"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="D45:D49"/>
+    <mergeCell ref="D50:D54"/>
+    <mergeCell ref="D55:D59"/>
+    <mergeCell ref="D60:D64"/>
+    <mergeCell ref="D65:D69"/>
+    <mergeCell ref="D70:D75"/>
+    <mergeCell ref="D76:D80"/>
+    <mergeCell ref="D81:D85"/>
+    <mergeCell ref="D86:D90"/>
+    <mergeCell ref="D91:D96"/>
+    <mergeCell ref="C117:C122"/>
+    <mergeCell ref="C123:C130"/>
+    <mergeCell ref="C131:C136"/>
+    <mergeCell ref="C310:C316"/>
+    <mergeCell ref="C220:C225"/>
+    <mergeCell ref="C226:C231"/>
+    <mergeCell ref="C258:C264"/>
+    <mergeCell ref="C265:C274"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B65:B69"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="B76:B80"/>
+    <mergeCell ref="B81:B85"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="C19:C23"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="B39:B44"/>
+    <mergeCell ref="B45:B49"/>
+    <mergeCell ref="B50:B54"/>
+    <mergeCell ref="C39:C44"/>
+    <mergeCell ref="C45:C49"/>
+    <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="D14:D18"/>
+    <mergeCell ref="D19:D23"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="D29:D33"/>
+    <mergeCell ref="D34:D38"/>
+    <mergeCell ref="C165:C170"/>
+    <mergeCell ref="C171:C176"/>
+    <mergeCell ref="C177:C182"/>
+    <mergeCell ref="C137:C146"/>
+    <mergeCell ref="C55:C59"/>
+    <mergeCell ref="C60:C64"/>
+    <mergeCell ref="C65:C69"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="C81:C85"/>
+    <mergeCell ref="C86:C90"/>
+    <mergeCell ref="C91:C96"/>
+    <mergeCell ref="C97:C103"/>
+    <mergeCell ref="C104:C109"/>
+    <mergeCell ref="C110:C116"/>
+    <mergeCell ref="D97:D103"/>
+    <mergeCell ref="D104:D109"/>
+    <mergeCell ref="D110:D116"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="C4:D6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="E2:H3"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="B220:B225"/>
+    <mergeCell ref="B165:B170"/>
+    <mergeCell ref="B171:B176"/>
+    <mergeCell ref="B177:B182"/>
+    <mergeCell ref="B183:B188"/>
+    <mergeCell ref="B189:B194"/>
+    <mergeCell ref="B195:B200"/>
+    <mergeCell ref="B201:B207"/>
+    <mergeCell ref="B208:B213"/>
+    <mergeCell ref="B214:B219"/>
+    <mergeCell ref="B104:B109"/>
+    <mergeCell ref="B110:B116"/>
+    <mergeCell ref="B117:B122"/>
+    <mergeCell ref="B123:B130"/>
+    <mergeCell ref="B131:B136"/>
+    <mergeCell ref="B137:B146"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="D339:D346"/>
+    <mergeCell ref="B258:B264"/>
+    <mergeCell ref="B265:B274"/>
+    <mergeCell ref="B432:B437"/>
+    <mergeCell ref="C432:C437"/>
+    <mergeCell ref="D432:D437"/>
+    <mergeCell ref="B400:B405"/>
+    <mergeCell ref="C400:C405"/>
+    <mergeCell ref="D400:D405"/>
+    <mergeCell ref="C406:C415"/>
+    <mergeCell ref="D406:D415"/>
+    <mergeCell ref="B416:B424"/>
+    <mergeCell ref="C416:C424"/>
+    <mergeCell ref="D416:D424"/>
+    <mergeCell ref="B406:B415"/>
+    <mergeCell ref="B425:B431"/>
+    <mergeCell ref="C425:C431"/>
+    <mergeCell ref="D425:D431"/>
+    <mergeCell ref="B290:B295"/>
+    <mergeCell ref="C296:C302"/>
+    <mergeCell ref="B275:B282"/>
+    <mergeCell ref="B283:B289"/>
+    <mergeCell ref="B310:B316"/>
+    <mergeCell ref="B317:B323"/>
+    <mergeCell ref="C339:C346"/>
+    <mergeCell ref="B86:B90"/>
+    <mergeCell ref="B91:B96"/>
+    <mergeCell ref="B97:B103"/>
+    <mergeCell ref="B226:B231"/>
+    <mergeCell ref="B232:B238"/>
+    <mergeCell ref="B239:B244"/>
+    <mergeCell ref="B245:B250"/>
+    <mergeCell ref="B251:B257"/>
+    <mergeCell ref="B296:B302"/>
+    <mergeCell ref="C232:C238"/>
+    <mergeCell ref="C239:C244"/>
+    <mergeCell ref="C245:C250"/>
+    <mergeCell ref="C251:C257"/>
+    <mergeCell ref="B147:B152"/>
+    <mergeCell ref="B153:B158"/>
+    <mergeCell ref="B159:B164"/>
+    <mergeCell ref="C183:C188"/>
+    <mergeCell ref="C189:C194"/>
+    <mergeCell ref="C195:C200"/>
+    <mergeCell ref="C201:C207"/>
+    <mergeCell ref="B303:B309"/>
+    <mergeCell ref="C147:C152"/>
+    <mergeCell ref="C153:C158"/>
+    <mergeCell ref="C347:C352"/>
+    <mergeCell ref="C353:C361"/>
+    <mergeCell ref="B394:B399"/>
+    <mergeCell ref="C394:C399"/>
+    <mergeCell ref="D394:D399"/>
+    <mergeCell ref="C388:C393"/>
+    <mergeCell ref="D388:D393"/>
+    <mergeCell ref="B347:B352"/>
+    <mergeCell ref="D369:D375"/>
+    <mergeCell ref="B362:B368"/>
+    <mergeCell ref="B369:B375"/>
+    <mergeCell ref="C369:C375"/>
+    <mergeCell ref="D376:D381"/>
     <mergeCell ref="AM1:AP1"/>
     <mergeCell ref="AJ25:AK25"/>
     <mergeCell ref="B438:B445"/>
@@ -38508,225 +38751,6 @@
     <mergeCell ref="C382:C387"/>
     <mergeCell ref="D382:D387"/>
     <mergeCell ref="B339:B346"/>
-    <mergeCell ref="C347:C352"/>
-    <mergeCell ref="C353:C361"/>
-    <mergeCell ref="B394:B399"/>
-    <mergeCell ref="C394:C399"/>
-    <mergeCell ref="D394:D399"/>
-    <mergeCell ref="C388:C393"/>
-    <mergeCell ref="D388:D393"/>
-    <mergeCell ref="B347:B352"/>
-    <mergeCell ref="D369:D375"/>
-    <mergeCell ref="B362:B368"/>
-    <mergeCell ref="B369:B375"/>
-    <mergeCell ref="C369:C375"/>
-    <mergeCell ref="D376:D381"/>
-    <mergeCell ref="C339:C346"/>
-    <mergeCell ref="B86:B90"/>
-    <mergeCell ref="B91:B96"/>
-    <mergeCell ref="B97:B103"/>
-    <mergeCell ref="B226:B231"/>
-    <mergeCell ref="B232:B238"/>
-    <mergeCell ref="B239:B244"/>
-    <mergeCell ref="B245:B250"/>
-    <mergeCell ref="B251:B257"/>
-    <mergeCell ref="B296:B302"/>
-    <mergeCell ref="C232:C238"/>
-    <mergeCell ref="C239:C244"/>
-    <mergeCell ref="C245:C250"/>
-    <mergeCell ref="C251:C257"/>
-    <mergeCell ref="B147:B152"/>
-    <mergeCell ref="B153:B158"/>
-    <mergeCell ref="B159:B164"/>
-    <mergeCell ref="C183:C188"/>
-    <mergeCell ref="C189:C194"/>
-    <mergeCell ref="C195:C200"/>
-    <mergeCell ref="C201:C207"/>
-    <mergeCell ref="B303:B309"/>
-    <mergeCell ref="C147:C152"/>
-    <mergeCell ref="C153:C158"/>
-    <mergeCell ref="D339:D346"/>
-    <mergeCell ref="B258:B264"/>
-    <mergeCell ref="B265:B274"/>
-    <mergeCell ref="B432:B437"/>
-    <mergeCell ref="C432:C437"/>
-    <mergeCell ref="D432:D437"/>
-    <mergeCell ref="B400:B405"/>
-    <mergeCell ref="C400:C405"/>
-    <mergeCell ref="D400:D405"/>
-    <mergeCell ref="C406:C415"/>
-    <mergeCell ref="D406:D415"/>
-    <mergeCell ref="B416:B424"/>
-    <mergeCell ref="C416:C424"/>
-    <mergeCell ref="D416:D424"/>
-    <mergeCell ref="B406:B415"/>
-    <mergeCell ref="B425:B431"/>
-    <mergeCell ref="C425:C431"/>
-    <mergeCell ref="D425:D431"/>
-    <mergeCell ref="B290:B295"/>
-    <mergeCell ref="C296:C302"/>
-    <mergeCell ref="B275:B282"/>
-    <mergeCell ref="B283:B289"/>
-    <mergeCell ref="B310:B316"/>
-    <mergeCell ref="B317:B323"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="C4:D6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="E2:H3"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:G6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="B220:B225"/>
-    <mergeCell ref="B165:B170"/>
-    <mergeCell ref="B171:B176"/>
-    <mergeCell ref="B177:B182"/>
-    <mergeCell ref="B183:B188"/>
-    <mergeCell ref="B189:B194"/>
-    <mergeCell ref="B195:B200"/>
-    <mergeCell ref="B201:B207"/>
-    <mergeCell ref="B208:B213"/>
-    <mergeCell ref="B214:B219"/>
-    <mergeCell ref="B104:B109"/>
-    <mergeCell ref="B110:B116"/>
-    <mergeCell ref="B117:B122"/>
-    <mergeCell ref="B123:B130"/>
-    <mergeCell ref="B131:B136"/>
-    <mergeCell ref="B137:B146"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="D14:D18"/>
-    <mergeCell ref="D19:D23"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="D29:D33"/>
-    <mergeCell ref="D34:D38"/>
-    <mergeCell ref="C165:C170"/>
-    <mergeCell ref="C171:C176"/>
-    <mergeCell ref="C177:C182"/>
-    <mergeCell ref="C137:C146"/>
-    <mergeCell ref="C55:C59"/>
-    <mergeCell ref="C60:C64"/>
-    <mergeCell ref="C65:C69"/>
-    <mergeCell ref="C70:C75"/>
-    <mergeCell ref="C76:C80"/>
-    <mergeCell ref="C81:C85"/>
-    <mergeCell ref="C86:C90"/>
-    <mergeCell ref="C91:C96"/>
-    <mergeCell ref="C97:C103"/>
-    <mergeCell ref="C104:C109"/>
-    <mergeCell ref="C110:C116"/>
-    <mergeCell ref="D97:D103"/>
-    <mergeCell ref="D104:D109"/>
-    <mergeCell ref="D110:D116"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="B60:B64"/>
-    <mergeCell ref="B65:B69"/>
-    <mergeCell ref="B70:B75"/>
-    <mergeCell ref="B76:B80"/>
-    <mergeCell ref="B81:B85"/>
-    <mergeCell ref="C9:C13"/>
-    <mergeCell ref="C14:C18"/>
-    <mergeCell ref="C19:C23"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="B39:B44"/>
-    <mergeCell ref="B45:B49"/>
-    <mergeCell ref="B50:B54"/>
-    <mergeCell ref="C39:C44"/>
-    <mergeCell ref="C45:C49"/>
-    <mergeCell ref="C50:C54"/>
-    <mergeCell ref="C303:C309"/>
-    <mergeCell ref="C317:C323"/>
-    <mergeCell ref="C324:C331"/>
-    <mergeCell ref="K24:K28"/>
-    <mergeCell ref="K91:K96"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="D45:D49"/>
-    <mergeCell ref="D50:D54"/>
-    <mergeCell ref="D55:D59"/>
-    <mergeCell ref="D60:D64"/>
-    <mergeCell ref="D65:D69"/>
-    <mergeCell ref="D70:D75"/>
-    <mergeCell ref="D76:D80"/>
-    <mergeCell ref="D81:D85"/>
-    <mergeCell ref="D86:D90"/>
-    <mergeCell ref="D91:D96"/>
-    <mergeCell ref="C117:C122"/>
-    <mergeCell ref="C123:C130"/>
-    <mergeCell ref="C131:C136"/>
-    <mergeCell ref="C310:C316"/>
-    <mergeCell ref="C220:C225"/>
-    <mergeCell ref="C226:C231"/>
-    <mergeCell ref="C258:C264"/>
-    <mergeCell ref="C265:C274"/>
-    <mergeCell ref="C275:C282"/>
-    <mergeCell ref="C283:C289"/>
-    <mergeCell ref="C290:C295"/>
-    <mergeCell ref="C159:C164"/>
-    <mergeCell ref="D220:D225"/>
-    <mergeCell ref="D226:D231"/>
-    <mergeCell ref="D232:D238"/>
-    <mergeCell ref="D239:D244"/>
-    <mergeCell ref="D245:D250"/>
-    <mergeCell ref="D251:D257"/>
-    <mergeCell ref="D258:D264"/>
-    <mergeCell ref="D265:D274"/>
-    <mergeCell ref="D275:D282"/>
-    <mergeCell ref="C208:C213"/>
-    <mergeCell ref="C214:C219"/>
-    <mergeCell ref="C332:C338"/>
-    <mergeCell ref="D332:D338"/>
-    <mergeCell ref="D117:D122"/>
-    <mergeCell ref="D123:D130"/>
-    <mergeCell ref="D131:D136"/>
-    <mergeCell ref="D137:D146"/>
-    <mergeCell ref="D147:D152"/>
-    <mergeCell ref="D153:D158"/>
-    <mergeCell ref="D159:D164"/>
-    <mergeCell ref="D165:D170"/>
-    <mergeCell ref="D171:D176"/>
-    <mergeCell ref="D177:D182"/>
-    <mergeCell ref="D183:D188"/>
-    <mergeCell ref="D189:D194"/>
-    <mergeCell ref="D195:D200"/>
-    <mergeCell ref="D201:D207"/>
-    <mergeCell ref="D290:D295"/>
-    <mergeCell ref="D296:D302"/>
-    <mergeCell ref="D303:D309"/>
-    <mergeCell ref="D310:D316"/>
-    <mergeCell ref="D208:D213"/>
-    <mergeCell ref="D214:D219"/>
-    <mergeCell ref="D324:D331"/>
-    <mergeCell ref="D283:D289"/>
-    <mergeCell ref="AB1:AE1"/>
-    <mergeCell ref="K183:K188"/>
-    <mergeCell ref="K14:K18"/>
-    <mergeCell ref="K332:K338"/>
-    <mergeCell ref="K110:K116"/>
-    <mergeCell ref="K117:K122"/>
-    <mergeCell ref="K65:K69"/>
-    <mergeCell ref="T2:T6"/>
-    <mergeCell ref="U2:W6"/>
-    <mergeCell ref="K195:K200"/>
-    <mergeCell ref="K2:K6"/>
-    <mergeCell ref="K81:K85"/>
-    <mergeCell ref="K104:K109"/>
-    <mergeCell ref="K60:K64"/>
-    <mergeCell ref="K86:K90"/>
-    <mergeCell ref="B452:B458"/>
-    <mergeCell ref="C452:C458"/>
-    <mergeCell ref="D452:D458"/>
-    <mergeCell ref="B459:B464"/>
-    <mergeCell ref="C459:C464"/>
-    <mergeCell ref="D459:D464"/>
-    <mergeCell ref="B465:B471"/>
-    <mergeCell ref="C465:C471"/>
-    <mergeCell ref="D465:D471"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="F7:F1048576">
@@ -38869,7 +38893,7 @@
       </c>
       <c r="J3" s="116">
         <f>R18</f>
-        <v>0.62228672047360289</v>
+        <v>0.64709378138821827</v>
       </c>
       <c r="K3" s="128">
         <v>0.8</v>
@@ -38896,15 +38920,15 @@
       </c>
       <c r="T3" s="8">
         <f>SUM(C3:C17)</f>
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U3" s="8">
         <f>SUM(D3:D17)</f>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="V3" s="8">
         <f>W4-T3-U3</f>
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="W3" s="8">
         <v>0</v>
@@ -38976,7 +39000,7 @@
       </c>
       <c r="W4" s="8">
         <f>SUM(E3:E17)</f>
-        <v>570</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -38988,19 +39012,19 @@
       </c>
       <c r="C5" s="22">
         <f>COUNTIFS(Tracker!E:E,A5,Tracker!F:F,"Done")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="22">
         <f>COUNTIFS(Tracker!E:E,A5,Tracker!F:F,"In Process")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" s="22">
         <f>COUNTIF(Tracker!E:E,A5)-COUNTIFS(Tracker!E:E,A5,Tracker!F:F,"No need")</f>
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="F5" s="25">
         <f>(C5+D5)/E5</f>
-        <v>0.58730158730158732</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="G5" s="28" t="b">
         <v>1</v>
@@ -39010,14 +39034,14 @@
       </c>
       <c r="J5" s="153">
         <f>Tracker!AD123</f>
-        <v>7.3261073197654084E-2</v>
+        <v>7.3772553683058351E-2</v>
       </c>
       <c r="K5" s="128">
         <v>0.2</v>
       </c>
       <c r="N5" s="108">
         <f>C5*(Tracker!AC7+Tracker!AD7)</f>
-        <v>215600</v>
+        <v>223300</v>
       </c>
       <c r="O5" s="113">
         <f>C5*(Tracker!AE5)</f>
@@ -39029,7 +39053,7 @@
       </c>
       <c r="R5" s="114">
         <f t="shared" si="0"/>
-        <v>0.58730158730158732</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="S5" s="8" t="s">
         <v>196</v>
@@ -39146,11 +39170,11 @@
       </c>
       <c r="E8" s="22">
         <f>COUNTIF(Tracker!E:E,A8)-COUNTIFS(Tracker!E:E,A8,Tracker!F:F,"No need")</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" s="25">
         <f t="shared" si="1"/>
-        <v>0.39436619718309857</v>
+        <v>0.4</v>
       </c>
       <c r="G8" s="28" t="b">
         <v>1</v>
@@ -39172,7 +39196,7 @@
       </c>
       <c r="R8" s="114">
         <f t="shared" si="0"/>
-        <v>0.39436619718309857</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -39267,7 +39291,7 @@
       </c>
       <c r="C11" s="22">
         <f>COUNTIFS(Tracker!E:E,A11,Tracker!F:F,"Done")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>COUNTIFS(Tracker!E:E,A11,Tracker!F:F,"In Process")</f>
@@ -39279,18 +39303,18 @@
       </c>
       <c r="F11" s="25">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G11" s="28" t="b">
         <v>0</v>
       </c>
       <c r="N11" s="108">
         <f>C11*(Tracker!AC10+Tracker!AD10)</f>
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="O11" s="113">
         <f>C11*(Tracker!AE10)</f>
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="Q11" s="108" t="str">
         <f t="shared" si="2"/>
@@ -39298,7 +39322,7 @@
       </c>
       <c r="R11" s="114">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -39314,14 +39338,14 @@
       </c>
       <c r="D12" s="22">
         <f>COUNTIFS(Tracker!E:E,A12,Tracker!F:F,"In Process")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="22">
         <v>72</v>
       </c>
       <c r="F12" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.7777777777777776E-2</v>
       </c>
       <c r="G12" s="28" t="b">
         <v>0</v>
@@ -39420,18 +39444,18 @@
     </row>
     <row r="15" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B15" s="109" t="s">
         <v>291</v>
       </c>
       <c r="C15" s="109">
         <f>COUNTIFS(Tracker!E:E,A15,Tracker!F:F,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="22">
         <f>COUNTIFS(Tracker!E:E,A15,Tracker!F:F,"In Process")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="22">
         <f>COUNTIF(Tracker!E:E,A15)-COUNTIFS(Tracker!E:E,A15,Tracker!F:F,"No need")</f>
@@ -39454,7 +39478,7 @@
     </row>
     <row r="16" spans="1:23" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B16" s="109">
         <v>2</v>
@@ -39541,7 +39565,7 @@
       </c>
       <c r="R18" s="115">
         <f>AVERAGE(R3:R17)</f>
-        <v>0.62228672047360289</v>
+        <v>0.64709378138821827</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -39564,13 +39588,13 @@
       </c>
       <c r="C21" s="95">
         <f>SUM(Tracker!H9:H491)+SUM(Tracker!I9:I491)+C13*Tracker!AD12</f>
-        <v>1657967.5126239005</v>
+        <v>1670508.0961286696</v>
       </c>
       <c r="D21" s="211"/>
       <c r="E21" s="214"/>
       <c r="G21" s="88">
         <f>MAX(B26:B92)</f>
-        <v>83316.233401907608</v>
+        <v>79887.581821582193</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -39579,7 +39603,7 @@
       </c>
       <c r="C22" s="93">
         <f>SUM(Tracker!J9:J491)</f>
-        <v>7014.2808958294409</v>
+        <v>7055.9397699644705</v>
       </c>
       <c r="D22" s="211" t="s">
         <v>298</v>
@@ -39604,14 +39628,14 @@
       </c>
       <c r="B25" s="77">
         <f>SUM(B26:B53)</f>
-        <v>678473.38040022447</v>
+        <v>694442.61548531894</v>
       </c>
       <c r="C25" s="75" t="s">
         <v>121</v>
       </c>
       <c r="D25" s="78">
         <f>SUM(D26:D53)</f>
-        <v>396663.58238264447</v>
+        <v>393234.93080231902</v>
       </c>
       <c r="E25" s="76" t="s">
         <v>122</v>
@@ -39630,7 +39654,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="70" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D26" s="81">
         <f>SUMIF(Tracker!$U$9:$U$491, C26, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, C26, Tracker!$I$9:$I$491)</f>
@@ -39719,11 +39743,11 @@
         <v>28470</v>
       </c>
       <c r="C29" s="70" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D29" s="82">
         <f>SUMIF(Tracker!$U$9:$U$491, C29, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, C29, Tracker!$I$9:$I$491)</f>
-        <v>83316.233401907608</v>
+        <v>79887.581821582193</v>
       </c>
       <c r="E29" s="72" t="s">
         <v>58</v>
@@ -39737,11 +39761,11 @@
       </c>
       <c r="R29" s="91">
         <f>D25</f>
-        <v>396663.58238264447</v>
+        <v>393234.93080231902</v>
       </c>
       <c r="S29" s="111">
         <f>R29/16</f>
-        <v>24791.473898915279</v>
+        <v>24577.183175144939</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -39771,11 +39795,11 @@
       </c>
       <c r="R30" s="91">
         <f>B25</f>
-        <v>678473.38040022447</v>
+        <v>694442.61548531894</v>
       </c>
       <c r="S30" s="111">
         <f>R30/28</f>
-        <v>24231.192157150876</v>
+        <v>24801.521981618534</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -39784,7 +39808,7 @@
       </c>
       <c r="B31" s="80">
         <f>SUMIF(Tracker!$U$9:$U$491, A31, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A31, Tracker!$I$9:$I$491)</f>
-        <v>10954.740976248364</v>
+        <v>16894.987843650648</v>
       </c>
       <c r="C31" s="70" t="s">
         <v>95</v>
@@ -39807,7 +39831,7 @@
       </c>
       <c r="B32" s="80">
         <f>SUMIF(Tracker!$U$9:$U$491, A32, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A32, Tracker!$I$9:$I$491)</f>
-        <v>16894.987843650648</v>
+        <v>26923.976061342808</v>
       </c>
       <c r="C32" s="70" t="s">
         <v>90</v>
@@ -40040,7 +40064,7 @@
         <v>25029.156536375536</v>
       </c>
       <c r="C42" s="70" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D42" s="82">
         <f>SUMIF(Tracker!$U$9:$U$491, C42, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, C42, Tracker!$I$9:$I$491)</f>
@@ -40063,7 +40087,7 @@
         <v>61944.305217879184</v>
       </c>
       <c r="C43" s="70" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D43" s="82">
         <f>SUMIF(Tracker!$U$9:$U$491, C43, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, C43, Tracker!$I$9:$I$491)</f>
@@ -40086,7 +40110,7 @@
         <v>25600.598466429772</v>
       </c>
       <c r="C44" s="70" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D44" s="82">
         <f>SUMIF(Tracker!$U$9:$U$491, C44, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, C44, Tracker!$I$9:$I$491)</f>
@@ -40109,7 +40133,7 @@
         <v>14560</v>
       </c>
       <c r="C45" s="70" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D45" s="82">
         <f>SUMIF(Tracker!$U$9:$U$491, C45, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, C45, Tracker!$I$9:$I$491)</f>
@@ -40132,7 +40156,7 @@
         <v>10660</v>
       </c>
       <c r="C46" s="70" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D46" s="82">
         <f>SUMIF(Tracker!$U$9:$U$491, C46, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, C46, Tracker!$I$9:$I$491)</f>
@@ -40175,7 +40199,7 @@
       <c r="C48" s="70"/>
       <c r="D48" s="82"/>
       <c r="E48" s="72" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="F48" s="84">
         <f>SUMIF(Tracker!$U$9:$U$491, E48, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E48, Tracker!$I$9:$I$491)</f>
@@ -40249,7 +40273,7 @@
     </row>
     <row r="54" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="89" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B54" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A54, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A54, Tracker!$I$9:$I$491)</f>
@@ -40276,11 +40300,11 @@
     </row>
     <row r="57" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="89" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B57" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A57, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A57, Tracker!$I$9:$I$491)</f>
-        <v>83316.233401907608</v>
+        <v>79887.581821582193</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -40591,7 +40615,7 @@
     </row>
     <row r="92" spans="1:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="89" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B92" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A92, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A92, Tracker!$I$9:$I$491)</f>
@@ -40600,7 +40624,7 @@
     </row>
     <row r="93" spans="1:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="89" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B93" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A93, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A93, Tracker!$I$9:$I$491)</f>
@@ -40609,7 +40633,7 @@
     </row>
     <row r="94" spans="1:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="89" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B94" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A94, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A94, Tracker!$I$9:$I$491)</f>
@@ -40618,7 +40642,7 @@
     </row>
     <row r="95" spans="1:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="89" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B95" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A95, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A95, Tracker!$I$9:$I$491)</f>
@@ -40627,7 +40651,7 @@
     </row>
     <row r="96" spans="1:2" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="89" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B96" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A96, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A96, Tracker!$I$9:$I$491)</f>
@@ -40636,7 +40660,7 @@
     </row>
     <row r="97" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="89" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B97" s="90">
         <f>SUMIF(Tracker!$U$9:$U$491, A97, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A97, Tracker!$I$9:$I$491)</f>
@@ -40645,11 +40669,11 @@
     </row>
     <row r="99" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B99" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A99, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A99, Tracker!$I$9:$I$491)</f>
-        <v>83316.233401907608</v>
+        <v>79887.581821582193</v>
       </c>
       <c r="C99" s="8">
         <f>SUMIF(Tracker!$U$9:$U$491, A99, Tracker!$J$9:$J$491)</f>
@@ -40686,11 +40710,11 @@
         <v>285.72096502711798</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F100" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E100, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E100, Tracker!$I$9:$I$491)</f>
-        <v>83316.233401907608</v>
+        <v>79887.581821582193</v>
       </c>
       <c r="G100" s="8">
         <f>SUMIF(Tracker!$U$9:$U$491, E100, Tracker!$J$9:$J$491)</f>
@@ -40698,11 +40722,11 @@
       </c>
       <c r="H100" s="49">
         <f t="shared" ref="H100:H163" si="3">80*((F100/52000)+(G100/210))/2</f>
-        <v>137.4516695199321</v>
+        <v>134.81424522737407</v>
       </c>
       <c r="I100" s="49">
         <f>H100</f>
-        <v>137.4516695199321</v>
+        <v>134.81424522737407</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -41554,19 +41578,19 @@
       </c>
       <c r="F127" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E127, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E127, Tracker!$I$9:$I$491)</f>
-        <v>16894.987843650648</v>
+        <v>26923.976061342808</v>
       </c>
       <c r="G127" s="8">
         <f>SUMIF(Tracker!$U$9:$U$491, E127, Tracker!$J$9:$J$491)</f>
-        <v>55.545165513371984</v>
+        <v>91.032354591359635</v>
       </c>
       <c r="H127" s="49">
         <f t="shared" si="3"/>
-        <v>23.576176021472453</v>
+        <v>38.050246929057472</v>
       </c>
       <c r="I127" s="8">
         <f>H127*(21600/VLOOKUP(E127, Tracker!$U$9:$W$491, 3, FALSE))</f>
-        <v>31.827837628987812</v>
+        <v>51.367833354227592</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -41746,19 +41770,19 @@
       </c>
       <c r="F133" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E133, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E133, Tracker!$I$9:$I$491)</f>
-        <v>10954.740976248364</v>
+        <v>16894.987843650648</v>
       </c>
       <c r="G133" s="8">
         <f>SUMIF(Tracker!$U$9:$U$491, E133, Tracker!$J$9:$J$491)</f>
-        <v>49.373480456330654</v>
+        <v>55.545165513371984</v>
       </c>
       <c r="H133" s="49">
         <f t="shared" si="3"/>
-        <v>17.831196295755863</v>
+        <v>23.576176021472453</v>
       </c>
       <c r="I133" s="8">
         <f>H133*(21600/VLOOKUP(E133, Tracker!$U$9:$W$491, 3, FALSE))</f>
-        <v>24.072114999270415</v>
+        <v>31.827837628987812</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
@@ -41927,11 +41951,11 @@
       </c>
       <c r="B139" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A139, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A139, Tracker!$I$9:$I$491)</f>
-        <v>16894.987843650648</v>
+        <v>26923.976061342808</v>
       </c>
       <c r="C139" s="8">
         <f>SUMIF(Tracker!$U$9:$U$491, A139, Tracker!$J$9:$J$491)</f>
-        <v>55.545165513371984</v>
+        <v>91.032354591359635</v>
       </c>
       <c r="E139" s="8" t="s">
         <v>15</v>
@@ -42051,7 +42075,7 @@
     </row>
     <row r="143" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B143" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A143, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A143, Tracker!$I$9:$I$491)</f>
@@ -42126,7 +42150,7 @@
         <v>54.858425285206657</v>
       </c>
       <c r="E145" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F145" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E145, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E145, Tracker!$I$9:$I$491)</f>
@@ -42247,11 +42271,11 @@
       </c>
       <c r="B149" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A149, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A149, Tracker!$I$9:$I$491)</f>
-        <v>10954.740976248364</v>
+        <v>16894.987843650648</v>
       </c>
       <c r="C149" s="8">
         <f>SUMIF(Tracker!$U$9:$U$491, A149, Tracker!$J$9:$J$491)</f>
-        <v>49.373480456330654</v>
+        <v>55.545165513371984</v>
       </c>
       <c r="E149" s="8" t="s">
         <v>39</v>
@@ -42499,7 +42523,7 @@
     </row>
     <row r="157" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="8" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B157" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A157, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A157, Tracker!$I$9:$I$491)</f>
@@ -42766,7 +42790,7 @@
         <v>0</v>
       </c>
       <c r="E165" s="8" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="F165" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E165, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E165, Tracker!$I$9:$I$491)</f>
@@ -42787,7 +42811,7 @@
     </row>
     <row r="166" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B166" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A166, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A166, Tracker!$I$9:$I$491)</f>
@@ -42798,7 +42822,7 @@
         <v>0</v>
       </c>
       <c r="E166" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F166" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E166, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E166, Tracker!$I$9:$I$491)</f>
@@ -42819,7 +42843,7 @@
     </row>
     <row r="167" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B167" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A167, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A167, Tracker!$I$9:$I$491)</f>
@@ -42830,7 +42854,7 @@
         <v>0</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F167" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E167, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E167, Tracker!$I$9:$I$491)</f>
@@ -42851,7 +42875,7 @@
     </row>
     <row r="168" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="150" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B168" s="152">
         <f>SUMIF(Tracker!$U$9:$U$491, A168, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A168, Tracker!$I$9:$I$491)</f>
@@ -42862,7 +42886,7 @@
         <v>0</v>
       </c>
       <c r="E168" s="150" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F168" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E168, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E168, Tracker!$I$9:$I$491)</f>
@@ -42883,7 +42907,7 @@
     </row>
     <row r="169" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="150" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B169" s="151">
         <f>SUMIF(Tracker!$U$9:$U$491, A169, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A169, Tracker!$I$9:$I$491)</f>
@@ -42894,7 +42918,7 @@
         <v>0</v>
       </c>
       <c r="E169" s="150" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F169" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E169, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E169, Tracker!$I$9:$I$491)</f>
@@ -42915,7 +42939,7 @@
     </row>
     <row r="170" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="150" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B170" s="151">
         <f>SUMIF(Tracker!$U$9:$U$491, A170, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, A170, Tracker!$I$9:$I$491)</f>
@@ -42926,7 +42950,7 @@
         <v>0</v>
       </c>
       <c r="E170" s="150" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F170" s="91">
         <f>SUMIF(Tracker!$U$9:$U$491, E170, Tracker!$H$9:$H$491)+SUMIF(Tracker!$U$9:$U$491, E170, Tracker!$I$9:$I$491)</f>
@@ -43000,11 +43024,11 @@
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="129">
         <f>Summary!C21</f>
-        <v>1657967.5126239005</v>
+        <v>1670508.0961286696</v>
       </c>
       <c r="B1" s="130">
         <f>Summary!C22</f>
-        <v>7014.2808958294409</v>
+        <v>7055.9397699644705</v>
       </c>
       <c r="C1" s="132">
         <f>Summary!C23</f>
@@ -43016,7 +43040,7 @@
       </c>
       <c r="E1" s="116">
         <f>Summary!J3</f>
-        <v>0.62228672047360289</v>
+        <v>0.64709378138821827</v>
       </c>
       <c r="F1" s="8">
         <f>Tracker!AE115</f>
@@ -43024,7 +43048,7 @@
       </c>
       <c r="G1" s="133">
         <f>Summary!J5</f>
-        <v>7.3261073197654084E-2</v>
+        <v>7.3772553683058351E-2</v>
       </c>
     </row>
   </sheetData>
@@ -43052,7 +43076,7 @@
       </c>
       <c r="B1" s="91">
         <f>Summary!B99</f>
-        <v>83316.233401907608</v>
+        <v>79887.581821582193</v>
       </c>
       <c r="C1" s="8">
         <f>Summary!C99</f>
@@ -43126,11 +43150,11 @@
       </c>
       <c r="E2" s="111">
         <f>Summary!D25</f>
-        <v>396663.58238264447</v>
+        <v>393234.93080231902</v>
       </c>
       <c r="F2" s="91">
         <f>E2/16</f>
-        <v>24791.473898915279</v>
+        <v>24577.183175144939</v>
       </c>
       <c r="G2" s="22" t="str">
         <f>Summary!A4</f>
@@ -43171,11 +43195,11 @@
       </c>
       <c r="E3" s="111">
         <f>Summary!B25</f>
-        <v>678473.38040022447</v>
+        <v>694442.61548531894</v>
       </c>
       <c r="F3" s="91">
         <f>E3/28</f>
-        <v>24231.192157150876</v>
+        <v>24801.521981618534</v>
       </c>
       <c r="G3" s="22" t="str">
         <f>Summary!A5</f>
@@ -43183,19 +43207,19 @@
       </c>
       <c r="H3" s="134">
         <f>Summary!C5</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="134">
         <f>Summary!D5</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J3" s="134">
         <f>Summary!E5</f>
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="K3" s="25">
         <f>Summary!F5</f>
-        <v>0.58730158730158732</v>
+        <v>0.95454545454545459</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -43259,11 +43283,11 @@
       </c>
       <c r="J5" s="134">
         <f>Summary!E8</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K5" s="25">
         <f>Summary!F8</f>
-        <v>0.39436619718309857</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -43353,7 +43377,7 @@
       </c>
       <c r="H8" s="134">
         <f>Summary!C11</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" s="134">
         <f>Summary!D11</f>
@@ -43365,7 +43389,7 @@
       </c>
       <c r="K8" s="25">
         <f>Summary!F11</f>
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -43903,11 +43927,11 @@
       </c>
       <c r="B41" s="91">
         <f>Summary!B139</f>
-        <v>16894.987843650648</v>
+        <v>26923.976061342808</v>
       </c>
       <c r="C41" s="8">
         <f>Summary!C139</f>
-        <v>55.545165513371984</v>
+        <v>91.032354591359635</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -44043,11 +44067,11 @@
       </c>
       <c r="B51" s="91">
         <f>Summary!B149</f>
-        <v>10954.740976248364</v>
+        <v>16894.987843650648</v>
       </c>
       <c r="C51" s="8">
         <f>Summary!C149</f>
-        <v>49.373480456330654</v>
+        <v>55.545165513371984</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -44151,7 +44175,7 @@
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="8" t="str">
         <f>Summary!A157</f>
-        <v>BOS Express</v>
+        <v>Britoil Courage</v>
       </c>
       <c r="B59" s="91">
         <f>Summary!B157</f>
@@ -44363,11 +44387,11 @@
       </c>
       <c r="B2" s="111">
         <f>Sheet2!E2</f>
-        <v>396663.58238264447</v>
+        <v>393234.93080231902</v>
       </c>
       <c r="C2" s="91">
         <f>Sheet2!F2</f>
-        <v>24791.473898915279</v>
+        <v>24577.183175144939</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -44376,11 +44400,11 @@
       </c>
       <c r="B3" s="111">
         <f>Sheet2!E3</f>
-        <v>678473.38040022447</v>
+        <v>694442.61548531894</v>
       </c>
       <c r="C3" s="91">
         <f>Sheet2!F3</f>
-        <v>24231.192157150876</v>
+        <v>24801.521981618534</v>
       </c>
     </row>
   </sheetData>
@@ -44447,19 +44471,19 @@
       </c>
       <c r="B3" s="134">
         <f>Sheet2!H3</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="134">
         <f>Sheet2!I3</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D3" s="134">
         <f>Sheet2!J3</f>
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E3" s="135">
         <f>Summary!N5</f>
-        <v>215600</v>
+        <v>223300</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -44499,7 +44523,7 @@
       </c>
       <c r="D5" s="134">
         <f>Sheet2!J5</f>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" s="135">
         <f>Summary!N8</f>
@@ -44547,7 +44571,7 @@
       </c>
       <c r="E7" s="135">
         <f>Summary!N11</f>
-        <v>24000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -44557,7 +44581,7 @@
       </c>
       <c r="B8" s="134">
         <f>Sheet2!H8</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="134">
         <f>Sheet2!I8</f>
